--- a/downloads/dados.xlsx
+++ b/downloads/dados.xlsx
@@ -2246,7 +2246,7 @@
         <v>28</v>
       </c>
       <c r="G2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s">
         <v>36</v>
@@ -2272,7 +2272,7 @@
         <v>28</v>
       </c>
       <c r="G3">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H3" t="s">
         <v>36</v>
@@ -2298,7 +2298,7 @@
         <v>28</v>
       </c>
       <c r="G4">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H4" t="s">
         <v>36</v>
@@ -2324,7 +2324,7 @@
         <v>28</v>
       </c>
       <c r="G5">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H5" t="s">
         <v>36</v>
@@ -2350,7 +2350,7 @@
         <v>28</v>
       </c>
       <c r="G6">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H6" t="s">
         <v>36</v>
@@ -2376,7 +2376,7 @@
         <v>28</v>
       </c>
       <c r="G7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H7" t="s">
         <v>36</v>
@@ -2402,7 +2402,7 @@
         <v>28</v>
       </c>
       <c r="G8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H8" t="s">
         <v>36</v>
@@ -2454,7 +2454,7 @@
         <v>28</v>
       </c>
       <c r="G10">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H10" t="s">
         <v>36</v>
@@ -2480,7 +2480,7 @@
         <v>28</v>
       </c>
       <c r="G11">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H11" t="s">
         <v>36</v>
@@ -2506,7 +2506,7 @@
         <v>28</v>
       </c>
       <c r="G12">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H12" t="s">
         <v>36</v>
@@ -2532,7 +2532,7 @@
         <v>28</v>
       </c>
       <c r="G13">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s">
         <v>36</v>
@@ -2558,7 +2558,7 @@
         <v>28</v>
       </c>
       <c r="G14">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H14" t="s">
         <v>36</v>
@@ -2584,7 +2584,7 @@
         <v>28</v>
       </c>
       <c r="G15">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H15" t="s">
         <v>36</v>
@@ -2610,7 +2610,7 @@
         <v>28</v>
       </c>
       <c r="G16">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H16" t="s">
         <v>36</v>
@@ -2636,7 +2636,7 @@
         <v>28</v>
       </c>
       <c r="G17">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H17" t="s">
         <v>36</v>
@@ -2662,7 +2662,7 @@
         <v>28</v>
       </c>
       <c r="G18">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H18" t="s">
         <v>36</v>
@@ -2688,7 +2688,7 @@
         <v>28</v>
       </c>
       <c r="G19">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H19" t="s">
         <v>36</v>
@@ -2714,7 +2714,7 @@
         <v>28</v>
       </c>
       <c r="G20">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s">
         <v>36</v>
@@ -2740,7 +2740,7 @@
         <v>28</v>
       </c>
       <c r="G21">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s">
         <v>36</v>
@@ -2766,7 +2766,7 @@
         <v>28</v>
       </c>
       <c r="G22">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H22" t="s">
         <v>36</v>
@@ -2870,7 +2870,7 @@
         <v>28</v>
       </c>
       <c r="G26">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H26" t="s">
         <v>36</v>
@@ -2922,7 +2922,7 @@
         <v>28</v>
       </c>
       <c r="G28">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s">
         <v>36</v>
@@ -2948,7 +2948,7 @@
         <v>28</v>
       </c>
       <c r="G29">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H29" t="s">
         <v>36</v>
@@ -2974,7 +2974,7 @@
         <v>28</v>
       </c>
       <c r="G30">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H30" t="s">
         <v>36</v>
@@ -3000,7 +3000,7 @@
         <v>28</v>
       </c>
       <c r="G31">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H31" t="s">
         <v>36</v>
@@ -3026,7 +3026,7 @@
         <v>28</v>
       </c>
       <c r="G32">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s">
         <v>36</v>
@@ -3052,7 +3052,7 @@
         <v>28</v>
       </c>
       <c r="G33">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H33" t="s">
         <v>36</v>
@@ -3104,7 +3104,7 @@
         <v>29</v>
       </c>
       <c r="G35">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H35" t="s">
         <v>36</v>
@@ -3130,7 +3130,7 @@
         <v>29</v>
       </c>
       <c r="G36">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H36" t="s">
         <v>36</v>
@@ -3156,7 +3156,7 @@
         <v>29</v>
       </c>
       <c r="G37">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H37" t="s">
         <v>36</v>
@@ -3182,7 +3182,7 @@
         <v>29</v>
       </c>
       <c r="G38">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H38" t="s">
         <v>36</v>
@@ -3208,7 +3208,7 @@
         <v>29</v>
       </c>
       <c r="G39">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H39" t="s">
         <v>36</v>
@@ -3234,7 +3234,7 @@
         <v>29</v>
       </c>
       <c r="G40">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H40" t="s">
         <v>36</v>
@@ -3260,7 +3260,7 @@
         <v>29</v>
       </c>
       <c r="G41">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="H41" t="s">
         <v>36</v>
@@ -3286,7 +3286,7 @@
         <v>29</v>
       </c>
       <c r="G42">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H42" t="s">
         <v>36</v>
@@ -3312,7 +3312,7 @@
         <v>29</v>
       </c>
       <c r="G43">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H43" t="s">
         <v>36</v>
@@ -3338,7 +3338,7 @@
         <v>29</v>
       </c>
       <c r="G44">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H44" t="s">
         <v>36</v>
@@ -3364,7 +3364,7 @@
         <v>29</v>
       </c>
       <c r="G45">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H45" t="s">
         <v>36</v>
@@ -3390,7 +3390,7 @@
         <v>29</v>
       </c>
       <c r="G46">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H46" t="s">
         <v>36</v>
@@ -3416,7 +3416,7 @@
         <v>29</v>
       </c>
       <c r="G47">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s">
         <v>36</v>
@@ -3442,7 +3442,7 @@
         <v>29</v>
       </c>
       <c r="G48">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H48" t="s">
         <v>36</v>
@@ -3468,7 +3468,7 @@
         <v>29</v>
       </c>
       <c r="G49">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H49" t="s">
         <v>36</v>
@@ -3520,7 +3520,7 @@
         <v>29</v>
       </c>
       <c r="G51">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H51" t="s">
         <v>36</v>
@@ -3546,7 +3546,7 @@
         <v>29</v>
       </c>
       <c r="G52">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H52" t="s">
         <v>36</v>
@@ -3572,7 +3572,7 @@
         <v>29</v>
       </c>
       <c r="G53">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H53" t="s">
         <v>36</v>
@@ -3598,7 +3598,7 @@
         <v>29</v>
       </c>
       <c r="G54">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H54" t="s">
         <v>36</v>
@@ -3624,7 +3624,7 @@
         <v>29</v>
       </c>
       <c r="G55">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H55" t="s">
         <v>36</v>
@@ -3650,7 +3650,7 @@
         <v>29</v>
       </c>
       <c r="G56">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H56" t="s">
         <v>36</v>
@@ -3676,7 +3676,7 @@
         <v>29</v>
       </c>
       <c r="G57">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H57" t="s">
         <v>36</v>
@@ -3702,7 +3702,7 @@
         <v>29</v>
       </c>
       <c r="G58">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s">
         <v>36</v>
@@ -3728,7 +3728,7 @@
         <v>29</v>
       </c>
       <c r="G59">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H59" t="s">
         <v>36</v>
@@ -3754,7 +3754,7 @@
         <v>29</v>
       </c>
       <c r="G60">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H60" t="s">
         <v>36</v>
@@ -3780,7 +3780,7 @@
         <v>29</v>
       </c>
       <c r="G61">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H61" t="s">
         <v>36</v>
@@ -3806,7 +3806,7 @@
         <v>29</v>
       </c>
       <c r="G62">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H62" t="s">
         <v>36</v>
@@ -3832,7 +3832,7 @@
         <v>29</v>
       </c>
       <c r="G63">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H63" t="s">
         <v>36</v>
@@ -3858,7 +3858,7 @@
         <v>29</v>
       </c>
       <c r="G64">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H64" t="s">
         <v>36</v>
@@ -3884,7 +3884,7 @@
         <v>29</v>
       </c>
       <c r="G65">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H65" t="s">
         <v>36</v>
@@ -3910,7 +3910,7 @@
         <v>29</v>
       </c>
       <c r="G66">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H66" t="s">
         <v>36</v>
@@ -3936,7 +3936,7 @@
         <v>29</v>
       </c>
       <c r="G67">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H67" t="s">
         <v>36</v>
@@ -3962,7 +3962,7 @@
         <v>30</v>
       </c>
       <c r="G68">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H68" t="s">
         <v>36</v>
@@ -3988,7 +3988,7 @@
         <v>30</v>
       </c>
       <c r="G69">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H69" t="s">
         <v>36</v>
@@ -4014,7 +4014,7 @@
         <v>30</v>
       </c>
       <c r="G70">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H70" t="s">
         <v>36</v>
@@ -4040,7 +4040,7 @@
         <v>30</v>
       </c>
       <c r="G71">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="H71" t="s">
         <v>36</v>
@@ -4066,7 +4066,7 @@
         <v>30</v>
       </c>
       <c r="G72">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H72" t="s">
         <v>36</v>
@@ -4092,7 +4092,7 @@
         <v>30</v>
       </c>
       <c r="G73">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H73" t="s">
         <v>36</v>
@@ -4118,7 +4118,7 @@
         <v>30</v>
       </c>
       <c r="G74">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H74" t="s">
         <v>36</v>
@@ -4144,7 +4144,7 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H75" t="s">
         <v>36</v>
@@ -4170,7 +4170,7 @@
         <v>30</v>
       </c>
       <c r="G76">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H76" t="s">
         <v>36</v>
@@ -4196,7 +4196,7 @@
         <v>30</v>
       </c>
       <c r="G77">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H77" t="s">
         <v>36</v>
@@ -4222,7 +4222,7 @@
         <v>30</v>
       </c>
       <c r="G78">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H78" t="s">
         <v>36</v>
@@ -4248,7 +4248,7 @@
         <v>30</v>
       </c>
       <c r="G79">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H79" t="s">
         <v>36</v>
@@ -4274,7 +4274,7 @@
         <v>30</v>
       </c>
       <c r="G80">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H80" t="s">
         <v>36</v>
@@ -4326,7 +4326,7 @@
         <v>30</v>
       </c>
       <c r="G82">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H82" t="s">
         <v>36</v>
@@ -4352,7 +4352,7 @@
         <v>30</v>
       </c>
       <c r="G83">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H83" t="s">
         <v>36</v>
@@ -4404,7 +4404,7 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H85" t="s">
         <v>36</v>
@@ -4430,7 +4430,7 @@
         <v>30</v>
       </c>
       <c r="G86">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="H86" t="s">
         <v>36</v>
@@ -4456,7 +4456,7 @@
         <v>30</v>
       </c>
       <c r="G87">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H87" t="s">
         <v>36</v>
@@ -4482,7 +4482,7 @@
         <v>30</v>
       </c>
       <c r="G88">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H88" t="s">
         <v>36</v>
@@ -4508,7 +4508,7 @@
         <v>30</v>
       </c>
       <c r="G89">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H89" t="s">
         <v>36</v>
@@ -4534,7 +4534,7 @@
         <v>30</v>
       </c>
       <c r="G90">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H90" t="s">
         <v>36</v>
@@ -4560,7 +4560,7 @@
         <v>30</v>
       </c>
       <c r="G91">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H91" t="s">
         <v>36</v>
@@ -4586,7 +4586,7 @@
         <v>30</v>
       </c>
       <c r="G92">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="H92" t="s">
         <v>36</v>
@@ -4612,7 +4612,7 @@
         <v>30</v>
       </c>
       <c r="G93">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="H93" t="s">
         <v>36</v>
@@ -4638,7 +4638,7 @@
         <v>30</v>
       </c>
       <c r="G94">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H94" t="s">
         <v>36</v>
@@ -4664,7 +4664,7 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="H95" t="s">
         <v>36</v>
@@ -4690,7 +4690,7 @@
         <v>30</v>
       </c>
       <c r="G96">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H96" t="s">
         <v>36</v>
@@ -4716,7 +4716,7 @@
         <v>30</v>
       </c>
       <c r="G97">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H97" t="s">
         <v>36</v>
@@ -4742,7 +4742,7 @@
         <v>30</v>
       </c>
       <c r="G98">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H98" t="s">
         <v>36</v>
@@ -4768,7 +4768,7 @@
         <v>30</v>
       </c>
       <c r="G99">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H99" t="s">
         <v>36</v>
@@ -4794,7 +4794,7 @@
         <v>30</v>
       </c>
       <c r="G100">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H100" t="s">
         <v>36</v>
@@ -4872,7 +4872,7 @@
         <v>31</v>
       </c>
       <c r="G103">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H103" t="s">
         <v>36</v>
@@ -4898,7 +4898,7 @@
         <v>31</v>
       </c>
       <c r="G104">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H104" t="s">
         <v>36</v>
@@ -4976,7 +4976,7 @@
         <v>31</v>
       </c>
       <c r="G107">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H107" t="s">
         <v>36</v>
@@ -5028,7 +5028,7 @@
         <v>31</v>
       </c>
       <c r="G109">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H109" t="s">
         <v>36</v>
@@ -5080,7 +5080,7 @@
         <v>31</v>
       </c>
       <c r="G111">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H111" t="s">
         <v>36</v>
@@ -5106,7 +5106,7 @@
         <v>31</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H112" t="s">
         <v>36</v>
@@ -5158,7 +5158,7 @@
         <v>31</v>
       </c>
       <c r="G114">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H114" t="s">
         <v>36</v>
@@ -5184,7 +5184,7 @@
         <v>31</v>
       </c>
       <c r="G115">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="H115" t="s">
         <v>36</v>
@@ -5210,7 +5210,7 @@
         <v>31</v>
       </c>
       <c r="G116">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="H116" t="s">
         <v>36</v>
@@ -5236,7 +5236,7 @@
         <v>31</v>
       </c>
       <c r="G117">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="H117" t="s">
         <v>36</v>
@@ -5262,7 +5262,7 @@
         <v>31</v>
       </c>
       <c r="G118">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="H118" t="s">
         <v>36</v>
@@ -5288,7 +5288,7 @@
         <v>31</v>
       </c>
       <c r="G119">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H119" t="s">
         <v>36</v>
@@ -5314,7 +5314,7 @@
         <v>31</v>
       </c>
       <c r="G120">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="H120" t="s">
         <v>36</v>
@@ -5340,7 +5340,7 @@
         <v>31</v>
       </c>
       <c r="G121">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="H121" t="s">
         <v>36</v>
@@ -5366,7 +5366,7 @@
         <v>31</v>
       </c>
       <c r="G122">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H122" t="s">
         <v>36</v>
@@ -5392,7 +5392,7 @@
         <v>31</v>
       </c>
       <c r="G123">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="H123" t="s">
         <v>36</v>
@@ -5418,7 +5418,7 @@
         <v>31</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H124" t="s">
         <v>36</v>
@@ -5444,7 +5444,7 @@
         <v>31</v>
       </c>
       <c r="G125">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H125" t="s">
         <v>36</v>
@@ -5470,7 +5470,7 @@
         <v>31</v>
       </c>
       <c r="G126">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H126" t="s">
         <v>36</v>
@@ -5496,7 +5496,7 @@
         <v>31</v>
       </c>
       <c r="G127">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="H127" t="s">
         <v>36</v>
@@ -5522,7 +5522,7 @@
         <v>31</v>
       </c>
       <c r="G128">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H128" t="s">
         <v>36</v>
@@ -5548,7 +5548,7 @@
         <v>31</v>
       </c>
       <c r="G129">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="H129" t="s">
         <v>36</v>
@@ -5574,7 +5574,7 @@
         <v>31</v>
       </c>
       <c r="G130">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="H130" t="s">
         <v>36</v>
@@ -5600,7 +5600,7 @@
         <v>31</v>
       </c>
       <c r="G131">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H131" t="s">
         <v>36</v>
@@ -5626,7 +5626,7 @@
         <v>31</v>
       </c>
       <c r="G132">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="H132" t="s">
         <v>36</v>
@@ -5652,7 +5652,7 @@
         <v>31</v>
       </c>
       <c r="G133">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H133" t="s">
         <v>36</v>
@@ -5730,7 +5730,7 @@
         <v>32</v>
       </c>
       <c r="G136">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="H136" t="s">
         <v>36</v>
@@ -6068,7 +6068,7 @@
         <v>32</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H149" t="s">
         <v>36</v>
@@ -6172,7 +6172,7 @@
         <v>32</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H153" t="s">
         <v>36</v>
@@ -6250,7 +6250,7 @@
         <v>32</v>
       </c>
       <c r="G156">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H156" t="s">
         <v>36</v>
@@ -6276,7 +6276,7 @@
         <v>32</v>
       </c>
       <c r="G157">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H157" t="s">
         <v>36</v>
@@ -6302,7 +6302,7 @@
         <v>32</v>
       </c>
       <c r="G158">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="H158" t="s">
         <v>36</v>
@@ -6354,7 +6354,7 @@
         <v>32</v>
       </c>
       <c r="G160">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H160" t="s">
         <v>36</v>
@@ -6406,7 +6406,7 @@
         <v>32</v>
       </c>
       <c r="G162">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="H162" t="s">
         <v>36</v>
@@ -6484,7 +6484,7 @@
         <v>32</v>
       </c>
       <c r="G165">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H165" t="s">
         <v>36</v>
@@ -6510,7 +6510,7 @@
         <v>32</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H166" t="s">
         <v>36</v>
@@ -6536,7 +6536,7 @@
         <v>33</v>
       </c>
       <c r="G167">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H167" t="s">
         <v>36</v>
@@ -6562,7 +6562,7 @@
         <v>33</v>
       </c>
       <c r="G168">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H168" t="s">
         <v>36</v>
@@ -6588,7 +6588,7 @@
         <v>33</v>
       </c>
       <c r="G169">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H169" t="s">
         <v>36</v>
@@ -6614,7 +6614,7 @@
         <v>33</v>
       </c>
       <c r="G170">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H170" t="s">
         <v>36</v>
@@ -6666,7 +6666,7 @@
         <v>33</v>
       </c>
       <c r="G172">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H172" t="s">
         <v>36</v>
@@ -6692,7 +6692,7 @@
         <v>33</v>
       </c>
       <c r="G173">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H173" t="s">
         <v>36</v>
@@ -6718,7 +6718,7 @@
         <v>33</v>
       </c>
       <c r="G174">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H174" t="s">
         <v>36</v>
@@ -6744,7 +6744,7 @@
         <v>33</v>
       </c>
       <c r="G175">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H175" t="s">
         <v>36</v>
@@ -6770,7 +6770,7 @@
         <v>33</v>
       </c>
       <c r="G176">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H176" t="s">
         <v>36</v>
@@ -6796,7 +6796,7 @@
         <v>33</v>
       </c>
       <c r="G177">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H177" t="s">
         <v>36</v>
@@ -6822,7 +6822,7 @@
         <v>33</v>
       </c>
       <c r="G178">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H178" t="s">
         <v>36</v>
@@ -6848,7 +6848,7 @@
         <v>33</v>
       </c>
       <c r="G179">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H179" t="s">
         <v>36</v>
@@ -6874,7 +6874,7 @@
         <v>33</v>
       </c>
       <c r="G180">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H180" t="s">
         <v>36</v>
@@ -6900,7 +6900,7 @@
         <v>33</v>
       </c>
       <c r="G181">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H181" t="s">
         <v>36</v>
@@ -6926,7 +6926,7 @@
         <v>33</v>
       </c>
       <c r="G182">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H182" t="s">
         <v>36</v>
@@ -6978,7 +6978,7 @@
         <v>33</v>
       </c>
       <c r="G184">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H184" t="s">
         <v>36</v>
@@ -7030,7 +7030,7 @@
         <v>33</v>
       </c>
       <c r="G186">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="H186" t="s">
         <v>36</v>
@@ -7056,7 +7056,7 @@
         <v>33</v>
       </c>
       <c r="G187">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H187" t="s">
         <v>36</v>
@@ -7082,7 +7082,7 @@
         <v>33</v>
       </c>
       <c r="G188">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H188" t="s">
         <v>36</v>
@@ -7108,7 +7108,7 @@
         <v>33</v>
       </c>
       <c r="G189">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="H189" t="s">
         <v>36</v>
@@ -7134,7 +7134,7 @@
         <v>33</v>
       </c>
       <c r="G190">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H190" t="s">
         <v>36</v>
@@ -7160,7 +7160,7 @@
         <v>33</v>
       </c>
       <c r="G191">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H191" t="s">
         <v>36</v>
@@ -7212,7 +7212,7 @@
         <v>33</v>
       </c>
       <c r="G193">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H193" t="s">
         <v>36</v>
@@ -7238,7 +7238,7 @@
         <v>33</v>
       </c>
       <c r="G194">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H194" t="s">
         <v>36</v>
@@ -7264,7 +7264,7 @@
         <v>33</v>
       </c>
       <c r="G195">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H195" t="s">
         <v>36</v>
@@ -7290,7 +7290,7 @@
         <v>33</v>
       </c>
       <c r="G196">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="H196" t="s">
         <v>36</v>
@@ -7342,7 +7342,7 @@
         <v>33</v>
       </c>
       <c r="G198">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H198" t="s">
         <v>36</v>
@@ -7368,7 +7368,7 @@
         <v>33</v>
       </c>
       <c r="G199">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H199" t="s">
         <v>36</v>
@@ -7394,7 +7394,7 @@
         <v>34</v>
       </c>
       <c r="G200">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H200" t="s">
         <v>36</v>
@@ -7420,7 +7420,7 @@
         <v>34</v>
       </c>
       <c r="G201">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H201" t="s">
         <v>36</v>
@@ -7446,7 +7446,7 @@
         <v>34</v>
       </c>
       <c r="G202">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H202" t="s">
         <v>36</v>
@@ -7472,7 +7472,7 @@
         <v>34</v>
       </c>
       <c r="G203">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="H203" t="s">
         <v>36</v>
@@ -7498,7 +7498,7 @@
         <v>34</v>
       </c>
       <c r="G204">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H204" t="s">
         <v>36</v>
@@ -7524,7 +7524,7 @@
         <v>34</v>
       </c>
       <c r="G205">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H205" t="s">
         <v>36</v>
@@ -7550,7 +7550,7 @@
         <v>34</v>
       </c>
       <c r="G206">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="H206" t="s">
         <v>36</v>
@@ -7576,7 +7576,7 @@
         <v>34</v>
       </c>
       <c r="G207">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H207" t="s">
         <v>36</v>
@@ -7602,7 +7602,7 @@
         <v>34</v>
       </c>
       <c r="G208">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="H208" t="s">
         <v>36</v>
@@ -7654,7 +7654,7 @@
         <v>34</v>
       </c>
       <c r="G210">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H210" t="s">
         <v>36</v>
@@ -7680,7 +7680,7 @@
         <v>34</v>
       </c>
       <c r="G211">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H211" t="s">
         <v>36</v>
@@ -7706,7 +7706,7 @@
         <v>34</v>
       </c>
       <c r="G212">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H212" t="s">
         <v>36</v>
@@ -7732,7 +7732,7 @@
         <v>34</v>
       </c>
       <c r="G213">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="H213" t="s">
         <v>36</v>
@@ -7758,7 +7758,7 @@
         <v>34</v>
       </c>
       <c r="G214">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="H214" t="s">
         <v>36</v>
@@ -7784,7 +7784,7 @@
         <v>34</v>
       </c>
       <c r="G215">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H215" t="s">
         <v>36</v>
@@ -7810,7 +7810,7 @@
         <v>34</v>
       </c>
       <c r="G216">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H216" t="s">
         <v>36</v>
@@ -7836,7 +7836,7 @@
         <v>34</v>
       </c>
       <c r="G217">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H217" t="s">
         <v>36</v>
@@ -7862,7 +7862,7 @@
         <v>34</v>
       </c>
       <c r="G218">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H218" t="s">
         <v>36</v>
@@ -7888,7 +7888,7 @@
         <v>34</v>
       </c>
       <c r="G219">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H219" t="s">
         <v>36</v>
@@ -7914,7 +7914,7 @@
         <v>34</v>
       </c>
       <c r="G220">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H220" t="s">
         <v>36</v>
@@ -7940,7 +7940,7 @@
         <v>34</v>
       </c>
       <c r="G221">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H221" t="s">
         <v>36</v>
@@ -7966,7 +7966,7 @@
         <v>34</v>
       </c>
       <c r="G222">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="H222" t="s">
         <v>36</v>
@@ -7992,7 +7992,7 @@
         <v>34</v>
       </c>
       <c r="G223">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H223" t="s">
         <v>36</v>
@@ -8018,7 +8018,7 @@
         <v>34</v>
       </c>
       <c r="G224">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="H224" t="s">
         <v>36</v>
@@ -8070,7 +8070,7 @@
         <v>34</v>
       </c>
       <c r="G226">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H226" t="s">
         <v>36</v>
@@ -8096,7 +8096,7 @@
         <v>34</v>
       </c>
       <c r="G227">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H227" t="s">
         <v>36</v>
@@ -8122,7 +8122,7 @@
         <v>34</v>
       </c>
       <c r="G228">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H228" t="s">
         <v>36</v>
@@ -8148,7 +8148,7 @@
         <v>34</v>
       </c>
       <c r="G229">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H229" t="s">
         <v>36</v>
@@ -8174,7 +8174,7 @@
         <v>34</v>
       </c>
       <c r="G230">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H230" t="s">
         <v>36</v>
@@ -8200,7 +8200,7 @@
         <v>34</v>
       </c>
       <c r="G231">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H231" t="s">
         <v>36</v>
@@ -8226,7 +8226,7 @@
         <v>34</v>
       </c>
       <c r="G232">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="H232" t="s">
         <v>36</v>
@@ -8252,7 +8252,7 @@
         <v>35</v>
       </c>
       <c r="G233">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="H233" t="s">
         <v>36</v>
@@ -8278,7 +8278,7 @@
         <v>35</v>
       </c>
       <c r="G234">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="H234" t="s">
         <v>36</v>
@@ -8304,7 +8304,7 @@
         <v>35</v>
       </c>
       <c r="G235">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="H235" t="s">
         <v>36</v>
@@ -8330,7 +8330,7 @@
         <v>35</v>
       </c>
       <c r="G236">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H236" t="s">
         <v>36</v>
@@ -8356,7 +8356,7 @@
         <v>35</v>
       </c>
       <c r="G237">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="H237" t="s">
         <v>36</v>
@@ -8382,7 +8382,7 @@
         <v>35</v>
       </c>
       <c r="G238">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="H238" t="s">
         <v>36</v>
@@ -8408,7 +8408,7 @@
         <v>35</v>
       </c>
       <c r="G239">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="H239" t="s">
         <v>36</v>
@@ -8434,7 +8434,7 @@
         <v>35</v>
       </c>
       <c r="G240">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H240" t="s">
         <v>36</v>
@@ -8460,7 +8460,7 @@
         <v>35</v>
       </c>
       <c r="G241">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="H241" t="s">
         <v>36</v>
@@ -8486,7 +8486,7 @@
         <v>35</v>
       </c>
       <c r="G242">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H242" t="s">
         <v>36</v>
@@ -8512,7 +8512,7 @@
         <v>35</v>
       </c>
       <c r="G243">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="H243" t="s">
         <v>36</v>
@@ -8538,7 +8538,7 @@
         <v>35</v>
       </c>
       <c r="G244">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H244" t="s">
         <v>36</v>
@@ -8564,7 +8564,7 @@
         <v>35</v>
       </c>
       <c r="G245">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="H245" t="s">
         <v>36</v>
@@ -8590,7 +8590,7 @@
         <v>35</v>
       </c>
       <c r="G246">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H246" t="s">
         <v>36</v>
@@ -8616,7 +8616,7 @@
         <v>35</v>
       </c>
       <c r="G247">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="H247" t="s">
         <v>36</v>
@@ -8642,7 +8642,7 @@
         <v>35</v>
       </c>
       <c r="G248">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="H248" t="s">
         <v>36</v>
@@ -8668,7 +8668,7 @@
         <v>35</v>
       </c>
       <c r="G249">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="H249" t="s">
         <v>36</v>
@@ -8694,7 +8694,7 @@
         <v>35</v>
       </c>
       <c r="G250">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="H250" t="s">
         <v>36</v>
@@ -8720,7 +8720,7 @@
         <v>35</v>
       </c>
       <c r="G251">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="H251" t="s">
         <v>36</v>
@@ -8746,7 +8746,7 @@
         <v>35</v>
       </c>
       <c r="G252">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="H252" t="s">
         <v>36</v>
@@ -8772,7 +8772,7 @@
         <v>35</v>
       </c>
       <c r="G253">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="H253" t="s">
         <v>36</v>
@@ -8798,7 +8798,7 @@
         <v>35</v>
       </c>
       <c r="G254">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H254" t="s">
         <v>36</v>
@@ -8824,7 +8824,7 @@
         <v>35</v>
       </c>
       <c r="G255">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="H255" t="s">
         <v>36</v>
@@ -8850,7 +8850,7 @@
         <v>35</v>
       </c>
       <c r="G256">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="H256" t="s">
         <v>36</v>
@@ -8876,7 +8876,7 @@
         <v>35</v>
       </c>
       <c r="G257">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="H257" t="s">
         <v>36</v>
@@ -8928,7 +8928,7 @@
         <v>35</v>
       </c>
       <c r="G259">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="H259" t="s">
         <v>36</v>
@@ -8954,7 +8954,7 @@
         <v>35</v>
       </c>
       <c r="G260">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="H260" t="s">
         <v>36</v>
@@ -8980,7 +8980,7 @@
         <v>35</v>
       </c>
       <c r="G261">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H261" t="s">
         <v>36</v>
@@ -9006,7 +9006,7 @@
         <v>35</v>
       </c>
       <c r="G262">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="H262" t="s">
         <v>36</v>
@@ -9032,7 +9032,7 @@
         <v>35</v>
       </c>
       <c r="G263">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="H263" t="s">
         <v>36</v>
@@ -9058,7 +9058,7 @@
         <v>35</v>
       </c>
       <c r="G264">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="H264" t="s">
         <v>36</v>
@@ -9084,7 +9084,7 @@
         <v>35</v>
       </c>
       <c r="G265">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="H265" t="s">
         <v>36</v>
@@ -9140,25 +9140,25 @@
         <v>28</v>
       </c>
       <c r="C2">
-        <v>75.66666666666667</v>
+        <v>77.22222222222223</v>
       </c>
       <c r="D2">
-        <v>76.77777777777777</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="E2">
-        <v>0.01468428781204101</v>
+        <v>0.00719424460431628</v>
       </c>
       <c r="F2">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="G2">
         <v>70.33333333333333</v>
       </c>
-      <c r="G2">
-        <v>69</v>
-      </c>
       <c r="H2">
-        <v>0.0193236714975844</v>
+        <v>0.01421800947867302</v>
       </c>
       <c r="I2">
-        <v>0.1426917818566693</v>
+        <v>0.140680687647711</v>
       </c>
       <c r="J2" t="s">
         <v>45</v>
@@ -9172,25 +9172,25 @@
         <v>29</v>
       </c>
       <c r="C3">
-        <v>55.11111111111111</v>
+        <v>50.77777777777778</v>
       </c>
       <c r="D3">
-        <v>50.88888888888889</v>
+        <v>47.11111111111111</v>
       </c>
       <c r="E3">
-        <v>-0.07661290322580661</v>
+        <v>-0.07221006564551413</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>31.66666666666667</v>
+        <v>29.66666666666667</v>
       </c>
       <c r="H3">
-        <v>0.2315789473684211</v>
+        <v>0.2134831460674156</v>
       </c>
       <c r="I3">
-        <v>0.4022630691754402</v>
+        <v>0.4230970861543641</v>
       </c>
       <c r="J3" t="s">
         <v>46</v>
@@ -9204,25 +9204,25 @@
         <v>30</v>
       </c>
       <c r="C4">
-        <v>58</v>
+        <v>55.88888888888889</v>
       </c>
       <c r="D4">
-        <v>44.11111111111111</v>
+        <v>38</v>
       </c>
       <c r="E4">
-        <v>-0.239463601532567</v>
+        <v>-0.320079522862823</v>
       </c>
       <c r="F4">
-        <v>31.33333333333333</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="G4">
-        <v>35</v>
+        <v>31.66666666666667</v>
       </c>
       <c r="H4">
-        <v>-0.1047619047619048</v>
+        <v>-0.2000000000000001</v>
       </c>
       <c r="I4">
-        <v>0.3537922878749164</v>
+        <v>0.38968929931421</v>
       </c>
       <c r="J4" t="s">
         <v>47</v>
@@ -9236,25 +9236,25 @@
         <v>31</v>
       </c>
       <c r="C5">
-        <v>58.88888888888889</v>
+        <v>50.44444444444444</v>
       </c>
       <c r="D5">
-        <v>78.44444444444444</v>
+        <v>69.22222222222223</v>
       </c>
       <c r="E5">
-        <v>0.3320754716981134</v>
+        <v>0.3722466960352424</v>
       </c>
       <c r="F5">
-        <v>79.33333333333333</v>
+        <v>65</v>
       </c>
       <c r="G5">
-        <v>70.33333333333333</v>
+        <v>61</v>
       </c>
       <c r="H5">
-        <v>0.127962085308057</v>
+        <v>0.06557377049180335</v>
       </c>
       <c r="I5">
-        <v>0.7886492748918057</v>
+        <v>0.7894911189938829</v>
       </c>
       <c r="J5" t="s">
         <v>46</v>
@@ -9268,22 +9268,28 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>20.77777777777778</v>
       </c>
       <c r="D6">
-        <v>10.22222222222222</v>
+        <v>41.77777777777778</v>
+      </c>
+      <c r="E6">
+        <v>1.010695187165775</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>42.33333333333334</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>23.66666666666667</v>
+      </c>
+      <c r="H6">
+        <v>0.7887323943661972</v>
       </c>
       <c r="I6">
-        <v>2.688230436269033</v>
+        <v>2.061790719574921</v>
       </c>
       <c r="J6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -9294,25 +9300,25 @@
         <v>33</v>
       </c>
       <c r="C7">
-        <v>58.44444444444444</v>
+        <v>55</v>
       </c>
       <c r="D7">
-        <v>72.55555555555556</v>
+        <v>72.11111111111111</v>
       </c>
       <c r="E7">
-        <v>0.2414448669201521</v>
+        <v>0.3111111111111111</v>
       </c>
       <c r="F7">
-        <v>52</v>
+        <v>51.33333333333334</v>
       </c>
       <c r="G7">
-        <v>71.33333333333333</v>
+        <v>73.66666666666667</v>
       </c>
       <c r="H7">
-        <v>-0.2710280373831775</v>
+        <v>-0.3031674208144797</v>
       </c>
       <c r="I7">
-        <v>0.27396272946646</v>
+        <v>0.273667644759039</v>
       </c>
       <c r="J7" t="s">
         <v>47</v>
@@ -9326,28 +9332,28 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>35.66666666666666</v>
+        <v>26.77777777777778</v>
       </c>
       <c r="D8">
-        <v>42.77777777777778</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="E8">
-        <v>0.1993769470404985</v>
+        <v>0.4315352697095436</v>
       </c>
       <c r="F8">
-        <v>32.33333333333334</v>
+        <v>29.66666666666667</v>
       </c>
       <c r="G8">
-        <v>34.33333333333334</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="H8">
-        <v>-0.05825242718446599</v>
+        <v>0.2535211267605633</v>
       </c>
       <c r="I8">
-        <v>0.6086974327906665</v>
+        <v>0.6275203823400812</v>
       </c>
       <c r="J8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -9358,28 +9364,28 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>35.66666666666666</v>
+        <v>76.11111111111111</v>
       </c>
       <c r="D9">
-        <v>42.77777777777778</v>
+        <v>77.66666666666667</v>
       </c>
       <c r="E9">
-        <v>0.1993769470404985</v>
+        <v>0.02043795620437949</v>
       </c>
       <c r="F9">
-        <v>32.33333333333334</v>
+        <v>68.66666666666667</v>
       </c>
       <c r="G9">
-        <v>34.33333333333334</v>
+        <v>70.33333333333333</v>
       </c>
       <c r="H9">
-        <v>-0.05825242718446599</v>
+        <v>-0.02369668246445489</v>
       </c>
       <c r="I9">
-        <v>0.6086974327906665</v>
+        <v>0.1434682196277631</v>
       </c>
       <c r="J9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -9444,40 +9450,40 @@
         <v>28</v>
       </c>
       <c r="C2">
-        <v>1.104106180008295</v>
+        <v>1.110339190845934</v>
       </c>
       <c r="D2">
-        <v>1.145167980091248</v>
+        <v>1.141806293420515</v>
       </c>
       <c r="E2">
-        <v>1.067606802156781</v>
+        <v>1.069881487535758</v>
       </c>
       <c r="F2">
-        <v>0.9717959352965574</v>
+        <v>0.9754801798120146</v>
       </c>
       <c r="G2">
-        <v>0.8531729572791373</v>
+        <v>0.8586023702492848</v>
       </c>
       <c r="H2">
-        <v>0.8440481128162588</v>
+        <v>0.8451164691458929</v>
       </c>
       <c r="I2">
-        <v>1.063044379925342</v>
+        <v>1.060890886800163</v>
       </c>
       <c r="J2">
-        <v>0.9900456242223143</v>
+        <v>0.9934613812832039</v>
       </c>
       <c r="K2">
-        <v>0.9535462463708005</v>
+        <v>0.9530036779730282</v>
       </c>
       <c r="L2">
-        <v>0.9375777685607631</v>
+        <v>0.9305271761340417</v>
       </c>
       <c r="M2">
-        <v>0.9102032351721278</v>
+        <v>0.9035553739272578</v>
       </c>
       <c r="N2">
-        <v>1.163417669017005</v>
+        <v>1.153044544340008</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -9488,40 +9494,40 @@
         <v>29</v>
       </c>
       <c r="C3">
-        <v>1.665445665445666</v>
+        <v>1.723160027008778</v>
       </c>
       <c r="D3">
-        <v>1.215506715506716</v>
+        <v>1.255232950708981</v>
       </c>
       <c r="E3">
-        <v>1.094627594627595</v>
+        <v>1.032410533423363</v>
       </c>
       <c r="F3">
-        <v>0.7454212454212454</v>
+        <v>0.7947332883187036</v>
       </c>
       <c r="G3">
-        <v>0.6043956043956045</v>
+        <v>0.6907494935854153</v>
       </c>
       <c r="H3">
-        <v>0.6648351648351649</v>
+        <v>0.6090479405806888</v>
       </c>
       <c r="I3">
-        <v>0.8394383394383395</v>
+        <v>0.824442943956786</v>
       </c>
       <c r="J3">
-        <v>0.8663003663003663</v>
+        <v>0.7873058744091831</v>
       </c>
       <c r="K3">
-        <v>0.8327228327228329</v>
+        <v>0.8541525995948684</v>
       </c>
       <c r="L3">
-        <v>1.087912087912088</v>
+        <v>0.9469952734638758</v>
       </c>
       <c r="M3">
-        <v>1.067765567765568</v>
+        <v>1.147535449020932</v>
       </c>
       <c r="N3">
-        <v>1.551282051282051</v>
+        <v>1.548615800135044</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -9532,40 +9538,40 @@
         <v>30</v>
       </c>
       <c r="C4">
-        <v>1.609920391916718</v>
+        <v>1.635333333333333</v>
       </c>
       <c r="D4">
-        <v>1.556031843233313</v>
+        <v>1.584</v>
       </c>
       <c r="E4">
-        <v>0.936313533374158</v>
+        <v>0.9533333333333334</v>
       </c>
       <c r="F4">
-        <v>0.8622167789344763</v>
+        <v>0.7406666666666666</v>
       </c>
       <c r="G4">
-        <v>0.8015921616656461</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="H4">
-        <v>0.6062461726883037</v>
+        <v>0.7040000000000001</v>
       </c>
       <c r="I4">
-        <v>0.8554807103490509</v>
+        <v>0.8360000000000001</v>
       </c>
       <c r="J4">
-        <v>0.8083282302510717</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K4">
-        <v>0.8622167789344763</v>
+        <v>0.858</v>
       </c>
       <c r="L4">
-        <v>1.000306184935701</v>
+        <v>1.056</v>
       </c>
       <c r="M4">
-        <v>1.020514390691978</v>
+        <v>1.078</v>
       </c>
       <c r="N4">
-        <v>1.1316595223515</v>
+        <v>1.166</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -9576,40 +9582,40 @@
         <v>31</v>
       </c>
       <c r="C5">
-        <v>0.6698961937716262</v>
+        <v>0.8258258258258259</v>
       </c>
       <c r="D5">
-        <v>1.050519031141868</v>
+        <v>1.106606606606606</v>
       </c>
       <c r="E5">
-        <v>1.263667820069204</v>
+        <v>1.106606606606606</v>
       </c>
       <c r="F5">
-        <v>1.126643598615917</v>
+        <v>0.9084084084084083</v>
       </c>
       <c r="G5">
-        <v>1.157093425605536</v>
+        <v>1.304804804804805</v>
       </c>
       <c r="H5">
-        <v>1.103806228373702</v>
+        <v>0.8588588588588587</v>
       </c>
       <c r="I5">
-        <v>1.103806228373702</v>
+        <v>1.156156156156156</v>
       </c>
       <c r="J5">
-        <v>1.050519031141868</v>
+        <v>0.801051051051051</v>
       </c>
       <c r="K5">
-        <v>1.499653979238754</v>
+        <v>1.197447447447447</v>
       </c>
       <c r="L5">
-        <v>0.5366782006920415</v>
+        <v>0.5326576576576576</v>
       </c>
       <c r="M5">
-        <v>0.9249134948096885</v>
+        <v>0.9786036036036035</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.09009009009009</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -9620,19 +9626,19 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>2.759322033898305</v>
+        <v>1.797513321492007</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2.013559322033898</v>
+        <v>1.680284191829485</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1.953818827708703</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1.387211367673179</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -9641,19 +9647,19 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0.6711864406779661</v>
+        <v>2.227353463587922</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1.953818827708703</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>2.740677966101695</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>5.593220338983051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -9664,40 +9670,40 @@
         <v>33</v>
       </c>
       <c r="C7">
-        <v>1.076690211907165</v>
+        <v>1.056692913385827</v>
       </c>
       <c r="D7">
-        <v>1.165489404641776</v>
+        <v>1.224146981627297</v>
       </c>
       <c r="E7">
-        <v>1.209889001009082</v>
+        <v>1.195275590551181</v>
       </c>
       <c r="F7">
-        <v>0.987891019172553</v>
+        <v>0.9758530183727034</v>
       </c>
       <c r="G7">
-        <v>1.015640766902119</v>
+        <v>1.039370078740157</v>
       </c>
       <c r="H7">
-        <v>0.8824419778002018</v>
+        <v>0.9412073490813648</v>
       </c>
       <c r="I7">
-        <v>1.032290615539859</v>
+        <v>1.056692913385827</v>
       </c>
       <c r="J7">
-        <v>0.9046417759838548</v>
+        <v>0.8661417322834646</v>
       </c>
       <c r="K7">
-        <v>0.7325933400605449</v>
+        <v>0.7564304461942257</v>
       </c>
       <c r="L7">
-        <v>0.6743188698284561</v>
+        <v>0.6755905511811023</v>
       </c>
       <c r="M7">
-        <v>1.082240161453078</v>
+        <v>1.013385826771654</v>
       </c>
       <c r="N7">
-        <v>1.232088799192735</v>
+        <v>1.143307086614173</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -9708,40 +9714,40 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>1.073789392774789</v>
+        <v>1.165942658557776</v>
       </c>
       <c r="D8">
-        <v>2.012298232129131</v>
+        <v>2.054735013032146</v>
       </c>
       <c r="E8">
-        <v>0.8370484242890085</v>
+        <v>0.9079061685490879</v>
       </c>
       <c r="F8">
-        <v>1.22598001537279</v>
+        <v>0.9748045178105996</v>
       </c>
       <c r="G8">
-        <v>0.8285933897002306</v>
+        <v>0.9079061685490879</v>
       </c>
       <c r="H8">
-        <v>0.6594926979246734</v>
+        <v>0.420503909643788</v>
       </c>
       <c r="I8">
-        <v>1.073789392774789</v>
+        <v>0.8887923544743702</v>
       </c>
       <c r="J8">
-        <v>1.200614911606457</v>
+        <v>1.156385751520417</v>
       </c>
       <c r="K8">
-        <v>0.6341275941583397</v>
+        <v>1.137271937445699</v>
       </c>
       <c r="L8">
-        <v>0.6975403535741738</v>
+        <v>0.6020851433536056</v>
       </c>
       <c r="M8">
-        <v>0.7736356648731745</v>
+        <v>0.4874022589052998</v>
       </c>
       <c r="N8">
-        <v>0.7102229054573406</v>
+        <v>0.9891398783666379</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -9752,40 +9758,40 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>1.073789392774789</v>
+        <v>1.123287671232877</v>
       </c>
       <c r="D9">
-        <v>2.012298232129131</v>
+        <v>1.155251141552511</v>
       </c>
       <c r="E9">
-        <v>0.8370484242890085</v>
+        <v>1.077625570776256</v>
       </c>
       <c r="F9">
-        <v>1.22598001537279</v>
+        <v>0.9817351598173517</v>
       </c>
       <c r="G9">
-        <v>0.8285933897002306</v>
+        <v>0.8584474885844748</v>
       </c>
       <c r="H9">
-        <v>0.6594926979246734</v>
+        <v>0.8447488584474886</v>
       </c>
       <c r="I9">
-        <v>1.073789392774789</v>
+        <v>1.027397260273973</v>
       </c>
       <c r="J9">
-        <v>1.200614911606457</v>
+        <v>1.031963470319635</v>
       </c>
       <c r="K9">
-        <v>0.6341275941583397</v>
+        <v>0.9315068493150684</v>
       </c>
       <c r="L9">
-        <v>0.6975403535741738</v>
+        <v>0.9383561643835616</v>
       </c>
       <c r="M9">
-        <v>0.7736356648731745</v>
+        <v>0.952054794520548</v>
       </c>
       <c r="N9">
-        <v>0.7102229054573406</v>
+        <v>1.061643835616438</v>
       </c>
     </row>
   </sheetData>
@@ -9881,7 +9887,7 @@
         <v>46082</v>
       </c>
       <c r="E4">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F4">
         <v>2026</v>
@@ -9904,7 +9910,7 @@
         <v>45839</v>
       </c>
       <c r="E5">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F5">
         <v>2025</v>
@@ -9924,16 +9930,16 @@
         <v>5</v>
       </c>
       <c r="D6" s="2">
-        <v>46023</v>
+        <v>45717</v>
       </c>
       <c r="E6">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F6">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -9947,13 +9953,13 @@
         <v>1</v>
       </c>
       <c r="D7" s="2">
-        <v>45658</v>
+        <v>46023</v>
       </c>
       <c r="E7">
         <v>100</v>
       </c>
       <c r="F7">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G7" t="s">
         <v>8</v>
@@ -9970,13 +9976,13 @@
         <v>2</v>
       </c>
       <c r="D8" s="2">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="E8">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F8">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G8" t="s">
         <v>8</v>
@@ -9996,7 +10002,7 @@
         <v>45992</v>
       </c>
       <c r="E9">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F9">
         <v>2025</v>
@@ -10019,7 +10025,7 @@
         <v>46054</v>
       </c>
       <c r="E10">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F10">
         <v>2026</v>
@@ -10042,7 +10048,7 @@
         <v>45627</v>
       </c>
       <c r="E11">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F11">
         <v>2024</v>
@@ -10088,7 +10094,7 @@
         <v>45658</v>
       </c>
       <c r="E13">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F13">
         <v>2025</v>
@@ -10111,7 +10117,7 @@
         <v>46023</v>
       </c>
       <c r="E14">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="F14">
         <v>2026</v>
@@ -10134,7 +10140,7 @@
         <v>45323</v>
       </c>
       <c r="E15">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F15">
         <v>2024</v>
@@ -10157,7 +10163,7 @@
         <v>46054</v>
       </c>
       <c r="E16">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F16">
         <v>2026</v>
@@ -10177,16 +10183,16 @@
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>45901</v>
+        <v>46023</v>
       </c>
       <c r="E17">
         <v>100</v>
       </c>
       <c r="F17">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -10200,16 +10206,16 @@
         <v>2</v>
       </c>
       <c r="D18" s="2">
-        <v>46023</v>
+        <v>45778</v>
       </c>
       <c r="E18">
         <v>88</v>
       </c>
       <c r="F18">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G18" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -10223,16 +10229,16 @@
         <v>3</v>
       </c>
       <c r="D19" s="2">
-        <v>46204</v>
+        <v>46054</v>
       </c>
       <c r="E19">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F19">
         <v>2026</v>
       </c>
       <c r="G19" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -10246,16 +10252,16 @@
         <v>4</v>
       </c>
       <c r="D20" s="2">
-        <v>46054</v>
+        <v>45962</v>
       </c>
       <c r="E20">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F20">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G20" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -10269,16 +10275,16 @@
         <v>5</v>
       </c>
       <c r="D21" s="2">
-        <v>46082</v>
+        <v>46204</v>
       </c>
       <c r="E21">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F21">
         <v>2026</v>
       </c>
       <c r="G21" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -10292,7 +10298,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="2">
-        <v>45992</v>
+        <v>45748</v>
       </c>
       <c r="E22">
         <v>100</v>
@@ -10301,7 +10307,7 @@
         <v>2025</v>
       </c>
       <c r="G22" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -10315,16 +10321,16 @@
         <v>2</v>
       </c>
       <c r="D23" s="2">
-        <v>46023</v>
+        <v>46266</v>
       </c>
       <c r="E23">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="F23">
         <v>2026</v>
       </c>
       <c r="G23" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -10338,16 +10344,16 @@
         <v>3</v>
       </c>
       <c r="D24" s="2">
-        <v>45352</v>
+        <v>46023</v>
       </c>
       <c r="E24">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="F24">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G24" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -10361,16 +10367,16 @@
         <v>4</v>
       </c>
       <c r="D25" s="2">
-        <v>45962</v>
+        <v>45870</v>
       </c>
       <c r="E25">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F25">
         <v>2025</v>
       </c>
       <c r="G25" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -10384,16 +10390,16 @@
         <v>5</v>
       </c>
       <c r="D26" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
       <c r="E26">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="F26">
         <v>2026</v>
       </c>
       <c r="G26" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -10433,7 +10439,7 @@
         <v>46082</v>
       </c>
       <c r="E28">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F28">
         <v>2026</v>
@@ -10456,7 +10462,7 @@
         <v>46023</v>
       </c>
       <c r="E29">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F29">
         <v>2026</v>
@@ -10476,16 +10482,16 @@
         <v>4</v>
       </c>
       <c r="D30" s="2">
-        <v>45992</v>
+        <v>45839</v>
       </c>
       <c r="E30">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F30">
         <v>2025</v>
       </c>
       <c r="G30" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -10499,16 +10505,16 @@
         <v>5</v>
       </c>
       <c r="D31" s="2">
-        <v>45839</v>
+        <v>46143</v>
       </c>
       <c r="E31">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F31">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -10545,16 +10551,16 @@
         <v>2</v>
       </c>
       <c r="D33" s="2">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="E33">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F33">
         <v>2024</v>
       </c>
       <c r="G33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -10568,16 +10574,16 @@
         <v>3</v>
       </c>
       <c r="D34" s="2">
-        <v>45689</v>
+        <v>45474</v>
       </c>
       <c r="E34">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="F34">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="G34" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -10591,16 +10597,16 @@
         <v>4</v>
       </c>
       <c r="D35" s="2">
-        <v>45505</v>
+        <v>45323</v>
       </c>
       <c r="E35">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F35">
         <v>2024</v>
       </c>
       <c r="G35" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -10614,16 +10620,16 @@
         <v>5</v>
       </c>
       <c r="D36" s="2">
-        <v>46023</v>
+        <v>45536</v>
       </c>
       <c r="E36">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F36">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="G36" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -10660,16 +10666,16 @@
         <v>2</v>
       </c>
       <c r="D38" s="2">
-        <v>45474</v>
+        <v>46023</v>
       </c>
       <c r="E38">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F38">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G38" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -10683,16 +10689,16 @@
         <v>3</v>
       </c>
       <c r="D39" s="2">
-        <v>45689</v>
+        <v>46082</v>
       </c>
       <c r="E39">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F39">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G39" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -10706,16 +10712,16 @@
         <v>4</v>
       </c>
       <c r="D40" s="2">
-        <v>45505</v>
+        <v>45992</v>
       </c>
       <c r="E40">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="F40">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G40" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -10729,16 +10735,16 @@
         <v>5</v>
       </c>
       <c r="D41" s="2">
-        <v>46023</v>
+        <v>45870</v>
       </c>
       <c r="E41">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F41">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G41" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -10819,10 +10825,10 @@
         <v>305</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="s">
         <v>36</v>
@@ -10939,10 +10945,10 @@
         <v>21</v>
       </c>
       <c r="C10">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D10">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s">
         <v>36</v>
@@ -11239,10 +11245,10 @@
         <v>325</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" t="s">
         <v>36</v>
@@ -11279,10 +11285,10 @@
         <v>20</v>
       </c>
       <c r="C27">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="D27">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="E27" t="s">
         <v>36</v>
@@ -11579,10 +11585,10 @@
         <v>22</v>
       </c>
       <c r="C42">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D42">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E42" t="s">
         <v>36</v>
@@ -11659,10 +11665,10 @@
         <v>23</v>
       </c>
       <c r="C46">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D46">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E46" t="s">
         <v>36</v>
@@ -11759,10 +11765,10 @@
         <v>348</v>
       </c>
       <c r="C51">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D51">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E51" t="s">
         <v>36</v>
@@ -11859,10 +11865,10 @@
         <v>353</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" t="s">
         <v>36</v>
@@ -11959,10 +11965,10 @@
         <v>358</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="s">
         <v>36</v>
@@ -11979,10 +11985,10 @@
         <v>359</v>
       </c>
       <c r="C62">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D62">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E62" t="s">
         <v>36</v>
@@ -12059,10 +12065,10 @@
         <v>363</v>
       </c>
       <c r="C66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E66" t="s">
         <v>36</v>
@@ -12219,10 +12225,10 @@
         <v>26</v>
       </c>
       <c r="C74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E74" t="s">
         <v>36</v>
@@ -12419,10 +12425,10 @@
         <v>379</v>
       </c>
       <c r="C84">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D84">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E84" t="s">
         <v>36</v>
@@ -12619,10 +12625,10 @@
         <v>389</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E94" t="s">
         <v>36</v>
@@ -12639,10 +12645,10 @@
         <v>390</v>
       </c>
       <c r="C95">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D95">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E95" t="s">
         <v>36</v>
@@ -12759,10 +12765,10 @@
         <v>396</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E101" t="s">
         <v>36</v>
@@ -13579,10 +13585,10 @@
         <v>437</v>
       </c>
       <c r="C142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142" t="s">
         <v>36</v>
@@ -13679,10 +13685,10 @@
         <v>442</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E147" t="s">
         <v>36</v>
@@ -13919,10 +13925,10 @@
         <v>454</v>
       </c>
       <c r="C159">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D159">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E159" t="s">
         <v>36</v>
@@ -14079,10 +14085,10 @@
         <v>462</v>
       </c>
       <c r="C167">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D167">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E167" t="s">
         <v>36</v>
@@ -14219,10 +14225,10 @@
         <v>469</v>
       </c>
       <c r="C174">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D174">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E174" t="s">
         <v>36</v>
@@ -14279,10 +14285,10 @@
         <v>472</v>
       </c>
       <c r="C177">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D177">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E177" t="s">
         <v>36</v>
@@ -14339,10 +14345,10 @@
         <v>475</v>
       </c>
       <c r="C180">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D180">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E180" t="s">
         <v>36</v>
@@ -14399,10 +14405,10 @@
         <v>478</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D183">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E183" t="s">
         <v>36</v>
@@ -14419,10 +14425,10 @@
         <v>479</v>
       </c>
       <c r="C184">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D184">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E184" t="s">
         <v>36</v>
@@ -14499,10 +14505,10 @@
         <v>483</v>
       </c>
       <c r="C188">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D188">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E188" t="s">
         <v>36</v>
@@ -14539,10 +14545,10 @@
         <v>485</v>
       </c>
       <c r="C190">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D190">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E190" t="s">
         <v>36</v>
@@ -14739,10 +14745,10 @@
         <v>495</v>
       </c>
       <c r="C200">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D200">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E200" t="s">
         <v>36</v>
@@ -14839,10 +14845,10 @@
         <v>500</v>
       </c>
       <c r="C205">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D205">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E205" t="s">
         <v>36</v>
@@ -14999,10 +15005,10 @@
         <v>508</v>
       </c>
       <c r="C213">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D213">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E213" t="s">
         <v>36</v>
@@ -15239,10 +15245,10 @@
         <v>520</v>
       </c>
       <c r="C225">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D225">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E225" t="s">
         <v>36</v>
@@ -15519,10 +15525,10 @@
         <v>534</v>
       </c>
       <c r="C239">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D239">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E239" t="s">
         <v>36</v>
@@ -15559,10 +15565,10 @@
         <v>24</v>
       </c>
       <c r="C241">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D241">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E241" t="s">
         <v>36</v>
@@ -15815,22 +15821,22 @@
         <v>28</v>
       </c>
       <c r="C2">
-        <v>76.77777777777777</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="D2">
-        <v>0.01468428781204101</v>
+        <v>0.00719424460431628</v>
       </c>
       <c r="E2">
-        <v>0.0193236714975844</v>
+        <v>0.01421800947867302</v>
       </c>
       <c r="F2">
-        <v>0.1426917818566693</v>
+        <v>0.140680687647711</v>
       </c>
       <c r="G2">
         <v>12</v>
       </c>
       <c r="H2">
-        <v>1.163417669017005</v>
+        <v>1.153044544340008</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -15841,22 +15847,22 @@
         <v>29</v>
       </c>
       <c r="C3">
-        <v>50.88888888888889</v>
+        <v>47.11111111111111</v>
       </c>
       <c r="D3">
-        <v>-0.07661290322580661</v>
+        <v>-0.07221006564551413</v>
       </c>
       <c r="E3">
-        <v>0.2315789473684211</v>
+        <v>0.2134831460674156</v>
       </c>
       <c r="F3">
-        <v>0.4022630691754402</v>
+        <v>0.4230970861543641</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1.665445665445666</v>
+        <v>1.723160027008778</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -15867,22 +15873,22 @@
         <v>30</v>
       </c>
       <c r="C4">
-        <v>44.11111111111111</v>
+        <v>38</v>
       </c>
       <c r="D4">
-        <v>-0.239463601532567</v>
+        <v>-0.320079522862823</v>
       </c>
       <c r="E4">
-        <v>-0.1047619047619048</v>
+        <v>-0.2000000000000001</v>
       </c>
       <c r="F4">
-        <v>0.3537922878749164</v>
+        <v>0.38968929931421</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4">
-        <v>1.609920391916718</v>
+        <v>1.635333333333333</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -15893,22 +15899,22 @@
         <v>31</v>
       </c>
       <c r="C5">
-        <v>78.44444444444444</v>
+        <v>69.22222222222223</v>
       </c>
       <c r="D5">
-        <v>0.3320754716981134</v>
+        <v>0.3722466960352424</v>
       </c>
       <c r="E5">
-        <v>0.127962085308057</v>
+        <v>0.06557377049180335</v>
       </c>
       <c r="F5">
-        <v>0.7886492748918057</v>
+        <v>0.7894911189938829</v>
       </c>
       <c r="G5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>1.499653979238754</v>
+        <v>1.304804804804805</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -15919,16 +15925,22 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>10.22222222222222</v>
+        <v>41.77777777777778</v>
+      </c>
+      <c r="D6">
+        <v>1.010695187165775</v>
+      </c>
+      <c r="E6">
+        <v>0.7887323943661972</v>
       </c>
       <c r="F6">
-        <v>2.688230436269033</v>
+        <v>2.061790719574921</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>5.593220338983051</v>
+        <v>2.227353463587922</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -15939,22 +15951,22 @@
         <v>33</v>
       </c>
       <c r="C7">
-        <v>72.55555555555556</v>
+        <v>72.11111111111111</v>
       </c>
       <c r="D7">
-        <v>0.2414448669201521</v>
+        <v>0.3111111111111111</v>
       </c>
       <c r="E7">
-        <v>-0.2710280373831775</v>
+        <v>-0.3031674208144797</v>
       </c>
       <c r="F7">
-        <v>0.27396272946646</v>
+        <v>0.273667644759039</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>1.232088799192735</v>
+        <v>1.224146981627297</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -15965,22 +15977,22 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>42.77777777777778</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="D8">
-        <v>0.1993769470404985</v>
+        <v>0.4315352697095436</v>
       </c>
       <c r="E8">
-        <v>-0.05825242718446599</v>
+        <v>0.2535211267605633</v>
       </c>
       <c r="F8">
-        <v>0.6086974327906665</v>
+        <v>0.6275203823400812</v>
       </c>
       <c r="G8">
         <v>2</v>
       </c>
       <c r="H8">
-        <v>2.012298232129131</v>
+        <v>2.054735013032146</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -15991,22 +16003,22 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>42.77777777777778</v>
+        <v>77.66666666666667</v>
       </c>
       <c r="D9">
-        <v>0.1993769470404985</v>
+        <v>0.02043795620437949</v>
       </c>
       <c r="E9">
-        <v>-0.05825242718446599</v>
+        <v>-0.02369668246445489</v>
       </c>
       <c r="F9">
-        <v>0.6086974327906665</v>
+        <v>0.1434682196277631</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9">
-        <v>2.012298232129131</v>
+        <v>1.155251141552511</v>
       </c>
     </row>
   </sheetData>
@@ -24800,10 +24812,10 @@
         <v>62</v>
       </c>
       <c r="D504">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E504">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F504" t="s">
         <v>36</v>
@@ -24920,10 +24932,10 @@
         <v>29</v>
       </c>
       <c r="D510">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E510">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F510" t="s">
         <v>36</v>
@@ -25220,10 +25232,10 @@
         <v>82</v>
       </c>
       <c r="D525">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E525">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F525" t="s">
         <v>36</v>
@@ -25260,10 +25272,10 @@
         <v>28</v>
       </c>
       <c r="D527">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="E527">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="F527" t="s">
         <v>36</v>
@@ -25560,10 +25572,10 @@
         <v>30</v>
       </c>
       <c r="D542">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E542">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F542" t="s">
         <v>36</v>
@@ -25640,10 +25652,10 @@
         <v>31</v>
       </c>
       <c r="D546">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E546">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F546" t="s">
         <v>36</v>
@@ -25740,10 +25752,10 @@
         <v>105</v>
       </c>
       <c r="D551">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E551">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F551" t="s">
         <v>36</v>
@@ -25840,10 +25852,10 @@
         <v>110</v>
       </c>
       <c r="D556">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E556">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F556" t="s">
         <v>36</v>
@@ -25940,10 +25952,10 @@
         <v>115</v>
       </c>
       <c r="D561">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E561">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F561" t="s">
         <v>36</v>
@@ -25960,10 +25972,10 @@
         <v>116</v>
       </c>
       <c r="D562">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E562">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F562" t="s">
         <v>36</v>
@@ -26040,10 +26052,10 @@
         <v>120</v>
       </c>
       <c r="D566">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E566">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F566" t="s">
         <v>36</v>
@@ -26200,10 +26212,10 @@
         <v>34</v>
       </c>
       <c r="D574">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E574">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F574" t="s">
         <v>36</v>
@@ -26400,10 +26412,10 @@
         <v>136</v>
       </c>
       <c r="D584">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E584">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F584" t="s">
         <v>36</v>
@@ -26600,10 +26612,10 @@
         <v>146</v>
       </c>
       <c r="D594">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E594">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F594" t="s">
         <v>36</v>
@@ -26620,10 +26632,10 @@
         <v>147</v>
       </c>
       <c r="D595">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E595">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F595" t="s">
         <v>36</v>
@@ -26740,10 +26752,10 @@
         <v>153</v>
       </c>
       <c r="D601">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E601">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F601" t="s">
         <v>36</v>
@@ -27560,10 +27572,10 @@
         <v>194</v>
       </c>
       <c r="D642">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E642">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F642" t="s">
         <v>36</v>
@@ -27660,10 +27672,10 @@
         <v>199</v>
       </c>
       <c r="D647">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E647">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F647" t="s">
         <v>36</v>
@@ -27900,10 +27912,10 @@
         <v>211</v>
       </c>
       <c r="D659">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E659">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F659" t="s">
         <v>36</v>
@@ -28060,10 +28072,10 @@
         <v>219</v>
       </c>
       <c r="D667">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E667">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F667" t="s">
         <v>36</v>
@@ -28200,10 +28212,10 @@
         <v>226</v>
       </c>
       <c r="D674">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E674">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F674" t="s">
         <v>36</v>
@@ -28260,10 +28272,10 @@
         <v>229</v>
       </c>
       <c r="D677">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E677">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F677" t="s">
         <v>36</v>
@@ -28320,10 +28332,10 @@
         <v>232</v>
       </c>
       <c r="D680">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E680">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F680" t="s">
         <v>36</v>
@@ -28380,10 +28392,10 @@
         <v>235</v>
       </c>
       <c r="D683">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E683">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F683" t="s">
         <v>36</v>
@@ -28400,10 +28412,10 @@
         <v>236</v>
       </c>
       <c r="D684">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E684">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F684" t="s">
         <v>36</v>
@@ -28480,10 +28492,10 @@
         <v>240</v>
       </c>
       <c r="D688">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E688">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F688" t="s">
         <v>36</v>
@@ -28520,10 +28532,10 @@
         <v>242</v>
       </c>
       <c r="D690">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E690">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F690" t="s">
         <v>36</v>
@@ -28720,10 +28732,10 @@
         <v>252</v>
       </c>
       <c r="D700">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E700">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F700" t="s">
         <v>36</v>
@@ -28820,10 +28832,10 @@
         <v>257</v>
       </c>
       <c r="D705">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E705">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F705" t="s">
         <v>36</v>
@@ -28980,10 +28992,10 @@
         <v>265</v>
       </c>
       <c r="D713">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E713">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F713" t="s">
         <v>36</v>
@@ -29220,10 +29232,10 @@
         <v>277</v>
       </c>
       <c r="D725">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E725">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F725" t="s">
         <v>36</v>
@@ -29500,10 +29512,10 @@
         <v>291</v>
       </c>
       <c r="D739">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E739">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F739" t="s">
         <v>36</v>
@@ -29540,10 +29552,10 @@
         <v>32</v>
       </c>
       <c r="D741">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E741">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F741" t="s">
         <v>36</v>
@@ -29799,7 +29811,7 @@
         <v>28</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G2">
         <v>9</v>
@@ -29822,7 +29834,7 @@
         <v>28</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G3">
         <v>9</v>
@@ -29868,7 +29880,7 @@
         <v>28</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5">
         <v>7</v>
@@ -29891,7 +29903,7 @@
         <v>28</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6">
         <v>7</v>
@@ -30029,7 +30041,7 @@
         <v>28</v>
       </c>
       <c r="F12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G12">
         <v>8</v>
@@ -30144,7 +30156,7 @@
         <v>28</v>
       </c>
       <c r="F17">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G17">
         <v>9</v>
@@ -30167,7 +30179,7 @@
         <v>28</v>
       </c>
       <c r="F18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G18">
         <v>8</v>
@@ -30262,7 +30274,7 @@
         <v>22</v>
       </c>
       <c r="G22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -30328,10 +30340,10 @@
         <v>28</v>
       </c>
       <c r="F25">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G25">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -30354,7 +30366,7 @@
         <v>22</v>
       </c>
       <c r="G26">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -30558,10 +30570,10 @@
         <v>29</v>
       </c>
       <c r="F35">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G35">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -30607,7 +30619,7 @@
         <v>42</v>
       </c>
       <c r="G37">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -30627,10 +30639,10 @@
         <v>29</v>
       </c>
       <c r="F38">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G38">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -30650,10 +30662,10 @@
         <v>29</v>
       </c>
       <c r="F39">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G39">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -30673,10 +30685,10 @@
         <v>29</v>
       </c>
       <c r="F40">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G40">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -30696,10 +30708,10 @@
         <v>29</v>
       </c>
       <c r="F41">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G41">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -30719,7 +30731,7 @@
         <v>29</v>
       </c>
       <c r="F42">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G42">
         <v>7</v>
@@ -30742,10 +30754,10 @@
         <v>29</v>
       </c>
       <c r="F43">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G43">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -30768,7 +30780,7 @@
         <v>69</v>
       </c>
       <c r="G44">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -30791,7 +30803,7 @@
         <v>48</v>
       </c>
       <c r="G45">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -30814,7 +30826,7 @@
         <v>64</v>
       </c>
       <c r="G46">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -30834,10 +30846,10 @@
         <v>29</v>
       </c>
       <c r="F47">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G47">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -30857,10 +30869,10 @@
         <v>29</v>
       </c>
       <c r="F48">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G48">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -30883,7 +30895,7 @@
         <v>53</v>
       </c>
       <c r="G49">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -30906,7 +30918,7 @@
         <v>50</v>
       </c>
       <c r="G50">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -30929,7 +30941,7 @@
         <v>100</v>
       </c>
       <c r="G51">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -30949,10 +30961,10 @@
         <v>29</v>
       </c>
       <c r="F52">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G52">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -30972,7 +30984,7 @@
         <v>29</v>
       </c>
       <c r="F53">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G53">
         <v>11</v>
@@ -30995,10 +31007,10 @@
         <v>29</v>
       </c>
       <c r="F54">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G54">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -31018,10 +31030,10 @@
         <v>29</v>
       </c>
       <c r="F55">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G55">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -31064,10 +31076,10 @@
         <v>29</v>
       </c>
       <c r="F57">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G57">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -31087,10 +31099,10 @@
         <v>29</v>
       </c>
       <c r="F58">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G58">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -31110,10 +31122,10 @@
         <v>29</v>
       </c>
       <c r="F59">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G59">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -31133,10 +31145,10 @@
         <v>29</v>
       </c>
       <c r="F60">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G60">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -31156,10 +31168,10 @@
         <v>29</v>
       </c>
       <c r="F61">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G61">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -31179,7 +31191,7 @@
         <v>29</v>
       </c>
       <c r="F62">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G62">
         <v>8</v>
@@ -31202,10 +31214,10 @@
         <v>29</v>
       </c>
       <c r="F63">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G63">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -31248,10 +31260,10 @@
         <v>29</v>
       </c>
       <c r="F65">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G65">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -31271,10 +31283,10 @@
         <v>29</v>
       </c>
       <c r="F66">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G66">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -31294,10 +31306,10 @@
         <v>29</v>
       </c>
       <c r="F67">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G67">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -31320,7 +31332,7 @@
         <v>53</v>
       </c>
       <c r="G68">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -31340,7 +31352,7 @@
         <v>30</v>
       </c>
       <c r="F69">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G69">
         <v>28</v>
@@ -31363,10 +31375,10 @@
         <v>30</v>
       </c>
       <c r="F70">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G70">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -31386,10 +31398,10 @@
         <v>30</v>
       </c>
       <c r="F71">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G71">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -31409,10 +31421,10 @@
         <v>30</v>
       </c>
       <c r="F72">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G72">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -31432,10 +31444,10 @@
         <v>30</v>
       </c>
       <c r="F73">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G73">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -31458,7 +31470,7 @@
         <v>54</v>
       </c>
       <c r="G74">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -31481,7 +31493,7 @@
         <v>64</v>
       </c>
       <c r="G75">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -31504,7 +31516,7 @@
         <v>71</v>
       </c>
       <c r="G76">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -31524,10 +31536,10 @@
         <v>30</v>
       </c>
       <c r="F77">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G77">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -31570,10 +31582,10 @@
         <v>30</v>
       </c>
       <c r="F79">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G79">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -31593,10 +31605,10 @@
         <v>30</v>
       </c>
       <c r="F80">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G80">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -31616,10 +31628,10 @@
         <v>30</v>
       </c>
       <c r="F81">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G81">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -31639,10 +31651,10 @@
         <v>30</v>
       </c>
       <c r="F82">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G82">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -31662,7 +31674,7 @@
         <v>30</v>
       </c>
       <c r="F83">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G83">
         <v>20</v>
@@ -31685,10 +31697,10 @@
         <v>30</v>
       </c>
       <c r="F84">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G84">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -31731,10 +31743,10 @@
         <v>30</v>
       </c>
       <c r="F86">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G86">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -31754,10 +31766,10 @@
         <v>30</v>
       </c>
       <c r="F87">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G87">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -31777,7 +31789,7 @@
         <v>30</v>
       </c>
       <c r="F88">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G88">
         <v>20</v>
@@ -31803,7 +31815,7 @@
         <v>52</v>
       </c>
       <c r="G89">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -31823,10 +31835,10 @@
         <v>30</v>
       </c>
       <c r="F90">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G90">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -31846,10 +31858,10 @@
         <v>30</v>
       </c>
       <c r="F91">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G91">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -31869,10 +31881,10 @@
         <v>30</v>
       </c>
       <c r="F92">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G92">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -31892,10 +31904,10 @@
         <v>30</v>
       </c>
       <c r="F93">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G93">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -31915,10 +31927,10 @@
         <v>30</v>
       </c>
       <c r="F94">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G94">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -31938,10 +31950,10 @@
         <v>30</v>
       </c>
       <c r="F95">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G95">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -31984,10 +31996,10 @@
         <v>30</v>
       </c>
       <c r="F97">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G97">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -32007,7 +32019,7 @@
         <v>30</v>
       </c>
       <c r="F98">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G98">
         <v>12</v>
@@ -32033,7 +32045,7 @@
         <v>44</v>
       </c>
       <c r="G99">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -32053,10 +32065,10 @@
         <v>30</v>
       </c>
       <c r="F100">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G100">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -32076,7 +32088,7 @@
         <v>31</v>
       </c>
       <c r="F101">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -32099,7 +32111,7 @@
         <v>31</v>
       </c>
       <c r="F102">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -32125,7 +32137,7 @@
         <v>47</v>
       </c>
       <c r="G103">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -32145,10 +32157,10 @@
         <v>31</v>
       </c>
       <c r="F104">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G104">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -32168,7 +32180,7 @@
         <v>31</v>
       </c>
       <c r="F105">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -32191,7 +32203,7 @@
         <v>31</v>
       </c>
       <c r="F106">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -32214,7 +32226,7 @@
         <v>31</v>
       </c>
       <c r="F107">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G107">
         <v>4</v>
@@ -32237,7 +32249,7 @@
         <v>31</v>
       </c>
       <c r="F108">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -32260,10 +32272,10 @@
         <v>31</v>
       </c>
       <c r="F109">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G109">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -32283,7 +32295,7 @@
         <v>31</v>
       </c>
       <c r="F110">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -32306,10 +32318,10 @@
         <v>31</v>
       </c>
       <c r="F111">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G111">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -32329,10 +32341,10 @@
         <v>31</v>
       </c>
       <c r="F112">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -32352,7 +32364,7 @@
         <v>31</v>
       </c>
       <c r="F113">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -32378,7 +32390,7 @@
         <v>45</v>
       </c>
       <c r="G114">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -32398,10 +32410,10 @@
         <v>31</v>
       </c>
       <c r="F115">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G115">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -32421,10 +32433,10 @@
         <v>31</v>
       </c>
       <c r="F116">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G116">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -32444,10 +32456,10 @@
         <v>31</v>
       </c>
       <c r="F117">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G117">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -32467,10 +32479,10 @@
         <v>31</v>
       </c>
       <c r="F118">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G118">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -32493,7 +32505,7 @@
         <v>58</v>
       </c>
       <c r="G119">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -32513,7 +32525,7 @@
         <v>31</v>
       </c>
       <c r="F120">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G120">
         <v>10</v>
@@ -32536,10 +32548,10 @@
         <v>31</v>
       </c>
       <c r="F121">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G121">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -32559,10 +32571,10 @@
         <v>31</v>
       </c>
       <c r="F122">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G122">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -32582,10 +32594,10 @@
         <v>31</v>
       </c>
       <c r="F123">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G123">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -32605,10 +32617,10 @@
         <v>31</v>
       </c>
       <c r="F124">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -32631,7 +32643,7 @@
         <v>53</v>
       </c>
       <c r="G125">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -32651,10 +32663,10 @@
         <v>31</v>
       </c>
       <c r="F126">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G126">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -32674,10 +32686,10 @@
         <v>31</v>
       </c>
       <c r="F127">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G127">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -32697,10 +32709,10 @@
         <v>31</v>
       </c>
       <c r="F128">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G128">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -32720,7 +32732,7 @@
         <v>31</v>
       </c>
       <c r="F129">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G129">
         <v>13</v>
@@ -32743,7 +32755,7 @@
         <v>31</v>
       </c>
       <c r="F130">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G130">
         <v>12</v>
@@ -32766,10 +32778,10 @@
         <v>31</v>
       </c>
       <c r="F131">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G131">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -32789,10 +32801,10 @@
         <v>31</v>
       </c>
       <c r="F132">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G132">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -32815,7 +32827,7 @@
         <v>55</v>
       </c>
       <c r="G133">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -32835,7 +32847,7 @@
         <v>32</v>
       </c>
       <c r="F134">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -32858,7 +32870,7 @@
         <v>32</v>
       </c>
       <c r="F135">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -32881,10 +32893,10 @@
         <v>32</v>
       </c>
       <c r="F136">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G136">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -32904,7 +32916,7 @@
         <v>32</v>
       </c>
       <c r="F137">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -32927,7 +32939,7 @@
         <v>32</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -32973,7 +32985,7 @@
         <v>32</v>
       </c>
       <c r="F140">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -33019,7 +33031,7 @@
         <v>32</v>
       </c>
       <c r="F142">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -33042,7 +33054,7 @@
         <v>32</v>
       </c>
       <c r="F143">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -33065,7 +33077,7 @@
         <v>32</v>
       </c>
       <c r="F144">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G144">
         <v>0</v>
@@ -33088,7 +33100,7 @@
         <v>32</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G145">
         <v>0</v>
@@ -33111,7 +33123,7 @@
         <v>32</v>
       </c>
       <c r="F146">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -33134,7 +33146,7 @@
         <v>32</v>
       </c>
       <c r="F147">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -33157,7 +33169,7 @@
         <v>32</v>
       </c>
       <c r="F148">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -33180,10 +33192,10 @@
         <v>32</v>
       </c>
       <c r="F149">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -33203,7 +33215,7 @@
         <v>32</v>
       </c>
       <c r="F150">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G150">
         <v>0</v>
@@ -33226,7 +33238,7 @@
         <v>32</v>
       </c>
       <c r="F151">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G151">
         <v>0</v>
@@ -33249,7 +33261,7 @@
         <v>32</v>
       </c>
       <c r="F152">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -33272,10 +33284,10 @@
         <v>32</v>
       </c>
       <c r="F153">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -33295,7 +33307,7 @@
         <v>32</v>
       </c>
       <c r="F154">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G154">
         <v>0</v>
@@ -33318,7 +33330,7 @@
         <v>32</v>
       </c>
       <c r="F155">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G155">
         <v>0</v>
@@ -33341,10 +33353,10 @@
         <v>32</v>
       </c>
       <c r="F156">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="G156">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -33364,10 +33376,10 @@
         <v>32</v>
       </c>
       <c r="F157">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="G157">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -33387,10 +33399,10 @@
         <v>32</v>
       </c>
       <c r="F158">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G158">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -33410,7 +33422,7 @@
         <v>32</v>
       </c>
       <c r="F159">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G159">
         <v>0</v>
@@ -33433,10 +33445,10 @@
         <v>32</v>
       </c>
       <c r="F160">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G160">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -33456,7 +33468,7 @@
         <v>32</v>
       </c>
       <c r="F161">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G161">
         <v>0</v>
@@ -33479,10 +33491,10 @@
         <v>32</v>
       </c>
       <c r="F162">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G162">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -33502,7 +33514,7 @@
         <v>32</v>
       </c>
       <c r="F163">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G163">
         <v>0</v>
@@ -33525,7 +33537,7 @@
         <v>32</v>
       </c>
       <c r="F164">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G164">
         <v>0</v>
@@ -33548,7 +33560,7 @@
         <v>32</v>
       </c>
       <c r="F165">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G165">
         <v>5</v>
@@ -33571,10 +33583,10 @@
         <v>32</v>
       </c>
       <c r="F166">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -33594,10 +33606,10 @@
         <v>33</v>
       </c>
       <c r="F167">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G167">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -33617,10 +33629,10 @@
         <v>33</v>
       </c>
       <c r="F168">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G168">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -33640,10 +33652,10 @@
         <v>33</v>
       </c>
       <c r="F169">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G169">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -33663,10 +33675,10 @@
         <v>33</v>
       </c>
       <c r="F170">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G170">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -33686,10 +33698,10 @@
         <v>33</v>
       </c>
       <c r="F171">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G171">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -33712,7 +33724,7 @@
         <v>33</v>
       </c>
       <c r="G172">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -33732,7 +33744,7 @@
         <v>33</v>
       </c>
       <c r="F173">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G173">
         <v>23</v>
@@ -33755,10 +33767,10 @@
         <v>33</v>
       </c>
       <c r="F174">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G174">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -33778,10 +33790,10 @@
         <v>33</v>
       </c>
       <c r="F175">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G175">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -33801,10 +33813,10 @@
         <v>33</v>
       </c>
       <c r="F176">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G176">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -33824,10 +33836,10 @@
         <v>33</v>
       </c>
       <c r="F177">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G177">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -33847,10 +33859,10 @@
         <v>33</v>
       </c>
       <c r="F178">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G178">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -33870,10 +33882,10 @@
         <v>33</v>
       </c>
       <c r="F179">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G179">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -33893,10 +33905,10 @@
         <v>33</v>
       </c>
       <c r="F180">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G180">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -33919,7 +33931,7 @@
         <v>44</v>
       </c>
       <c r="G181">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -33939,7 +33951,7 @@
         <v>33</v>
       </c>
       <c r="F182">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G182">
         <v>27</v>
@@ -33962,7 +33974,7 @@
         <v>33</v>
       </c>
       <c r="F183">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G183">
         <v>26</v>
@@ -33985,10 +33997,10 @@
         <v>33</v>
       </c>
       <c r="F184">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G184">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -34008,10 +34020,10 @@
         <v>33</v>
       </c>
       <c r="F185">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G185">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -34031,10 +34043,10 @@
         <v>33</v>
       </c>
       <c r="F186">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G186">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -34054,10 +34066,10 @@
         <v>33</v>
       </c>
       <c r="F187">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G187">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -34077,10 +34089,10 @@
         <v>33</v>
       </c>
       <c r="F188">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G188">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -34103,7 +34115,7 @@
         <v>52</v>
       </c>
       <c r="G189">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -34123,10 +34135,10 @@
         <v>33</v>
       </c>
       <c r="F190">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G190">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -34146,10 +34158,10 @@
         <v>33</v>
       </c>
       <c r="F191">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G191">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -34169,10 +34181,10 @@
         <v>33</v>
       </c>
       <c r="F192">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G192">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -34195,7 +34207,7 @@
         <v>63</v>
       </c>
       <c r="G193">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -34215,7 +34227,7 @@
         <v>33</v>
       </c>
       <c r="F194">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G194">
         <v>36</v>
@@ -34238,10 +34250,10 @@
         <v>33</v>
       </c>
       <c r="F195">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G195">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -34261,10 +34273,10 @@
         <v>33</v>
       </c>
       <c r="F196">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G196">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -34287,7 +34299,7 @@
         <v>56</v>
       </c>
       <c r="G197">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -34307,10 +34319,10 @@
         <v>33</v>
       </c>
       <c r="F198">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G198">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -34330,7 +34342,7 @@
         <v>33</v>
       </c>
       <c r="F199">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G199">
         <v>23</v>
@@ -34353,10 +34365,10 @@
         <v>34</v>
       </c>
       <c r="F200">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G200">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -34379,7 +34391,7 @@
         <v>0</v>
       </c>
       <c r="G201">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -34399,10 +34411,10 @@
         <v>34</v>
       </c>
       <c r="F202">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G202">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -34425,7 +34437,7 @@
         <v>0</v>
       </c>
       <c r="G203">
-        <v>63</v>
+        <v>42</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -34448,7 +34460,7 @@
         <v>0</v>
       </c>
       <c r="G204">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -34468,10 +34480,10 @@
         <v>34</v>
       </c>
       <c r="F205">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G205">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -34494,7 +34506,7 @@
         <v>0</v>
       </c>
       <c r="G206">
-        <v>87</v>
+        <v>64</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -34514,10 +34526,10 @@
         <v>34</v>
       </c>
       <c r="F207">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G207">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -34540,7 +34552,7 @@
         <v>0</v>
       </c>
       <c r="G208">
-        <v>22</v>
+        <v>59</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -34586,7 +34598,7 @@
         <v>0</v>
       </c>
       <c r="G210">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -34606,10 +34618,10 @@
         <v>34</v>
       </c>
       <c r="F211">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G211">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -34629,10 +34641,10 @@
         <v>34</v>
       </c>
       <c r="F212">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G212">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -34655,7 +34667,7 @@
         <v>0</v>
       </c>
       <c r="G213">
-        <v>84</v>
+        <v>55</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -34675,10 +34687,10 @@
         <v>34</v>
       </c>
       <c r="F214">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G214">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -34701,7 +34713,7 @@
         <v>0</v>
       </c>
       <c r="G215">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -34721,10 +34733,10 @@
         <v>34</v>
       </c>
       <c r="F216">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G216">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -34744,10 +34756,10 @@
         <v>34</v>
       </c>
       <c r="F217">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G217">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -34770,7 +34782,7 @@
         <v>0</v>
       </c>
       <c r="G218">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -34790,10 +34802,10 @@
         <v>34</v>
       </c>
       <c r="F219">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G219">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -34813,10 +34825,10 @@
         <v>34</v>
       </c>
       <c r="F220">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G220">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -34839,7 +34851,7 @@
         <v>0</v>
       </c>
       <c r="G221">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -34859,10 +34871,10 @@
         <v>34</v>
       </c>
       <c r="F222">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G222">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -34882,10 +34894,10 @@
         <v>34</v>
       </c>
       <c r="F223">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G223">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -34908,7 +34920,7 @@
         <v>14</v>
       </c>
       <c r="G224">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -34954,7 +34966,7 @@
         <v>0</v>
       </c>
       <c r="G226">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -34977,7 +34989,7 @@
         <v>0</v>
       </c>
       <c r="G227">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -34997,10 +35009,10 @@
         <v>34</v>
       </c>
       <c r="F228">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G228">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -35023,7 +35035,7 @@
         <v>0</v>
       </c>
       <c r="G229">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -35046,7 +35058,7 @@
         <v>0</v>
       </c>
       <c r="G230">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -35069,7 +35081,7 @@
         <v>7</v>
       </c>
       <c r="G231">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -35092,7 +35104,7 @@
         <v>0</v>
       </c>
       <c r="G232">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -35112,10 +35124,10 @@
         <v>35</v>
       </c>
       <c r="F233">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G233">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -35135,10 +35147,10 @@
         <v>35</v>
       </c>
       <c r="F234">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G234">
-        <v>54</v>
+        <v>12</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -35158,10 +35170,10 @@
         <v>35</v>
       </c>
       <c r="F235">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G235">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -35181,10 +35193,10 @@
         <v>35</v>
       </c>
       <c r="F236">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G236">
-        <v>63</v>
+        <v>10</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -35204,10 +35216,10 @@
         <v>35</v>
       </c>
       <c r="F237">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G237">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -35227,10 +35239,10 @@
         <v>35</v>
       </c>
       <c r="F238">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G238">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -35250,10 +35262,10 @@
         <v>35</v>
       </c>
       <c r="F239">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G239">
-        <v>87</v>
+        <v>11</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -35273,10 +35285,10 @@
         <v>35</v>
       </c>
       <c r="F240">
+        <v>33</v>
+      </c>
+      <c r="G240">
         <v>12</v>
-      </c>
-      <c r="G240">
-        <v>75</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -35296,10 +35308,10 @@
         <v>35</v>
       </c>
       <c r="F241">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G241">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -35319,10 +35331,10 @@
         <v>35</v>
       </c>
       <c r="F242">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G242">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -35342,10 +35354,10 @@
         <v>35</v>
       </c>
       <c r="F243">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G243">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -35365,10 +35377,10 @@
         <v>35</v>
       </c>
       <c r="F244">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G244">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -35388,10 +35400,10 @@
         <v>35</v>
       </c>
       <c r="F245">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G245">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -35411,10 +35423,10 @@
         <v>35</v>
       </c>
       <c r="F246">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G246">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -35434,10 +35446,10 @@
         <v>35</v>
       </c>
       <c r="F247">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="G247">
-        <v>49</v>
+        <v>12</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -35457,10 +35469,10 @@
         <v>35</v>
       </c>
       <c r="F248">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G248">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -35480,10 +35492,10 @@
         <v>35</v>
       </c>
       <c r="F249">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="G249">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -35503,10 +35515,10 @@
         <v>35</v>
       </c>
       <c r="F250">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G250">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -35526,10 +35538,10 @@
         <v>35</v>
       </c>
       <c r="F251">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G251">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -35549,10 +35561,10 @@
         <v>35</v>
       </c>
       <c r="F252">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G252">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -35572,10 +35584,10 @@
         <v>35</v>
       </c>
       <c r="F253">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G253">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -35595,10 +35607,10 @@
         <v>35</v>
       </c>
       <c r="F254">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G254">
-        <v>55</v>
+        <v>11</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -35618,10 +35630,10 @@
         <v>35</v>
       </c>
       <c r="F255">
+        <v>30</v>
+      </c>
+      <c r="G255">
         <v>12</v>
-      </c>
-      <c r="G255">
-        <v>47</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -35641,10 +35653,10 @@
         <v>35</v>
       </c>
       <c r="F256">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G256">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -35664,10 +35676,10 @@
         <v>35</v>
       </c>
       <c r="F257">
+        <v>30</v>
+      </c>
+      <c r="G257">
         <v>14</v>
-      </c>
-      <c r="G257">
-        <v>64</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -35687,10 +35699,10 @@
         <v>35</v>
       </c>
       <c r="F258">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="G258">
-        <v>100</v>
+        <v>16</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -35710,10 +35722,10 @@
         <v>35</v>
       </c>
       <c r="F259">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G259">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -35733,10 +35745,10 @@
         <v>35</v>
       </c>
       <c r="F260">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G260">
-        <v>50</v>
+        <v>12</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -35756,10 +35768,10 @@
         <v>35</v>
       </c>
       <c r="F261">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G261">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -35779,10 +35791,10 @@
         <v>35</v>
       </c>
       <c r="F262">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G262">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -35802,10 +35814,10 @@
         <v>35</v>
       </c>
       <c r="F263">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G263">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -35825,10 +35837,10 @@
         <v>35</v>
       </c>
       <c r="F264">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="G264">
-        <v>41</v>
+        <v>11</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -35848,10 +35860,10 @@
         <v>35</v>
       </c>
       <c r="F265">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G265">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/dados.xlsx
+++ b/downloads/dados.xlsx
@@ -3936,7 +3936,7 @@
         <v>29</v>
       </c>
       <c r="G67">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H67" t="s">
         <v>36</v>
@@ -4794,7 +4794,7 @@
         <v>30</v>
       </c>
       <c r="G100">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H100" t="s">
         <v>36</v>
@@ -5652,7 +5652,7 @@
         <v>31</v>
       </c>
       <c r="G133">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H133" t="s">
         <v>36</v>
@@ -6588,7 +6588,7 @@
         <v>33</v>
       </c>
       <c r="G169">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H169" t="s">
         <v>36</v>
@@ -6640,7 +6640,7 @@
         <v>33</v>
       </c>
       <c r="G171">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H171" t="s">
         <v>36</v>
@@ -6848,7 +6848,7 @@
         <v>33</v>
       </c>
       <c r="G179">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H179" t="s">
         <v>36</v>
@@ -6926,7 +6926,7 @@
         <v>33</v>
       </c>
       <c r="G182">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H182" t="s">
         <v>36</v>
@@ -7108,7 +7108,7 @@
         <v>33</v>
       </c>
       <c r="G189">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H189" t="s">
         <v>36</v>
@@ -7212,7 +7212,7 @@
         <v>33</v>
       </c>
       <c r="G193">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H193" t="s">
         <v>36</v>
@@ -7368,7 +7368,7 @@
         <v>33</v>
       </c>
       <c r="G199">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H199" t="s">
         <v>36</v>
@@ -8226,7 +8226,7 @@
         <v>34</v>
       </c>
       <c r="G232">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H232" t="s">
         <v>36</v>
@@ -9175,22 +9175,22 @@
         <v>50.77777777777778</v>
       </c>
       <c r="D3">
-        <v>47.11111111111111</v>
+        <v>46.88888888888889</v>
       </c>
       <c r="E3">
-        <v>-0.07221006564551413</v>
+        <v>-0.07658643326039394</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>35.33333333333334</v>
       </c>
       <c r="G3">
         <v>29.66666666666667</v>
       </c>
       <c r="H3">
-        <v>0.2134831460674156</v>
+        <v>0.1910112359550562</v>
       </c>
       <c r="I3">
-        <v>0.4230970861543641</v>
+        <v>0.4238783724201226</v>
       </c>
       <c r="J3" t="s">
         <v>46</v>
@@ -9207,22 +9207,22 @@
         <v>55.88888888888889</v>
       </c>
       <c r="D4">
-        <v>38</v>
+        <v>38.11111111111111</v>
       </c>
       <c r="E4">
-        <v>-0.320079522862823</v>
+        <v>-0.3180914512922465</v>
       </c>
       <c r="F4">
-        <v>25.33333333333333</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="G4">
         <v>31.66666666666667</v>
       </c>
       <c r="H4">
-        <v>-0.2000000000000001</v>
+        <v>-0.1894736842105263</v>
       </c>
       <c r="I4">
-        <v>0.38968929931421</v>
+        <v>0.3888486146797661</v>
       </c>
       <c r="J4" t="s">
         <v>47</v>
@@ -9239,22 +9239,22 @@
         <v>50.44444444444444</v>
       </c>
       <c r="D5">
-        <v>69.22222222222223</v>
+        <v>69</v>
       </c>
       <c r="E5">
-        <v>0.3722466960352424</v>
+        <v>0.36784140969163</v>
       </c>
       <c r="F5">
-        <v>65</v>
+        <v>64.33333333333333</v>
       </c>
       <c r="G5">
         <v>61</v>
       </c>
       <c r="H5">
-        <v>0.06557377049180335</v>
+        <v>0.05464480874316924</v>
       </c>
       <c r="I5">
-        <v>0.7894911189938829</v>
+        <v>0.7890870428085769</v>
       </c>
       <c r="J5" t="s">
         <v>46</v>
@@ -9303,22 +9303,22 @@
         <v>55</v>
       </c>
       <c r="D7">
-        <v>72.11111111111111</v>
+        <v>72.55555555555556</v>
       </c>
       <c r="E7">
-        <v>0.3111111111111111</v>
+        <v>0.3191919191919192</v>
       </c>
       <c r="F7">
-        <v>51.33333333333334</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>73.66666666666667</v>
       </c>
       <c r="H7">
-        <v>-0.3031674208144797</v>
+        <v>-0.2805429864253394</v>
       </c>
       <c r="I7">
-        <v>0.273667644759039</v>
+        <v>0.2705889226732273</v>
       </c>
       <c r="J7" t="s">
         <v>47</v>
@@ -9335,22 +9335,22 @@
         <v>26.77777777777778</v>
       </c>
       <c r="D8">
-        <v>38.33333333333334</v>
+        <v>38.44444444444444</v>
       </c>
       <c r="E8">
-        <v>0.4315352697095436</v>
+        <v>0.4356846473029046</v>
       </c>
       <c r="F8">
-        <v>29.66666666666667</v>
+        <v>30</v>
       </c>
       <c r="G8">
         <v>23.66666666666667</v>
       </c>
       <c r="H8">
-        <v>0.2535211267605633</v>
+        <v>0.2676056338028168</v>
       </c>
       <c r="I8">
-        <v>0.6275203823400812</v>
+        <v>0.6273275480689409</v>
       </c>
       <c r="J8" t="s">
         <v>46</v>
@@ -9494,40 +9494,40 @@
         <v>29</v>
       </c>
       <c r="C3">
-        <v>1.723160027008778</v>
+        <v>1.725490196078431</v>
       </c>
       <c r="D3">
-        <v>1.255232950708981</v>
+        <v>1.256930358350237</v>
       </c>
       <c r="E3">
-        <v>1.032410533423363</v>
+        <v>1.033806626098715</v>
       </c>
       <c r="F3">
-        <v>0.7947332883187036</v>
+        <v>0.7958079783637592</v>
       </c>
       <c r="G3">
-        <v>0.6907494935854153</v>
+        <v>0.691683569979716</v>
       </c>
       <c r="H3">
-        <v>0.6090479405806888</v>
+        <v>0.6098715348208248</v>
       </c>
       <c r="I3">
-        <v>0.824442943956786</v>
+        <v>0.8255578093306287</v>
       </c>
       <c r="J3">
-        <v>0.7873058744091831</v>
+        <v>0.7883705206220419</v>
       </c>
       <c r="K3">
-        <v>0.8541525995948684</v>
+        <v>0.8404327248140635</v>
       </c>
       <c r="L3">
-        <v>0.9469952734638758</v>
+        <v>0.9482758620689655</v>
       </c>
       <c r="M3">
-        <v>1.147535449020932</v>
+        <v>1.149087221095335</v>
       </c>
       <c r="N3">
-        <v>1.548615800135044</v>
+        <v>1.550709939148073</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -9538,40 +9538,40 @@
         <v>30</v>
       </c>
       <c r="C4">
-        <v>1.635333333333333</v>
+        <v>1.634243837441705</v>
       </c>
       <c r="D4">
-        <v>1.584</v>
+        <v>1.582944703530979</v>
       </c>
       <c r="E4">
-        <v>0.9533333333333334</v>
+        <v>0.9526982011992006</v>
       </c>
       <c r="F4">
-        <v>0.7406666666666666</v>
+        <v>0.7401732178547634</v>
       </c>
       <c r="G4">
-        <v>0.8066666666666666</v>
+        <v>0.8061292471685543</v>
       </c>
       <c r="H4">
-        <v>0.7040000000000001</v>
+        <v>0.703530979347102</v>
       </c>
       <c r="I4">
-        <v>0.8360000000000001</v>
+        <v>0.8354430379746836</v>
       </c>
       <c r="J4">
-        <v>0.6820000000000001</v>
+        <v>0.681545636242505</v>
       </c>
       <c r="K4">
-        <v>0.858</v>
+        <v>0.8647568287808128</v>
       </c>
       <c r="L4">
-        <v>1.056</v>
+        <v>1.055296469020653</v>
       </c>
       <c r="M4">
-        <v>1.078</v>
+        <v>1.07728181212525</v>
       </c>
       <c r="N4">
-        <v>1.166</v>
+        <v>1.165223184543638</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -9582,40 +9582,40 @@
         <v>31</v>
       </c>
       <c r="C5">
-        <v>0.8258258258258259</v>
+        <v>0.8270676691729324</v>
       </c>
       <c r="D5">
-        <v>1.106606606606606</v>
+        <v>1.108270676691729</v>
       </c>
       <c r="E5">
-        <v>1.106606606606606</v>
+        <v>1.108270676691729</v>
       </c>
       <c r="F5">
-        <v>0.9084084084084083</v>
+        <v>0.9097744360902255</v>
       </c>
       <c r="G5">
-        <v>1.304804804804805</v>
+        <v>1.306766917293233</v>
       </c>
       <c r="H5">
-        <v>0.8588588588588587</v>
+        <v>0.8601503759398496</v>
       </c>
       <c r="I5">
-        <v>1.156156156156156</v>
+        <v>1.157894736842105</v>
       </c>
       <c r="J5">
-        <v>0.801051051051051</v>
+        <v>0.8022556390977444</v>
       </c>
       <c r="K5">
-        <v>1.197447447447447</v>
+        <v>1.182706766917293</v>
       </c>
       <c r="L5">
-        <v>0.5326576576576576</v>
+        <v>0.5334586466165413</v>
       </c>
       <c r="M5">
-        <v>0.9786036036036035</v>
+        <v>0.9800751879699248</v>
       </c>
       <c r="N5">
-        <v>1.09009009009009</v>
+        <v>1.091729323308271</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -9670,40 +9670,40 @@
         <v>33</v>
       </c>
       <c r="C7">
-        <v>1.056692913385827</v>
+        <v>1.061909758656873</v>
       </c>
       <c r="D7">
-        <v>1.224146981627297</v>
+        <v>1.223504721930745</v>
       </c>
       <c r="E7">
-        <v>1.195275590551181</v>
+        <v>1.183105981112277</v>
       </c>
       <c r="F7">
-        <v>0.9758530183727034</v>
+        <v>0.9695697796432319</v>
       </c>
       <c r="G7">
-        <v>1.039370078740157</v>
+        <v>1.03305351521511</v>
       </c>
       <c r="H7">
-        <v>0.9412073490813648</v>
+        <v>0.9407135362014691</v>
       </c>
       <c r="I7">
-        <v>1.056692913385827</v>
+        <v>1.056138509968521</v>
       </c>
       <c r="J7">
-        <v>0.8661417322834646</v>
+        <v>0.8656873032528857</v>
       </c>
       <c r="K7">
-        <v>0.7564304461942257</v>
+        <v>0.7848898216159497</v>
       </c>
       <c r="L7">
-        <v>0.6755905511811023</v>
+        <v>0.6752360965372508</v>
       </c>
       <c r="M7">
-        <v>1.013385826771654</v>
+        <v>1.004197271773347</v>
       </c>
       <c r="N7">
-        <v>1.143307086614173</v>
+        <v>1.142707240293809</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -9714,40 +9714,40 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>1.165942658557776</v>
+        <v>1.164930555555556</v>
       </c>
       <c r="D8">
-        <v>2.054735013032146</v>
+        <v>2.052951388888889</v>
       </c>
       <c r="E8">
-        <v>0.9079061685490879</v>
+        <v>0.9071180555555557</v>
       </c>
       <c r="F8">
-        <v>0.9748045178105996</v>
+        <v>0.9739583333333334</v>
       </c>
       <c r="G8">
-        <v>0.9079061685490879</v>
+        <v>0.9071180555555557</v>
       </c>
       <c r="H8">
-        <v>0.420503909643788</v>
+        <v>0.4201388888888889</v>
       </c>
       <c r="I8">
-        <v>0.8887923544743702</v>
+        <v>0.8880208333333334</v>
       </c>
       <c r="J8">
-        <v>1.156385751520417</v>
+        <v>1.155381944444445</v>
       </c>
       <c r="K8">
-        <v>1.137271937445699</v>
+        <v>1.145833333333333</v>
       </c>
       <c r="L8">
-        <v>0.6020851433536056</v>
+        <v>0.6015625</v>
       </c>
       <c r="M8">
-        <v>0.4874022589052998</v>
+        <v>0.4869791666666667</v>
       </c>
       <c r="N8">
-        <v>0.9891398783666379</v>
+        <v>0.9882812500000001</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -10439,7 +10439,7 @@
         <v>46082</v>
       </c>
       <c r="E28">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F28">
         <v>2026</v>
@@ -15847,22 +15847,22 @@
         <v>29</v>
       </c>
       <c r="C3">
-        <v>47.11111111111111</v>
+        <v>46.88888888888889</v>
       </c>
       <c r="D3">
-        <v>-0.07221006564551413</v>
+        <v>-0.07658643326039394</v>
       </c>
       <c r="E3">
-        <v>0.2134831460674156</v>
+        <v>0.1910112359550562</v>
       </c>
       <c r="F3">
-        <v>0.4230970861543641</v>
+        <v>0.4238783724201226</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1.723160027008778</v>
+        <v>1.725490196078431</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -15873,22 +15873,22 @@
         <v>30</v>
       </c>
       <c r="C4">
-        <v>38</v>
+        <v>38.11111111111111</v>
       </c>
       <c r="D4">
-        <v>-0.320079522862823</v>
+        <v>-0.3180914512922465</v>
       </c>
       <c r="E4">
-        <v>-0.2000000000000001</v>
+        <v>-0.1894736842105263</v>
       </c>
       <c r="F4">
-        <v>0.38968929931421</v>
+        <v>0.3888486146797661</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4">
-        <v>1.635333333333333</v>
+        <v>1.634243837441705</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -15899,22 +15899,22 @@
         <v>31</v>
       </c>
       <c r="C5">
-        <v>69.22222222222223</v>
+        <v>69</v>
       </c>
       <c r="D5">
-        <v>0.3722466960352424</v>
+        <v>0.36784140969163</v>
       </c>
       <c r="E5">
-        <v>0.06557377049180335</v>
+        <v>0.05464480874316924</v>
       </c>
       <c r="F5">
-        <v>0.7894911189938829</v>
+        <v>0.7890870428085769</v>
       </c>
       <c r="G5">
         <v>5</v>
       </c>
       <c r="H5">
-        <v>1.304804804804805</v>
+        <v>1.306766917293233</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -15951,22 +15951,22 @@
         <v>33</v>
       </c>
       <c r="C7">
-        <v>72.11111111111111</v>
+        <v>72.55555555555556</v>
       </c>
       <c r="D7">
-        <v>0.3111111111111111</v>
+        <v>0.3191919191919192</v>
       </c>
       <c r="E7">
-        <v>-0.3031674208144797</v>
+        <v>-0.2805429864253394</v>
       </c>
       <c r="F7">
-        <v>0.273667644759039</v>
+        <v>0.2705889226732273</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
       <c r="H7">
-        <v>1.224146981627297</v>
+        <v>1.223504721930745</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -15977,22 +15977,22 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>38.33333333333334</v>
+        <v>38.44444444444444</v>
       </c>
       <c r="D8">
-        <v>0.4315352697095436</v>
+        <v>0.4356846473029046</v>
       </c>
       <c r="E8">
-        <v>0.2535211267605633</v>
+        <v>0.2676056338028168</v>
       </c>
       <c r="F8">
-        <v>0.6275203823400812</v>
+        <v>0.6273275480689409</v>
       </c>
       <c r="G8">
         <v>2</v>
       </c>
       <c r="H8">
-        <v>2.054735013032146</v>
+        <v>2.052951388888889</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -29811,7 +29811,7 @@
         <v>28</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G2">
         <v>9</v>
@@ -29834,10 +29834,10 @@
         <v>28</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -29857,7 +29857,7 @@
         <v>28</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G4">
         <v>7</v>
@@ -29880,7 +29880,7 @@
         <v>28</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G5">
         <v>7</v>
@@ -29903,7 +29903,7 @@
         <v>28</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G6">
         <v>7</v>
@@ -29926,7 +29926,7 @@
         <v>28</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G7">
         <v>7</v>
@@ -29949,10 +29949,10 @@
         <v>28</v>
       </c>
       <c r="F8">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -29972,7 +29972,7 @@
         <v>28</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G9">
         <v>9</v>
@@ -29995,7 +29995,7 @@
         <v>28</v>
       </c>
       <c r="F10">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G10">
         <v>9</v>
@@ -30018,10 +30018,10 @@
         <v>28</v>
       </c>
       <c r="F11">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -30041,7 +30041,7 @@
         <v>28</v>
       </c>
       <c r="F12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G12">
         <v>8</v>
@@ -30067,7 +30067,7 @@
         <v>21</v>
       </c>
       <c r="G13">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -30087,7 +30087,7 @@
         <v>28</v>
       </c>
       <c r="F14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G14">
         <v>9</v>
@@ -30110,7 +30110,7 @@
         <v>28</v>
       </c>
       <c r="F15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G15">
         <v>10</v>
@@ -30156,7 +30156,7 @@
         <v>28</v>
       </c>
       <c r="F17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G17">
         <v>9</v>
@@ -30179,7 +30179,7 @@
         <v>28</v>
       </c>
       <c r="F18">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G18">
         <v>8</v>
@@ -30202,7 +30202,7 @@
         <v>28</v>
       </c>
       <c r="F19">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G19">
         <v>8</v>
@@ -30225,7 +30225,7 @@
         <v>28</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G20">
         <v>10</v>
@@ -30248,7 +30248,7 @@
         <v>28</v>
       </c>
       <c r="F21">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G21">
         <v>10</v>
@@ -30271,7 +30271,7 @@
         <v>28</v>
       </c>
       <c r="F22">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G22">
         <v>9</v>
@@ -30294,7 +30294,7 @@
         <v>28</v>
       </c>
       <c r="F23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G23">
         <v>8</v>
@@ -30317,10 +30317,10 @@
         <v>28</v>
       </c>
       <c r="F24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G24">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -30340,7 +30340,7 @@
         <v>28</v>
       </c>
       <c r="F25">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G25">
         <v>11</v>
@@ -30363,10 +30363,10 @@
         <v>28</v>
       </c>
       <c r="F26">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G26">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -30409,7 +30409,7 @@
         <v>28</v>
       </c>
       <c r="F28">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G28">
         <v>10</v>
@@ -30432,7 +30432,7 @@
         <v>28</v>
       </c>
       <c r="F29">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G29">
         <v>10</v>
@@ -30455,10 +30455,10 @@
         <v>28</v>
       </c>
       <c r="F30">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G30">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -30478,10 +30478,10 @@
         <v>28</v>
       </c>
       <c r="F31">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G31">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -30501,7 +30501,7 @@
         <v>28</v>
       </c>
       <c r="F32">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G32">
         <v>10</v>
@@ -30524,10 +30524,10 @@
         <v>28</v>
       </c>
       <c r="F33">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G33">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -30547,7 +30547,7 @@
         <v>28</v>
       </c>
       <c r="F34">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G34">
         <v>7</v>
@@ -30570,10 +30570,10 @@
         <v>29</v>
       </c>
       <c r="F35">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G35">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -30593,10 +30593,10 @@
         <v>29</v>
       </c>
       <c r="F36">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G36">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -30616,10 +30616,10 @@
         <v>29</v>
       </c>
       <c r="F37">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G37">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -30639,10 +30639,10 @@
         <v>29</v>
       </c>
       <c r="F38">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="G38">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -30662,10 +30662,10 @@
         <v>29</v>
       </c>
       <c r="F39">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="G39">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -30685,10 +30685,10 @@
         <v>29</v>
       </c>
       <c r="F40">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="G40">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -30708,10 +30708,10 @@
         <v>29</v>
       </c>
       <c r="F41">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="G41">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -30731,10 +30731,10 @@
         <v>29</v>
       </c>
       <c r="F42">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="G42">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -30754,10 +30754,10 @@
         <v>29</v>
       </c>
       <c r="F43">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="G43">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -30777,10 +30777,10 @@
         <v>29</v>
       </c>
       <c r="F44">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="G44">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -30800,10 +30800,10 @@
         <v>29</v>
       </c>
       <c r="F45">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G45">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -30823,10 +30823,10 @@
         <v>29</v>
       </c>
       <c r="F46">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G46">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -30846,10 +30846,10 @@
         <v>29</v>
       </c>
       <c r="F47">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G47">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -30869,10 +30869,10 @@
         <v>29</v>
       </c>
       <c r="F48">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G48">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -30892,10 +30892,10 @@
         <v>29</v>
       </c>
       <c r="F49">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G49">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -30915,10 +30915,10 @@
         <v>29</v>
       </c>
       <c r="F50">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G50">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -30938,10 +30938,10 @@
         <v>29</v>
       </c>
       <c r="F51">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G51">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -30961,10 +30961,10 @@
         <v>29</v>
       </c>
       <c r="F52">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="G52">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -30984,10 +30984,10 @@
         <v>29</v>
       </c>
       <c r="F53">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="G53">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -31007,10 +31007,10 @@
         <v>29</v>
       </c>
       <c r="F54">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="G54">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -31030,10 +31030,10 @@
         <v>29</v>
       </c>
       <c r="F55">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G55">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -31053,10 +31053,10 @@
         <v>29</v>
       </c>
       <c r="F56">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G56">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -31076,10 +31076,10 @@
         <v>29</v>
       </c>
       <c r="F57">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G57">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -31099,10 +31099,10 @@
         <v>29</v>
       </c>
       <c r="F58">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="G58">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -31122,10 +31122,10 @@
         <v>29</v>
       </c>
       <c r="F59">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G59">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -31145,10 +31145,10 @@
         <v>29</v>
       </c>
       <c r="F60">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G60">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -31168,10 +31168,10 @@
         <v>29</v>
       </c>
       <c r="F61">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G61">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -31191,10 +31191,10 @@
         <v>29</v>
       </c>
       <c r="F62">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G62">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -31214,10 +31214,10 @@
         <v>29</v>
       </c>
       <c r="F63">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G63">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -31237,10 +31237,10 @@
         <v>29</v>
       </c>
       <c r="F64">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G64">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -31260,10 +31260,10 @@
         <v>29</v>
       </c>
       <c r="F65">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="G65">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -31283,10 +31283,10 @@
         <v>29</v>
       </c>
       <c r="F66">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="G66">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -31306,10 +31306,10 @@
         <v>29</v>
       </c>
       <c r="F67">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="G67">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -31329,10 +31329,10 @@
         <v>30</v>
       </c>
       <c r="F68">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G68">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -31375,10 +31375,10 @@
         <v>30</v>
       </c>
       <c r="F70">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G70">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -31398,10 +31398,10 @@
         <v>30</v>
       </c>
       <c r="F71">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="G71">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -31421,10 +31421,10 @@
         <v>30</v>
       </c>
       <c r="F72">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G72">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -31444,7 +31444,7 @@
         <v>30</v>
       </c>
       <c r="F73">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="G73">
         <v>14</v>
@@ -31467,7 +31467,7 @@
         <v>30</v>
       </c>
       <c r="F74">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G74">
         <v>17</v>
@@ -31490,7 +31490,7 @@
         <v>30</v>
       </c>
       <c r="F75">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="G75">
         <v>17</v>
@@ -31513,10 +31513,10 @@
         <v>30</v>
       </c>
       <c r="F76">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="G76">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -31536,10 +31536,10 @@
         <v>30</v>
       </c>
       <c r="F77">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="G77">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -31559,7 +31559,7 @@
         <v>30</v>
       </c>
       <c r="F78">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G78">
         <v>21</v>
@@ -31582,10 +31582,10 @@
         <v>30</v>
       </c>
       <c r="F79">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G79">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -31605,10 +31605,10 @@
         <v>30</v>
       </c>
       <c r="F80">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="G80">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -31628,10 +31628,10 @@
         <v>30</v>
       </c>
       <c r="F81">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="G81">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -31651,10 +31651,10 @@
         <v>30</v>
       </c>
       <c r="F82">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G82">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -31674,7 +31674,7 @@
         <v>30</v>
       </c>
       <c r="F83">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G83">
         <v>20</v>
@@ -31697,10 +31697,10 @@
         <v>30</v>
       </c>
       <c r="F84">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="G84">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -31720,7 +31720,7 @@
         <v>30</v>
       </c>
       <c r="F85">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="G85">
         <v>18</v>
@@ -31743,10 +31743,10 @@
         <v>30</v>
       </c>
       <c r="F86">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G86">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -31766,10 +31766,10 @@
         <v>30</v>
       </c>
       <c r="F87">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="G87">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -31789,10 +31789,10 @@
         <v>30</v>
       </c>
       <c r="F88">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G88">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -31812,7 +31812,7 @@
         <v>30</v>
       </c>
       <c r="F89">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G89">
         <v>25</v>
@@ -31835,10 +31835,10 @@
         <v>30</v>
       </c>
       <c r="F90">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G90">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -31858,10 +31858,10 @@
         <v>30</v>
       </c>
       <c r="F91">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G91">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -31881,10 +31881,10 @@
         <v>30</v>
       </c>
       <c r="F92">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="G92">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -31904,7 +31904,7 @@
         <v>30</v>
       </c>
       <c r="F93">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="G93">
         <v>26</v>
@@ -31927,10 +31927,10 @@
         <v>30</v>
       </c>
       <c r="F94">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="G94">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -31950,10 +31950,10 @@
         <v>30</v>
       </c>
       <c r="F95">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G95">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -31973,7 +31973,7 @@
         <v>30</v>
       </c>
       <c r="F96">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G96">
         <v>16</v>
@@ -31996,10 +31996,10 @@
         <v>30</v>
       </c>
       <c r="F97">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G97">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -32019,10 +32019,10 @@
         <v>30</v>
       </c>
       <c r="F98">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G98">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -32042,7 +32042,7 @@
         <v>30</v>
       </c>
       <c r="F99">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G99">
         <v>9</v>
@@ -32065,10 +32065,10 @@
         <v>30</v>
       </c>
       <c r="F100">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G100">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -32088,7 +32088,7 @@
         <v>31</v>
       </c>
       <c r="F101">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -32111,7 +32111,7 @@
         <v>31</v>
       </c>
       <c r="F102">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -32134,10 +32134,10 @@
         <v>31</v>
       </c>
       <c r="F103">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G103">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -32157,7 +32157,7 @@
         <v>31</v>
       </c>
       <c r="F104">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -32180,7 +32180,7 @@
         <v>31</v>
       </c>
       <c r="F105">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -32203,7 +32203,7 @@
         <v>31</v>
       </c>
       <c r="F106">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -32226,10 +32226,10 @@
         <v>31</v>
       </c>
       <c r="F107">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G107">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -32249,7 +32249,7 @@
         <v>31</v>
       </c>
       <c r="F108">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -32272,7 +32272,7 @@
         <v>31</v>
       </c>
       <c r="F109">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -32295,7 +32295,7 @@
         <v>31</v>
       </c>
       <c r="F110">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -32318,7 +32318,7 @@
         <v>31</v>
       </c>
       <c r="F111">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -32341,10 +32341,10 @@
         <v>31</v>
       </c>
       <c r="F112">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="G112">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -32364,7 +32364,7 @@
         <v>31</v>
       </c>
       <c r="F113">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -32387,10 +32387,10 @@
         <v>31</v>
       </c>
       <c r="F114">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G114">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -32410,10 +32410,10 @@
         <v>31</v>
       </c>
       <c r="F115">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G115">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -32433,10 +32433,10 @@
         <v>31</v>
       </c>
       <c r="F116">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="G116">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -32456,10 +32456,10 @@
         <v>31</v>
       </c>
       <c r="F117">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G117">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -32479,10 +32479,10 @@
         <v>31</v>
       </c>
       <c r="F118">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G118">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -32502,10 +32502,10 @@
         <v>31</v>
       </c>
       <c r="F119">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G119">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -32525,10 +32525,10 @@
         <v>31</v>
       </c>
       <c r="F120">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G120">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -32548,10 +32548,10 @@
         <v>31</v>
       </c>
       <c r="F121">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G121">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -32571,10 +32571,10 @@
         <v>31</v>
       </c>
       <c r="F122">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G122">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -32594,10 +32594,10 @@
         <v>31</v>
       </c>
       <c r="F123">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="G123">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -32617,10 +32617,10 @@
         <v>31</v>
       </c>
       <c r="F124">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="G124">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -32640,10 +32640,10 @@
         <v>31</v>
       </c>
       <c r="F125">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="G125">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -32663,10 +32663,10 @@
         <v>31</v>
       </c>
       <c r="F126">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="G126">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -32686,10 +32686,10 @@
         <v>31</v>
       </c>
       <c r="F127">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="G127">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -32709,10 +32709,10 @@
         <v>31</v>
       </c>
       <c r="F128">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="G128">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -32732,10 +32732,10 @@
         <v>31</v>
       </c>
       <c r="F129">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="G129">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -32755,10 +32755,10 @@
         <v>31</v>
       </c>
       <c r="F130">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="G130">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -32778,10 +32778,10 @@
         <v>31</v>
       </c>
       <c r="F131">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G131">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -32801,10 +32801,10 @@
         <v>31</v>
       </c>
       <c r="F132">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="G132">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -32824,10 +32824,10 @@
         <v>31</v>
       </c>
       <c r="F133">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G133">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -32847,7 +32847,7 @@
         <v>32</v>
       </c>
       <c r="F134">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -32870,7 +32870,7 @@
         <v>32</v>
       </c>
       <c r="F135">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -32893,7 +32893,7 @@
         <v>32</v>
       </c>
       <c r="F136">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -32939,7 +32939,7 @@
         <v>32</v>
       </c>
       <c r="F138">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -32962,7 +32962,7 @@
         <v>32</v>
       </c>
       <c r="F139">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G139">
         <v>0</v>
@@ -32985,7 +32985,7 @@
         <v>32</v>
       </c>
       <c r="F140">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -33008,7 +33008,7 @@
         <v>32</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -33031,7 +33031,7 @@
         <v>32</v>
       </c>
       <c r="F142">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -33054,7 +33054,7 @@
         <v>32</v>
       </c>
       <c r="F143">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -33077,7 +33077,7 @@
         <v>32</v>
       </c>
       <c r="F144">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G144">
         <v>0</v>
@@ -33100,7 +33100,7 @@
         <v>32</v>
       </c>
       <c r="F145">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G145">
         <v>0</v>
@@ -33123,7 +33123,7 @@
         <v>32</v>
       </c>
       <c r="F146">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -33146,7 +33146,7 @@
         <v>32</v>
       </c>
       <c r="F147">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -33169,7 +33169,7 @@
         <v>32</v>
       </c>
       <c r="F148">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -33192,10 +33192,10 @@
         <v>32</v>
       </c>
       <c r="F149">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G149">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -33215,7 +33215,7 @@
         <v>32</v>
       </c>
       <c r="F150">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="G150">
         <v>0</v>
@@ -33238,7 +33238,7 @@
         <v>32</v>
       </c>
       <c r="F151">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G151">
         <v>0</v>
@@ -33261,7 +33261,7 @@
         <v>32</v>
       </c>
       <c r="F152">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -33284,10 +33284,10 @@
         <v>32</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G153">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -33307,7 +33307,7 @@
         <v>32</v>
       </c>
       <c r="F154">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G154">
         <v>0</v>
@@ -33330,7 +33330,7 @@
         <v>32</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G155">
         <v>0</v>
@@ -33353,7 +33353,7 @@
         <v>32</v>
       </c>
       <c r="F156">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G156">
         <v>0</v>
@@ -33376,7 +33376,7 @@
         <v>32</v>
       </c>
       <c r="F157">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G157">
         <v>0</v>
@@ -33399,10 +33399,10 @@
         <v>32</v>
       </c>
       <c r="F158">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G158">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -33422,7 +33422,7 @@
         <v>32</v>
       </c>
       <c r="F159">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="G159">
         <v>0</v>
@@ -33445,10 +33445,10 @@
         <v>32</v>
       </c>
       <c r="F160">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G160">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -33468,7 +33468,7 @@
         <v>32</v>
       </c>
       <c r="F161">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G161">
         <v>0</v>
@@ -33491,10 +33491,10 @@
         <v>32</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G162">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -33514,7 +33514,7 @@
         <v>32</v>
       </c>
       <c r="F163">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G163">
         <v>0</v>
@@ -33537,7 +33537,7 @@
         <v>32</v>
       </c>
       <c r="F164">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G164">
         <v>0</v>
@@ -33560,10 +33560,10 @@
         <v>32</v>
       </c>
       <c r="F165">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G165">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -33583,10 +33583,10 @@
         <v>32</v>
       </c>
       <c r="F166">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G166">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -33606,10 +33606,10 @@
         <v>33</v>
       </c>
       <c r="F167">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G167">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -33629,10 +33629,10 @@
         <v>33</v>
       </c>
       <c r="F168">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="G168">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -33652,10 +33652,10 @@
         <v>33</v>
       </c>
       <c r="F169">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G169">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -33675,10 +33675,10 @@
         <v>33</v>
       </c>
       <c r="F170">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G170">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -33698,10 +33698,10 @@
         <v>33</v>
       </c>
       <c r="F171">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G171">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -33721,10 +33721,10 @@
         <v>33</v>
       </c>
       <c r="F172">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G172">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -33744,10 +33744,10 @@
         <v>33</v>
       </c>
       <c r="F173">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G173">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -33767,10 +33767,10 @@
         <v>33</v>
       </c>
       <c r="F174">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G174">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -33790,10 +33790,10 @@
         <v>33</v>
       </c>
       <c r="F175">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G175">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -33813,10 +33813,10 @@
         <v>33</v>
       </c>
       <c r="F176">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G176">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -33836,10 +33836,10 @@
         <v>33</v>
       </c>
       <c r="F177">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="G177">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -33859,10 +33859,10 @@
         <v>33</v>
       </c>
       <c r="F178">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="G178">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -33882,10 +33882,10 @@
         <v>33</v>
       </c>
       <c r="F179">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G179">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -33905,10 +33905,10 @@
         <v>33</v>
       </c>
       <c r="F180">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G180">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -33928,10 +33928,10 @@
         <v>33</v>
       </c>
       <c r="F181">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G181">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -33951,10 +33951,10 @@
         <v>33</v>
       </c>
       <c r="F182">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="G182">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -33974,10 +33974,10 @@
         <v>33</v>
       </c>
       <c r="F183">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="G183">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -33997,10 +33997,10 @@
         <v>33</v>
       </c>
       <c r="F184">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G184">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -34020,10 +34020,10 @@
         <v>33</v>
       </c>
       <c r="F185">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="G185">
-        <v>44</v>
+        <v>4</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -34043,10 +34043,10 @@
         <v>33</v>
       </c>
       <c r="F186">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G186">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -34066,10 +34066,10 @@
         <v>33</v>
       </c>
       <c r="F187">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G187">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -34089,10 +34089,10 @@
         <v>33</v>
       </c>
       <c r="F188">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G188">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -34112,10 +34112,10 @@
         <v>33</v>
       </c>
       <c r="F189">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="G189">
-        <v>33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -34135,10 +34135,10 @@
         <v>33</v>
       </c>
       <c r="F190">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="G190">
-        <v>39</v>
+        <v>4</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -34158,10 +34158,10 @@
         <v>33</v>
       </c>
       <c r="F191">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="G191">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -34181,10 +34181,10 @@
         <v>33</v>
       </c>
       <c r="F192">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="G192">
-        <v>53</v>
+        <v>6</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -34204,10 +34204,10 @@
         <v>33</v>
       </c>
       <c r="F193">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="G193">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -34227,10 +34227,10 @@
         <v>33</v>
       </c>
       <c r="F194">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="G194">
-        <v>36</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -34250,10 +34250,10 @@
         <v>33</v>
       </c>
       <c r="F195">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="G195">
-        <v>41</v>
+        <v>4</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -34273,10 +34273,10 @@
         <v>33</v>
       </c>
       <c r="F196">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="G196">
-        <v>41</v>
+        <v>4</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -34296,10 +34296,10 @@
         <v>33</v>
       </c>
       <c r="F197">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="G197">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -34319,10 +34319,10 @@
         <v>33</v>
       </c>
       <c r="F198">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="G198">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -34342,10 +34342,10 @@
         <v>33</v>
       </c>
       <c r="F199">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="G199">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -34365,10 +34365,10 @@
         <v>34</v>
       </c>
       <c r="F200">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G200">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -34388,10 +34388,10 @@
         <v>34</v>
       </c>
       <c r="F201">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G201">
-        <v>60</v>
+        <v>13</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -34411,10 +34411,10 @@
         <v>34</v>
       </c>
       <c r="F202">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G202">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -34434,10 +34434,10 @@
         <v>34</v>
       </c>
       <c r="F203">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G203">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -34457,10 +34457,10 @@
         <v>34</v>
       </c>
       <c r="F204">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G204">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -34480,10 +34480,10 @@
         <v>34</v>
       </c>
       <c r="F205">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G205">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -34503,10 +34503,10 @@
         <v>34</v>
       </c>
       <c r="F206">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="G206">
-        <v>64</v>
+        <v>13</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -34526,10 +34526,10 @@
         <v>34</v>
       </c>
       <c r="F207">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G207">
-        <v>76</v>
+        <v>16</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -34549,10 +34549,10 @@
         <v>34</v>
       </c>
       <c r="F208">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G208">
-        <v>59</v>
+        <v>12</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -34572,7 +34572,7 @@
         <v>34</v>
       </c>
       <c r="F209">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G209">
         <v>0</v>
@@ -34595,10 +34595,10 @@
         <v>34</v>
       </c>
       <c r="F210">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G210">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -34618,10 +34618,10 @@
         <v>34</v>
       </c>
       <c r="F211">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G211">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -34641,10 +34641,10 @@
         <v>34</v>
       </c>
       <c r="F212">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G212">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -34664,10 +34664,10 @@
         <v>34</v>
       </c>
       <c r="F213">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G213">
-        <v>55</v>
+        <v>12</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -34687,10 +34687,10 @@
         <v>34</v>
       </c>
       <c r="F214">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="G214">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -34710,10 +34710,10 @@
         <v>34</v>
       </c>
       <c r="F215">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G215">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -34733,10 +34733,10 @@
         <v>34</v>
       </c>
       <c r="F216">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="G216">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -34756,10 +34756,10 @@
         <v>34</v>
       </c>
       <c r="F217">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="G217">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -34779,10 +34779,10 @@
         <v>34</v>
       </c>
       <c r="F218">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G218">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -34802,10 +34802,10 @@
         <v>34</v>
       </c>
       <c r="F219">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="G219">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -34825,10 +34825,10 @@
         <v>34</v>
       </c>
       <c r="F220">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G220">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -34848,10 +34848,10 @@
         <v>34</v>
       </c>
       <c r="F221">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G221">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -34871,10 +34871,10 @@
         <v>34</v>
       </c>
       <c r="F222">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G222">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -34894,10 +34894,10 @@
         <v>34</v>
       </c>
       <c r="F223">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="G223">
-        <v>55</v>
+        <v>11</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -34917,10 +34917,10 @@
         <v>34</v>
       </c>
       <c r="F224">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="G224">
-        <v>51</v>
+        <v>11</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -34940,10 +34940,10 @@
         <v>34</v>
       </c>
       <c r="F225">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="G225">
-        <v>100</v>
+        <v>21</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -34963,10 +34963,10 @@
         <v>34</v>
       </c>
       <c r="F226">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G226">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -34986,10 +34986,10 @@
         <v>34</v>
       </c>
       <c r="F227">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G227">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -35009,10 +35009,10 @@
         <v>34</v>
       </c>
       <c r="F228">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="G228">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -35032,7 +35032,7 @@
         <v>34</v>
       </c>
       <c r="F229">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G229">
         <v>0</v>
@@ -35055,10 +35055,10 @@
         <v>34</v>
       </c>
       <c r="F230">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G230">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -35078,10 +35078,10 @@
         <v>34</v>
       </c>
       <c r="F231">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="G231">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -35101,10 +35101,10 @@
         <v>34</v>
       </c>
       <c r="F232">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G232">
-        <v>43</v>
+        <v>9</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -35124,10 +35124,10 @@
         <v>35</v>
       </c>
       <c r="F233">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G233">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -35147,10 +35147,10 @@
         <v>35</v>
       </c>
       <c r="F234">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G234">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -35170,10 +35170,10 @@
         <v>35</v>
       </c>
       <c r="F235">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G235">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -35193,7 +35193,7 @@
         <v>35</v>
       </c>
       <c r="F236">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G236">
         <v>10</v>
@@ -35216,7 +35216,7 @@
         <v>35</v>
       </c>
       <c r="F237">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G237">
         <v>9</v>
@@ -35239,7 +35239,7 @@
         <v>35</v>
       </c>
       <c r="F238">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G238">
         <v>9</v>
@@ -35262,10 +35262,10 @@
         <v>35</v>
       </c>
       <c r="F239">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G239">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -35285,10 +35285,10 @@
         <v>35</v>
       </c>
       <c r="F240">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G240">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -35308,7 +35308,7 @@
         <v>35</v>
       </c>
       <c r="F241">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G241">
         <v>11</v>
@@ -35331,10 +35331,10 @@
         <v>35</v>
       </c>
       <c r="F242">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G242">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -35354,10 +35354,10 @@
         <v>35</v>
       </c>
       <c r="F243">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G243">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -35377,10 +35377,10 @@
         <v>35</v>
       </c>
       <c r="F244">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G244">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -35400,10 +35400,10 @@
         <v>35</v>
       </c>
       <c r="F245">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G245">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -35423,10 +35423,10 @@
         <v>35</v>
       </c>
       <c r="F246">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G246">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -35446,10 +35446,10 @@
         <v>35</v>
       </c>
       <c r="F247">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G247">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -35469,10 +35469,10 @@
         <v>35</v>
       </c>
       <c r="F248">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G248">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -35492,7 +35492,7 @@
         <v>35</v>
       </c>
       <c r="F249">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G249">
         <v>10</v>
@@ -35515,10 +35515,10 @@
         <v>35</v>
       </c>
       <c r="F250">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G250">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -35538,7 +35538,7 @@
         <v>35</v>
       </c>
       <c r="F251">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G251">
         <v>12</v>
@@ -35561,7 +35561,7 @@
         <v>35</v>
       </c>
       <c r="F252">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G252">
         <v>13</v>
@@ -35584,10 +35584,10 @@
         <v>35</v>
       </c>
       <c r="F253">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G253">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -35607,7 +35607,7 @@
         <v>35</v>
       </c>
       <c r="F254">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G254">
         <v>11</v>
@@ -35630,10 +35630,10 @@
         <v>35</v>
       </c>
       <c r="F255">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G255">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -35653,7 +35653,7 @@
         <v>35</v>
       </c>
       <c r="F256">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G256">
         <v>14</v>
@@ -35676,10 +35676,10 @@
         <v>35</v>
       </c>
       <c r="F257">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G257">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -35699,10 +35699,10 @@
         <v>35</v>
       </c>
       <c r="F258">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G258">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -35722,10 +35722,10 @@
         <v>35</v>
       </c>
       <c r="F259">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G259">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -35745,10 +35745,10 @@
         <v>35</v>
       </c>
       <c r="F260">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G260">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -35768,10 +35768,10 @@
         <v>35</v>
       </c>
       <c r="F261">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G261">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -35791,10 +35791,10 @@
         <v>35</v>
       </c>
       <c r="F262">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G262">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -35814,7 +35814,7 @@
         <v>35</v>
       </c>
       <c r="F263">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G263">
         <v>12</v>
@@ -35837,7 +35837,7 @@
         <v>35</v>
       </c>
       <c r="F264">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G264">
         <v>11</v>
@@ -35860,7 +35860,7 @@
         <v>35</v>
       </c>
       <c r="F265">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G265">
         <v>9</v>

--- a/downloads/dados.xlsx
+++ b/downloads/dados.xlsx
@@ -248,8 +248,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -265,7 +273,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -273,12 +281,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -578,39 +604,39 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>44927</v>
       </c>
       <c r="B2">
@@ -629,7 +655,7 @@
         <v>27</v>
       </c>
       <c r="G2">
-        <v>67.2</v>
+        <v>66.3</v>
       </c>
       <c r="H2" t="s">
         <v>32</v>
@@ -642,7 +668,7 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>44958</v>
       </c>
       <c r="B3">
@@ -661,7 +687,7 @@
         <v>27</v>
       </c>
       <c r="G3">
-        <v>43.1</v>
+        <v>40.7</v>
       </c>
       <c r="H3" t="s">
         <v>32</v>
@@ -674,7 +700,7 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>44986</v>
       </c>
       <c r="B4">
@@ -693,7 +719,7 @@
         <v>27</v>
       </c>
       <c r="G4">
-        <v>40.1</v>
+        <v>39.6</v>
       </c>
       <c r="H4" t="s">
         <v>32</v>
@@ -706,7 +732,7 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>45017</v>
       </c>
       <c r="B5">
@@ -725,7 +751,7 @@
         <v>27</v>
       </c>
       <c r="G5">
-        <v>44.1</v>
+        <v>43.9</v>
       </c>
       <c r="H5" t="s">
         <v>32</v>
@@ -738,7 +764,7 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>45047</v>
       </c>
       <c r="B6">
@@ -770,7 +796,7 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>45078</v>
       </c>
       <c r="B7">
@@ -789,7 +815,7 @@
         <v>27</v>
       </c>
       <c r="G7">
-        <v>59.4</v>
+        <v>57.9</v>
       </c>
       <c r="H7" t="s">
         <v>32</v>
@@ -802,7 +828,7 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>45108</v>
       </c>
       <c r="B8">
@@ -821,7 +847,7 @@
         <v>27</v>
       </c>
       <c r="G8">
-        <v>69.7</v>
+        <v>70</v>
       </c>
       <c r="H8" t="s">
         <v>32</v>
@@ -834,7 +860,7 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>45139</v>
       </c>
       <c r="B9">
@@ -853,7 +879,7 @@
         <v>27</v>
       </c>
       <c r="G9">
-        <v>46.5</v>
+        <v>45.2</v>
       </c>
       <c r="H9" t="s">
         <v>32</v>
@@ -866,7 +892,7 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>45170</v>
       </c>
       <c r="B10">
@@ -885,7 +911,7 @@
         <v>27</v>
       </c>
       <c r="G10">
-        <v>41.5</v>
+        <v>40.4</v>
       </c>
       <c r="H10" t="s">
         <v>32</v>
@@ -898,7 +924,7 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <v>45200</v>
       </c>
       <c r="B11">
@@ -917,7 +943,7 @@
         <v>27</v>
       </c>
       <c r="G11">
-        <v>51.1</v>
+        <v>49.4</v>
       </c>
       <c r="H11" t="s">
         <v>32</v>
@@ -930,7 +956,7 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <v>45231</v>
       </c>
       <c r="B12">
@@ -949,7 +975,7 @@
         <v>27</v>
       </c>
       <c r="G12">
-        <v>45.7</v>
+        <v>45.4</v>
       </c>
       <c r="H12" t="s">
         <v>32</v>
@@ -962,7 +988,7 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <v>45261</v>
       </c>
       <c r="B13">
@@ -981,7 +1007,7 @@
         <v>27</v>
       </c>
       <c r="G13">
-        <v>57.8</v>
+        <v>57.4</v>
       </c>
       <c r="H13" t="s">
         <v>32</v>
@@ -994,7 +1020,7 @@
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="1">
+      <c r="A14" s="2">
         <v>45292</v>
       </c>
       <c r="B14">
@@ -1013,7 +1039,7 @@
         <v>27</v>
       </c>
       <c r="G14">
-        <v>45.4</v>
+        <v>46.8</v>
       </c>
       <c r="H14" t="s">
         <v>32</v>
@@ -1026,7 +1052,7 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="1">
+      <c r="A15" s="2">
         <v>45323</v>
       </c>
       <c r="B15">
@@ -1045,7 +1071,7 @@
         <v>27</v>
       </c>
       <c r="G15">
-        <v>37.3</v>
+        <v>36.3</v>
       </c>
       <c r="H15" t="s">
         <v>32</v>
@@ -1058,7 +1084,7 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="1">
+      <c r="A16" s="2">
         <v>45352</v>
       </c>
       <c r="B16">
@@ -1077,7 +1103,7 @@
         <v>27</v>
       </c>
       <c r="G16">
-        <v>45</v>
+        <v>44.1</v>
       </c>
       <c r="H16" t="s">
         <v>32</v>
@@ -1090,7 +1116,7 @@
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="1">
+      <c r="A17" s="2">
         <v>45383</v>
       </c>
       <c r="B17">
@@ -1109,7 +1135,7 @@
         <v>27</v>
       </c>
       <c r="G17">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="H17" t="s">
         <v>32</v>
@@ -1122,7 +1148,7 @@
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="1">
+      <c r="A18" s="2">
         <v>45413</v>
       </c>
       <c r="B18">
@@ -1141,7 +1167,7 @@
         <v>27</v>
       </c>
       <c r="G18">
-        <v>5.3</v>
+        <v>6.9</v>
       </c>
       <c r="H18" t="s">
         <v>32</v>
@@ -1154,7 +1180,7 @@
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="1">
+      <c r="A19" s="2">
         <v>45444</v>
       </c>
       <c r="B19">
@@ -1173,7 +1199,7 @@
         <v>27</v>
       </c>
       <c r="G19">
-        <v>21.7</v>
+        <v>23.3</v>
       </c>
       <c r="H19" t="s">
         <v>32</v>
@@ -1186,7 +1212,7 @@
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="1">
+      <c r="A20" s="2">
         <v>45474</v>
       </c>
       <c r="B20">
@@ -1218,7 +1244,7 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="1">
+      <c r="A21" s="2">
         <v>45505</v>
       </c>
       <c r="B21">
@@ -1237,7 +1263,7 @@
         <v>27</v>
       </c>
       <c r="G21">
-        <v>31.1</v>
+        <v>25.8</v>
       </c>
       <c r="H21" t="s">
         <v>32</v>
@@ -1250,7 +1276,7 @@
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="1">
+      <c r="A22" s="2">
         <v>45536</v>
       </c>
       <c r="B22">
@@ -1269,7 +1295,7 @@
         <v>27</v>
       </c>
       <c r="G22">
-        <v>42.4</v>
+        <v>44.5</v>
       </c>
       <c r="H22" t="s">
         <v>32</v>
@@ -1282,7 +1308,7 @@
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="1">
+      <c r="A23" s="2">
         <v>45566</v>
       </c>
       <c r="B23">
@@ -1301,7 +1327,7 @@
         <v>27</v>
       </c>
       <c r="G23">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="H23" t="s">
         <v>32</v>
@@ -1314,7 +1340,7 @@
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="1">
+      <c r="A24" s="2">
         <v>45597</v>
       </c>
       <c r="B24">
@@ -1333,7 +1359,7 @@
         <v>27</v>
       </c>
       <c r="G24">
-        <v>28.6</v>
+        <v>27.1</v>
       </c>
       <c r="H24" t="s">
         <v>32</v>
@@ -1346,7 +1372,7 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="1">
+      <c r="A25" s="2">
         <v>45627</v>
       </c>
       <c r="B25">
@@ -1365,7 +1391,7 @@
         <v>27</v>
       </c>
       <c r="G25">
-        <v>36.1</v>
+        <v>38.3</v>
       </c>
       <c r="H25" t="s">
         <v>32</v>
@@ -1378,7 +1404,7 @@
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="1">
+      <c r="A26" s="2">
         <v>45658</v>
       </c>
       <c r="B26">
@@ -1397,7 +1423,7 @@
         <v>27</v>
       </c>
       <c r="G26">
-        <v>28.3</v>
+        <v>28.8</v>
       </c>
       <c r="H26" t="s">
         <v>32</v>
@@ -1410,7 +1436,7 @@
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="1">
+      <c r="A27" s="2">
         <v>45689</v>
       </c>
       <c r="B27">
@@ -1429,7 +1455,7 @@
         <v>27</v>
       </c>
       <c r="G27">
-        <v>17.6</v>
+        <v>19.1</v>
       </c>
       <c r="H27" t="s">
         <v>32</v>
@@ -1442,7 +1468,7 @@
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="1">
+      <c r="A28" s="2">
         <v>45717</v>
       </c>
       <c r="B28">
@@ -1461,7 +1487,7 @@
         <v>27</v>
       </c>
       <c r="G28">
-        <v>28</v>
+        <v>30.6</v>
       </c>
       <c r="H28" t="s">
         <v>32</v>
@@ -1474,7 +1500,7 @@
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="1">
+      <c r="A29" s="2">
         <v>45748</v>
       </c>
       <c r="B29">
@@ -1493,7 +1519,7 @@
         <v>27</v>
       </c>
       <c r="G29">
-        <v>37.8</v>
+        <v>35.7</v>
       </c>
       <c r="H29" t="s">
         <v>32</v>
@@ -1506,7 +1532,7 @@
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="1">
+      <c r="A30" s="2">
         <v>45778</v>
       </c>
       <c r="B30">
@@ -1525,7 +1551,7 @@
         <v>27</v>
       </c>
       <c r="G30">
-        <v>50.4</v>
+        <v>47.1</v>
       </c>
       <c r="H30" t="s">
         <v>32</v>
@@ -1538,7 +1564,7 @@
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="1">
+      <c r="A31" s="2">
         <v>45809</v>
       </c>
       <c r="B31">
@@ -1557,7 +1583,7 @@
         <v>27</v>
       </c>
       <c r="G31">
-        <v>56.9</v>
+        <v>58.5</v>
       </c>
       <c r="H31" t="s">
         <v>32</v>
@@ -1570,7 +1596,7 @@
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="1">
+      <c r="A32" s="2">
         <v>45839</v>
       </c>
       <c r="B32">
@@ -1589,7 +1615,7 @@
         <v>27</v>
       </c>
       <c r="G32">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H32" t="s">
         <v>32</v>
@@ -1602,7 +1628,7 @@
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="1">
+      <c r="A33" s="2">
         <v>45870</v>
       </c>
       <c r="B33">
@@ -1621,7 +1647,7 @@
         <v>27</v>
       </c>
       <c r="G33">
-        <v>52.9</v>
+        <v>51.4</v>
       </c>
       <c r="H33" t="s">
         <v>32</v>
@@ -1634,7 +1660,7 @@
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="1">
+      <c r="A34" s="2">
         <v>45901</v>
       </c>
       <c r="B34">
@@ -1653,7 +1679,7 @@
         <v>27</v>
       </c>
       <c r="G34">
-        <v>46.8</v>
+        <v>46.5</v>
       </c>
       <c r="H34" t="s">
         <v>32</v>
@@ -1666,7 +1692,7 @@
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="1">
+      <c r="A35" s="2">
         <v>45931</v>
       </c>
       <c r="B35">
@@ -1685,7 +1711,7 @@
         <v>27</v>
       </c>
       <c r="G35">
-        <v>54.3</v>
+        <v>53.5</v>
       </c>
       <c r="H35" t="s">
         <v>32</v>
@@ -1698,7 +1724,7 @@
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="1">
+      <c r="A36" s="2">
         <v>45962</v>
       </c>
       <c r="B36">
@@ -1717,7 +1743,7 @@
         <v>27</v>
       </c>
       <c r="G36">
-        <v>58.3</v>
+        <v>58.7</v>
       </c>
       <c r="H36" t="s">
         <v>32</v>
@@ -1730,7 +1756,7 @@
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="1">
+      <c r="A37" s="2">
         <v>45992</v>
       </c>
       <c r="B37">
@@ -1749,7 +1775,7 @@
         <v>27</v>
       </c>
       <c r="G37">
-        <v>81.5</v>
+        <v>81.2</v>
       </c>
       <c r="H37" t="s">
         <v>32</v>
@@ -1762,7 +1788,7 @@
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="1">
+      <c r="A38" s="2">
         <v>46023</v>
       </c>
       <c r="B38">
@@ -1781,7 +1807,7 @@
         <v>27</v>
       </c>
       <c r="G38">
-        <v>63.3</v>
+        <v>63.4</v>
       </c>
       <c r="H38" t="s">
         <v>32</v>
@@ -1794,7 +1820,7 @@
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="1">
+      <c r="A39" s="2">
         <v>46054</v>
       </c>
       <c r="B39">
@@ -1813,7 +1839,7 @@
         <v>27</v>
       </c>
       <c r="G39">
-        <v>50.1</v>
+        <v>48.5</v>
       </c>
       <c r="H39" t="s">
         <v>32</v>
@@ -1826,7 +1852,7 @@
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="1">
+      <c r="A40" s="2">
         <v>46082</v>
       </c>
       <c r="B40">
@@ -1845,7 +1871,7 @@
         <v>27</v>
       </c>
       <c r="G40">
-        <v>55.1</v>
+        <v>58.9</v>
       </c>
       <c r="H40" t="s">
         <v>32</v>
@@ -1858,7 +1884,7 @@
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="1">
+      <c r="A41" s="2">
         <v>46113</v>
       </c>
       <c r="B41">
@@ -1877,7 +1903,7 @@
         <v>27</v>
       </c>
       <c r="G41">
-        <v>64.09999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="H41" t="s">
         <v>32</v>
@@ -1890,7 +1916,7 @@
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="1">
+      <c r="A42" s="2">
         <v>46143</v>
       </c>
       <c r="B42">
@@ -1909,7 +1935,7 @@
         <v>27</v>
       </c>
       <c r="G42">
-        <v>72.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H42" t="s">
         <v>32</v>
@@ -1922,7 +1948,7 @@
       </c>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="1">
+      <c r="A43" s="2">
         <v>46174</v>
       </c>
       <c r="B43">
@@ -1941,7 +1967,7 @@
         <v>27</v>
       </c>
       <c r="G43">
-        <v>66.09999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="H43" t="s">
         <v>32</v>
@@ -1954,7 +1980,7 @@
       </c>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="1">
+      <c r="A44" s="2">
         <v>46204</v>
       </c>
       <c r="B44">
@@ -1986,7 +2012,7 @@
       </c>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="1">
+      <c r="A45" s="2">
         <v>46235</v>
       </c>
       <c r="B45">
@@ -2005,7 +2031,7 @@
         <v>27</v>
       </c>
       <c r="G45">
-        <v>64.09999999999999</v>
+        <v>60.1</v>
       </c>
       <c r="H45" t="s">
         <v>32</v>
@@ -2018,7 +2044,7 @@
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="1">
+      <c r="A46" s="2">
         <v>46266</v>
       </c>
       <c r="B46">
@@ -2037,7 +2063,7 @@
         <v>27</v>
       </c>
       <c r="G46">
-        <v>55.7</v>
+        <v>58.4</v>
       </c>
       <c r="H46" t="s">
         <v>32</v>
@@ -2050,7 +2076,7 @@
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="1">
+      <c r="A47" s="2">
         <v>44927</v>
       </c>
       <c r="B47">
@@ -2082,7 +2108,7 @@
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="1">
+      <c r="A48" s="2">
         <v>44958</v>
       </c>
       <c r="B48">
@@ -2101,7 +2127,7 @@
         <v>28</v>
       </c>
       <c r="G48">
-        <v>51.4</v>
+        <v>50.7</v>
       </c>
       <c r="H48" t="s">
         <v>33</v>
@@ -2114,7 +2140,7 @@
       </c>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="1">
+      <c r="A49" s="2">
         <v>44986</v>
       </c>
       <c r="B49">
@@ -2133,7 +2159,7 @@
         <v>28</v>
       </c>
       <c r="G49">
-        <v>53.8</v>
+        <v>53.4</v>
       </c>
       <c r="H49" t="s">
         <v>33</v>
@@ -2146,7 +2172,7 @@
       </c>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="1">
+      <c r="A50" s="2">
         <v>45017</v>
       </c>
       <c r="B50">
@@ -2165,7 +2191,7 @@
         <v>28</v>
       </c>
       <c r="G50">
-        <v>73.5</v>
+        <v>72.2</v>
       </c>
       <c r="H50" t="s">
         <v>33</v>
@@ -2178,7 +2204,7 @@
       </c>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="1">
+      <c r="A51" s="2">
         <v>45047</v>
       </c>
       <c r="B51">
@@ -2197,7 +2223,7 @@
         <v>28</v>
       </c>
       <c r="G51">
-        <v>77.3</v>
+        <v>75.5</v>
       </c>
       <c r="H51" t="s">
         <v>33</v>
@@ -2210,7 +2236,7 @@
       </c>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="1">
+      <c r="A52" s="2">
         <v>45078</v>
       </c>
       <c r="B52">
@@ -2229,7 +2255,7 @@
         <v>28</v>
       </c>
       <c r="G52">
-        <v>81.5</v>
+        <v>79.7</v>
       </c>
       <c r="H52" t="s">
         <v>33</v>
@@ -2242,7 +2268,7 @@
       </c>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="1">
+      <c r="A53" s="2">
         <v>45108</v>
       </c>
       <c r="B53">
@@ -2274,7 +2300,7 @@
       </c>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="1">
+      <c r="A54" s="2">
         <v>45139</v>
       </c>
       <c r="B54">
@@ -2293,7 +2319,7 @@
         <v>28</v>
       </c>
       <c r="G54">
-        <v>66.3</v>
+        <v>66.7</v>
       </c>
       <c r="H54" t="s">
         <v>33</v>
@@ -2306,7 +2332,7 @@
       </c>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="1">
+      <c r="A55" s="2">
         <v>45170</v>
       </c>
       <c r="B55">
@@ -2325,7 +2351,7 @@
         <v>28</v>
       </c>
       <c r="G55">
-        <v>56.6</v>
+        <v>54.6</v>
       </c>
       <c r="H55" t="s">
         <v>33</v>
@@ -2338,7 +2364,7 @@
       </c>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="1">
+      <c r="A56" s="2">
         <v>45200</v>
       </c>
       <c r="B56">
@@ -2357,7 +2383,7 @@
         <v>28</v>
       </c>
       <c r="G56">
-        <v>56.4</v>
+        <v>55.8</v>
       </c>
       <c r="H56" t="s">
         <v>33</v>
@@ -2370,7 +2396,7 @@
       </c>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="1">
+      <c r="A57" s="2">
         <v>45231</v>
       </c>
       <c r="B57">
@@ -2389,7 +2415,7 @@
         <v>28</v>
       </c>
       <c r="G57">
-        <v>56.9</v>
+        <v>56.5</v>
       </c>
       <c r="H57" t="s">
         <v>33</v>
@@ -2402,7 +2428,7 @@
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="1">
+      <c r="A58" s="2">
         <v>45261</v>
       </c>
       <c r="B58">
@@ -2421,7 +2447,7 @@
         <v>28</v>
       </c>
       <c r="G58">
-        <v>70.3</v>
+        <v>70.5</v>
       </c>
       <c r="H58" t="s">
         <v>33</v>
@@ -2434,7 +2460,7 @@
       </c>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="1">
+      <c r="A59" s="2">
         <v>45292</v>
       </c>
       <c r="B59">
@@ -2453,7 +2479,7 @@
         <v>28</v>
       </c>
       <c r="G59">
-        <v>55</v>
+        <v>51.6</v>
       </c>
       <c r="H59" t="s">
         <v>33</v>
@@ -2466,7 +2492,7 @@
       </c>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="1">
+      <c r="A60" s="2">
         <v>45323</v>
       </c>
       <c r="B60">
@@ -2485,7 +2511,7 @@
         <v>28</v>
       </c>
       <c r="G60">
-        <v>41.7</v>
+        <v>40.8</v>
       </c>
       <c r="H60" t="s">
         <v>33</v>
@@ -2498,7 +2524,7 @@
       </c>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="1">
+      <c r="A61" s="2">
         <v>45352</v>
       </c>
       <c r="B61">
@@ -2517,7 +2543,7 @@
         <v>28</v>
       </c>
       <c r="G61">
-        <v>54</v>
+        <v>54.6</v>
       </c>
       <c r="H61" t="s">
         <v>33</v>
@@ -2530,7 +2556,7 @@
       </c>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="1">
+      <c r="A62" s="2">
         <v>45383</v>
       </c>
       <c r="B62">
@@ -2549,7 +2575,7 @@
         <v>28</v>
       </c>
       <c r="G62">
-        <v>47.1</v>
+        <v>48</v>
       </c>
       <c r="H62" t="s">
         <v>33</v>
@@ -2562,7 +2588,7 @@
       </c>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="1">
+      <c r="A63" s="2">
         <v>45413</v>
       </c>
       <c r="B63">
@@ -2581,7 +2607,7 @@
         <v>28</v>
       </c>
       <c r="G63">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="H63" t="s">
         <v>33</v>
@@ -2594,7 +2620,7 @@
       </c>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="1">
+      <c r="A64" s="2">
         <v>45444</v>
       </c>
       <c r="B64">
@@ -2613,7 +2639,7 @@
         <v>28</v>
       </c>
       <c r="G64">
-        <v>29</v>
+        <v>28.3</v>
       </c>
       <c r="H64" t="s">
         <v>33</v>
@@ -2626,7 +2652,7 @@
       </c>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="1">
+      <c r="A65" s="2">
         <v>45474</v>
       </c>
       <c r="B65">
@@ -2645,7 +2671,7 @@
         <v>28</v>
       </c>
       <c r="G65">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="H65" t="s">
         <v>33</v>
@@ -2658,7 +2684,7 @@
       </c>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="1">
+      <c r="A66" s="2">
         <v>45505</v>
       </c>
       <c r="B66">
@@ -2677,7 +2703,7 @@
         <v>28</v>
       </c>
       <c r="G66">
-        <v>32.5</v>
+        <v>30.2</v>
       </c>
       <c r="H66" t="s">
         <v>33</v>
@@ -2690,7 +2716,7 @@
       </c>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="1">
+      <c r="A67" s="2">
         <v>45536</v>
       </c>
       <c r="B67">
@@ -2709,7 +2735,7 @@
         <v>28</v>
       </c>
       <c r="G67">
-        <v>35</v>
+        <v>34.1</v>
       </c>
       <c r="H67" t="s">
         <v>33</v>
@@ -2722,7 +2748,7 @@
       </c>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="1">
+      <c r="A68" s="2">
         <v>45566</v>
       </c>
       <c r="B68">
@@ -2741,7 +2767,7 @@
         <v>28</v>
       </c>
       <c r="G68">
-        <v>45.9</v>
+        <v>45.6</v>
       </c>
       <c r="H68" t="s">
         <v>33</v>
@@ -2754,7 +2780,7 @@
       </c>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="1">
+      <c r="A69" s="2">
         <v>45597</v>
       </c>
       <c r="B69">
@@ -2773,7 +2799,7 @@
         <v>28</v>
       </c>
       <c r="G69">
-        <v>48.7</v>
+        <v>46.2</v>
       </c>
       <c r="H69" t="s">
         <v>33</v>
@@ -2786,7 +2812,7 @@
       </c>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="1">
+      <c r="A70" s="2">
         <v>45627</v>
       </c>
       <c r="B70">
@@ -2805,7 +2831,7 @@
         <v>28</v>
       </c>
       <c r="G70">
-        <v>59.4</v>
+        <v>58.9</v>
       </c>
       <c r="H70" t="s">
         <v>33</v>
@@ -2818,7 +2844,7 @@
       </c>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="1">
+      <c r="A71" s="2">
         <v>45658</v>
       </c>
       <c r="B71">
@@ -2837,7 +2863,7 @@
         <v>28</v>
       </c>
       <c r="G71">
-        <v>44.1</v>
+        <v>43.2</v>
       </c>
       <c r="H71" t="s">
         <v>33</v>
@@ -2850,7 +2876,7 @@
       </c>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="1">
+      <c r="A72" s="2">
         <v>45689</v>
       </c>
       <c r="B72">
@@ -2869,7 +2895,7 @@
         <v>28</v>
       </c>
       <c r="G72">
-        <v>28</v>
+        <v>28.4</v>
       </c>
       <c r="H72" t="s">
         <v>33</v>
@@ -2882,7 +2908,7 @@
       </c>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="1">
+      <c r="A73" s="2">
         <v>45717</v>
       </c>
       <c r="B73">
@@ -2914,7 +2940,7 @@
       </c>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="1">
+      <c r="A74" s="2">
         <v>45748</v>
       </c>
       <c r="B74">
@@ -2933,7 +2959,7 @@
         <v>28</v>
       </c>
       <c r="G74">
-        <v>51.4</v>
+        <v>50.7</v>
       </c>
       <c r="H74" t="s">
         <v>33</v>
@@ -2946,7 +2972,7 @@
       </c>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="1">
+      <c r="A75" s="2">
         <v>45778</v>
       </c>
       <c r="B75">
@@ -2965,7 +2991,7 @@
         <v>28</v>
       </c>
       <c r="G75">
-        <v>51.1</v>
+        <v>51.9</v>
       </c>
       <c r="H75" t="s">
         <v>33</v>
@@ -2978,7 +3004,7 @@
       </c>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="1">
+      <c r="A76" s="2">
         <v>45809</v>
       </c>
       <c r="B76">
@@ -2997,7 +3023,7 @@
         <v>28</v>
       </c>
       <c r="G76">
-        <v>59.6</v>
+        <v>57.7</v>
       </c>
       <c r="H76" t="s">
         <v>33</v>
@@ -3010,7 +3036,7 @@
       </c>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="1">
+      <c r="A77" s="2">
         <v>45839</v>
       </c>
       <c r="B77">
@@ -3029,7 +3055,7 @@
         <v>28</v>
       </c>
       <c r="G77">
-        <v>67.2</v>
+        <v>63.4</v>
       </c>
       <c r="H77" t="s">
         <v>33</v>
@@ -3042,7 +3068,7 @@
       </c>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="1">
+      <c r="A78" s="2">
         <v>45870</v>
       </c>
       <c r="B78">
@@ -3061,7 +3087,7 @@
         <v>28</v>
       </c>
       <c r="G78">
-        <v>50.1</v>
+        <v>48.6</v>
       </c>
       <c r="H78" t="s">
         <v>33</v>
@@ -3074,7 +3100,7 @@
       </c>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="1">
+      <c r="A79" s="2">
         <v>45901</v>
       </c>
       <c r="B79">
@@ -3093,7 +3119,7 @@
         <v>28</v>
       </c>
       <c r="G79">
-        <v>47.1</v>
+        <v>43.8</v>
       </c>
       <c r="H79" t="s">
         <v>33</v>
@@ -3106,7 +3132,7 @@
       </c>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="1">
+      <c r="A80" s="2">
         <v>45931</v>
       </c>
       <c r="B80">
@@ -3125,7 +3151,7 @@
         <v>28</v>
       </c>
       <c r="G80">
-        <v>57.2</v>
+        <v>55.9</v>
       </c>
       <c r="H80" t="s">
         <v>33</v>
@@ -3138,7 +3164,7 @@
       </c>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="1">
+      <c r="A81" s="2">
         <v>45962</v>
       </c>
       <c r="B81">
@@ -3157,7 +3183,7 @@
         <v>28</v>
       </c>
       <c r="G81">
-        <v>60.8</v>
+        <v>61.1</v>
       </c>
       <c r="H81" t="s">
         <v>33</v>
@@ -3170,7 +3196,7 @@
       </c>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="1">
+      <c r="A82" s="2">
         <v>45992</v>
       </c>
       <c r="B82">
@@ -3189,7 +3215,7 @@
         <v>28</v>
       </c>
       <c r="G82">
-        <v>64.8</v>
+        <v>65.5</v>
       </c>
       <c r="H82" t="s">
         <v>33</v>
@@ -3202,7 +3228,7 @@
       </c>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="1">
+      <c r="A83" s="2">
         <v>46023</v>
       </c>
       <c r="B83">
@@ -3221,7 +3247,7 @@
         <v>28</v>
       </c>
       <c r="G83">
-        <v>47.4</v>
+        <v>48</v>
       </c>
       <c r="H83" t="s">
         <v>33</v>
@@ -3234,7 +3260,7 @@
       </c>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="1">
+      <c r="A84" s="2">
         <v>46054</v>
       </c>
       <c r="B84">
@@ -3253,7 +3279,7 @@
         <v>28</v>
       </c>
       <c r="G84">
-        <v>31.9</v>
+        <v>33.2</v>
       </c>
       <c r="H84" t="s">
         <v>33</v>
@@ -3266,7 +3292,7 @@
       </c>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="1">
+      <c r="A85" s="2">
         <v>46082</v>
       </c>
       <c r="B85">
@@ -3285,7 +3311,7 @@
         <v>28</v>
       </c>
       <c r="G85">
-        <v>36.5</v>
+        <v>38.2</v>
       </c>
       <c r="H85" t="s">
         <v>33</v>
@@ -3298,7 +3324,7 @@
       </c>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="1">
+      <c r="A86" s="2">
         <v>46113</v>
       </c>
       <c r="B86">
@@ -3317,7 +3343,7 @@
         <v>28</v>
       </c>
       <c r="G86">
-        <v>44.1</v>
+        <v>42</v>
       </c>
       <c r="H86" t="s">
         <v>33</v>
@@ -3330,7 +3356,7 @@
       </c>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="1">
+      <c r="A87" s="2">
         <v>46143</v>
       </c>
       <c r="B87">
@@ -3349,7 +3375,7 @@
         <v>28</v>
       </c>
       <c r="G87">
-        <v>47.9</v>
+        <v>46.4</v>
       </c>
       <c r="H87" t="s">
         <v>33</v>
@@ -3362,7 +3388,7 @@
       </c>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="1">
+      <c r="A88" s="2">
         <v>46174</v>
       </c>
       <c r="B88">
@@ -3381,7 +3407,7 @@
         <v>28</v>
       </c>
       <c r="G88">
-        <v>44.4</v>
+        <v>43.2</v>
       </c>
       <c r="H88" t="s">
         <v>33</v>
@@ -3394,7 +3420,7 @@
       </c>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="1">
+      <c r="A89" s="2">
         <v>46204</v>
       </c>
       <c r="B89">
@@ -3413,7 +3439,7 @@
         <v>28</v>
       </c>
       <c r="G89">
-        <v>53.2</v>
+        <v>52.8</v>
       </c>
       <c r="H89" t="s">
         <v>33</v>
@@ -3426,7 +3452,7 @@
       </c>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="1">
+      <c r="A90" s="2">
         <v>46235</v>
       </c>
       <c r="B90">
@@ -3445,7 +3471,7 @@
         <v>28</v>
       </c>
       <c r="G90">
-        <v>34.8</v>
+        <v>34.5</v>
       </c>
       <c r="H90" t="s">
         <v>33</v>
@@ -3458,7 +3484,7 @@
       </c>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="1">
+      <c r="A91" s="2">
         <v>46266</v>
       </c>
       <c r="B91">
@@ -3477,7 +3503,7 @@
         <v>28</v>
       </c>
       <c r="G91">
-        <v>30.7</v>
+        <v>30.2</v>
       </c>
       <c r="H91" t="s">
         <v>33</v>
@@ -3490,7 +3516,7 @@
       </c>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="1">
+      <c r="A92" s="2">
         <v>44927</v>
       </c>
       <c r="B92">
@@ -3509,7 +3535,7 @@
         <v>29</v>
       </c>
       <c r="G92">
-        <v>72.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="H92" t="s">
         <v>34</v>
@@ -3522,7 +3548,7 @@
       </c>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="1">
+      <c r="A93" s="2">
         <v>44958</v>
       </c>
       <c r="B93">
@@ -3541,7 +3567,7 @@
         <v>29</v>
       </c>
       <c r="G93">
-        <v>52.4</v>
+        <v>52.7</v>
       </c>
       <c r="H93" t="s">
         <v>34</v>
@@ -3554,7 +3580,7 @@
       </c>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="1">
+      <c r="A94" s="2">
         <v>44986</v>
       </c>
       <c r="B94">
@@ -3573,7 +3599,7 @@
         <v>29</v>
       </c>
       <c r="G94">
-        <v>61.3</v>
+        <v>61</v>
       </c>
       <c r="H94" t="s">
         <v>34</v>
@@ -3586,7 +3612,7 @@
       </c>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="1">
+      <c r="A95" s="2">
         <v>45017</v>
       </c>
       <c r="B95">
@@ -3605,7 +3631,7 @@
         <v>29</v>
       </c>
       <c r="G95">
-        <v>73.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H95" t="s">
         <v>34</v>
@@ -3618,7 +3644,7 @@
       </c>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="1">
+      <c r="A96" s="2">
         <v>45047</v>
       </c>
       <c r="B96">
@@ -3637,7 +3663,7 @@
         <v>29</v>
       </c>
       <c r="G96">
-        <v>69.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H96" t="s">
         <v>34</v>
@@ -3650,7 +3676,7 @@
       </c>
     </row>
     <row r="97" spans="1:10">
-      <c r="A97" s="1">
+      <c r="A97" s="2">
         <v>45078</v>
       </c>
       <c r="B97">
@@ -3669,7 +3695,7 @@
         <v>29</v>
       </c>
       <c r="G97">
-        <v>79.8</v>
+        <v>78.2</v>
       </c>
       <c r="H97" t="s">
         <v>34</v>
@@ -3682,7 +3708,7 @@
       </c>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="1">
+      <c r="A98" s="2">
         <v>45108</v>
       </c>
       <c r="B98">
@@ -3714,7 +3740,7 @@
       </c>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="1">
+      <c r="A99" s="2">
         <v>45139</v>
       </c>
       <c r="B99">
@@ -3733,7 +3759,7 @@
         <v>29</v>
       </c>
       <c r="G99">
-        <v>59.8</v>
+        <v>58.9</v>
       </c>
       <c r="H99" t="s">
         <v>34</v>
@@ -3746,7 +3772,7 @@
       </c>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="1">
+      <c r="A100" s="2">
         <v>45170</v>
       </c>
       <c r="B100">
@@ -3765,7 +3791,7 @@
         <v>29</v>
       </c>
       <c r="G100">
-        <v>54.5</v>
+        <v>53.3</v>
       </c>
       <c r="H100" t="s">
         <v>34</v>
@@ -3778,7 +3804,7 @@
       </c>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" s="1">
+      <c r="A101" s="2">
         <v>45200</v>
       </c>
       <c r="B101">
@@ -3797,7 +3823,7 @@
         <v>29</v>
       </c>
       <c r="G101">
-        <v>59</v>
+        <v>59.2</v>
       </c>
       <c r="H101" t="s">
         <v>34</v>
@@ -3810,7 +3836,7 @@
       </c>
     </row>
     <row r="102" spans="1:10">
-      <c r="A102" s="1">
+      <c r="A102" s="2">
         <v>45231</v>
       </c>
       <c r="B102">
@@ -3829,7 +3855,7 @@
         <v>29</v>
       </c>
       <c r="G102">
-        <v>66.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="H102" t="s">
         <v>34</v>
@@ -3842,7 +3868,7 @@
       </c>
     </row>
     <row r="103" spans="1:10">
-      <c r="A103" s="1">
+      <c r="A103" s="2">
         <v>45261</v>
       </c>
       <c r="B103">
@@ -3861,7 +3887,7 @@
         <v>29</v>
       </c>
       <c r="G103">
-        <v>75.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H103" t="s">
         <v>34</v>
@@ -3874,7 +3900,7 @@
       </c>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" s="1">
+      <c r="A104" s="2">
         <v>45292</v>
       </c>
       <c r="B104">
@@ -3906,7 +3932,7 @@
       </c>
     </row>
     <row r="105" spans="1:10">
-      <c r="A105" s="1">
+      <c r="A105" s="2">
         <v>45323</v>
       </c>
       <c r="B105">
@@ -3925,7 +3951,7 @@
         <v>29</v>
       </c>
       <c r="G105">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="H105" t="s">
         <v>34</v>
@@ -3938,7 +3964,7 @@
       </c>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" s="1">
+      <c r="A106" s="2">
         <v>45352</v>
       </c>
       <c r="B106">
@@ -3957,7 +3983,7 @@
         <v>29</v>
       </c>
       <c r="G106">
-        <v>57.6</v>
+        <v>57.8</v>
       </c>
       <c r="H106" t="s">
         <v>34</v>
@@ -3970,7 +3996,7 @@
       </c>
     </row>
     <row r="107" spans="1:10">
-      <c r="A107" s="1">
+      <c r="A107" s="2">
         <v>45383</v>
       </c>
       <c r="B107">
@@ -3989,7 +4015,7 @@
         <v>29</v>
       </c>
       <c r="G107">
-        <v>69.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="H107" t="s">
         <v>34</v>
@@ -4002,7 +4028,7 @@
       </c>
     </row>
     <row r="108" spans="1:10">
-      <c r="A108" s="1">
+      <c r="A108" s="2">
         <v>45413</v>
       </c>
       <c r="B108">
@@ -4021,7 +4047,7 @@
         <v>29</v>
       </c>
       <c r="G108">
-        <v>25.6</v>
+        <v>26.4</v>
       </c>
       <c r="H108" t="s">
         <v>34</v>
@@ -4034,7 +4060,7 @@
       </c>
     </row>
     <row r="109" spans="1:10">
-      <c r="A109" s="1">
+      <c r="A109" s="2">
         <v>45444</v>
       </c>
       <c r="B109">
@@ -4053,7 +4079,7 @@
         <v>29</v>
       </c>
       <c r="G109">
-        <v>42.6</v>
+        <v>42.2</v>
       </c>
       <c r="H109" t="s">
         <v>34</v>
@@ -4066,7 +4092,7 @@
       </c>
     </row>
     <row r="110" spans="1:10">
-      <c r="A110" s="1">
+      <c r="A110" s="2">
         <v>45474</v>
       </c>
       <c r="B110">
@@ -4085,7 +4111,7 @@
         <v>29</v>
       </c>
       <c r="G110">
-        <v>67</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H110" t="s">
         <v>34</v>
@@ -4098,7 +4124,7 @@
       </c>
     </row>
     <row r="111" spans="1:10">
-      <c r="A111" s="1">
+      <c r="A111" s="2">
         <v>45505</v>
       </c>
       <c r="B111">
@@ -4117,7 +4143,7 @@
         <v>29</v>
       </c>
       <c r="G111">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="H111" t="s">
         <v>34</v>
@@ -4130,7 +4156,7 @@
       </c>
     </row>
     <row r="112" spans="1:10">
-      <c r="A112" s="1">
+      <c r="A112" s="2">
         <v>45536</v>
       </c>
       <c r="B112">
@@ -4149,7 +4175,7 @@
         <v>29</v>
       </c>
       <c r="G112">
-        <v>38.1</v>
+        <v>36.5</v>
       </c>
       <c r="H112" t="s">
         <v>34</v>
@@ -4162,7 +4188,7 @@
       </c>
     </row>
     <row r="113" spans="1:10">
-      <c r="A113" s="1">
+      <c r="A113" s="2">
         <v>45566</v>
       </c>
       <c r="B113">
@@ -4181,7 +4207,7 @@
         <v>29</v>
       </c>
       <c r="G113">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="H113" t="s">
         <v>34</v>
@@ -4194,7 +4220,7 @@
       </c>
     </row>
     <row r="114" spans="1:10">
-      <c r="A114" s="1">
+      <c r="A114" s="2">
         <v>45597</v>
       </c>
       <c r="B114">
@@ -4213,7 +4239,7 @@
         <v>29</v>
       </c>
       <c r="G114">
-        <v>53.9</v>
+        <v>52.7</v>
       </c>
       <c r="H114" t="s">
         <v>34</v>
@@ -4226,7 +4252,7 @@
       </c>
     </row>
     <row r="115" spans="1:10">
-      <c r="A115" s="1">
+      <c r="A115" s="2">
         <v>45627</v>
       </c>
       <c r="B115">
@@ -4258,7 +4284,7 @@
       </c>
     </row>
     <row r="116" spans="1:10">
-      <c r="A116" s="1">
+      <c r="A116" s="2">
         <v>45658</v>
       </c>
       <c r="B116">
@@ -4277,7 +4303,7 @@
         <v>29</v>
       </c>
       <c r="G116">
-        <v>51.8</v>
+        <v>51.2</v>
       </c>
       <c r="H116" t="s">
         <v>34</v>
@@ -4290,7 +4316,7 @@
       </c>
     </row>
     <row r="117" spans="1:10">
-      <c r="A117" s="1">
+      <c r="A117" s="2">
         <v>45689</v>
       </c>
       <c r="B117">
@@ -4309,7 +4335,7 @@
         <v>29</v>
       </c>
       <c r="G117">
-        <v>33</v>
+        <v>32.6</v>
       </c>
       <c r="H117" t="s">
         <v>34</v>
@@ -4322,7 +4348,7 @@
       </c>
     </row>
     <row r="118" spans="1:10">
-      <c r="A118" s="1">
+      <c r="A118" s="2">
         <v>45717</v>
       </c>
       <c r="B118">
@@ -4341,7 +4367,7 @@
         <v>29</v>
       </c>
       <c r="G118">
-        <v>51.2</v>
+        <v>50.5</v>
       </c>
       <c r="H118" t="s">
         <v>34</v>
@@ -4354,7 +4380,7 @@
       </c>
     </row>
     <row r="119" spans="1:10">
-      <c r="A119" s="1">
+      <c r="A119" s="2">
         <v>45748</v>
       </c>
       <c r="B119">
@@ -4373,7 +4399,7 @@
         <v>29</v>
       </c>
       <c r="G119">
-        <v>58.9</v>
+        <v>59.5</v>
       </c>
       <c r="H119" t="s">
         <v>34</v>
@@ -4386,7 +4412,7 @@
       </c>
     </row>
     <row r="120" spans="1:10">
-      <c r="A120" s="1">
+      <c r="A120" s="2">
         <v>45778</v>
       </c>
       <c r="B120">
@@ -4405,7 +4431,7 @@
         <v>29</v>
       </c>
       <c r="G120">
-        <v>55.1</v>
+        <v>54.8</v>
       </c>
       <c r="H120" t="s">
         <v>34</v>
@@ -4418,7 +4444,7 @@
       </c>
     </row>
     <row r="121" spans="1:10">
-      <c r="A121" s="1">
+      <c r="A121" s="2">
         <v>45809</v>
       </c>
       <c r="B121">
@@ -4437,7 +4463,7 @@
         <v>29</v>
       </c>
       <c r="G121">
-        <v>72.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="H121" t="s">
         <v>34</v>
@@ -4450,7 +4476,7 @@
       </c>
     </row>
     <row r="122" spans="1:10">
-      <c r="A122" s="1">
+      <c r="A122" s="2">
         <v>45839</v>
       </c>
       <c r="B122">
@@ -4469,7 +4495,7 @@
         <v>29</v>
       </c>
       <c r="G122">
-        <v>84.2</v>
+        <v>83.5</v>
       </c>
       <c r="H122" t="s">
         <v>34</v>
@@ -4482,7 +4508,7 @@
       </c>
     </row>
     <row r="123" spans="1:10">
-      <c r="A123" s="1">
+      <c r="A123" s="2">
         <v>45870</v>
       </c>
       <c r="B123">
@@ -4501,7 +4527,7 @@
         <v>29</v>
       </c>
       <c r="G123">
-        <v>49.8</v>
+        <v>49.5</v>
       </c>
       <c r="H123" t="s">
         <v>34</v>
@@ -4514,7 +4540,7 @@
       </c>
     </row>
     <row r="124" spans="1:10">
-      <c r="A124" s="1">
+      <c r="A124" s="2">
         <v>45901</v>
       </c>
       <c r="B124">
@@ -4533,7 +4559,7 @@
         <v>29</v>
       </c>
       <c r="G124">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="H124" t="s">
         <v>34</v>
@@ -4546,7 +4572,7 @@
       </c>
     </row>
     <row r="125" spans="1:10">
-      <c r="A125" s="1">
+      <c r="A125" s="2">
         <v>45931</v>
       </c>
       <c r="B125">
@@ -4565,7 +4591,7 @@
         <v>29</v>
       </c>
       <c r="G125">
-        <v>56</v>
+        <v>55.4</v>
       </c>
       <c r="H125" t="s">
         <v>34</v>
@@ -4578,7 +4604,7 @@
       </c>
     </row>
     <row r="126" spans="1:10">
-      <c r="A126" s="1">
+      <c r="A126" s="2">
         <v>45962</v>
       </c>
       <c r="B126">
@@ -4597,7 +4623,7 @@
         <v>29</v>
       </c>
       <c r="G126">
-        <v>64</v>
+        <v>62.6</v>
       </c>
       <c r="H126" t="s">
         <v>34</v>
@@ -4610,7 +4636,7 @@
       </c>
     </row>
     <row r="127" spans="1:10">
-      <c r="A127" s="1">
+      <c r="A127" s="2">
         <v>45992</v>
       </c>
       <c r="B127">
@@ -4642,7 +4668,7 @@
       </c>
     </row>
     <row r="128" spans="1:10">
-      <c r="A128" s="1">
+      <c r="A128" s="2">
         <v>46023</v>
       </c>
       <c r="B128">
@@ -4661,7 +4687,7 @@
         <v>29</v>
       </c>
       <c r="G128">
-        <v>58.3</v>
+        <v>59.5</v>
       </c>
       <c r="H128" t="s">
         <v>34</v>
@@ -4674,7 +4700,7 @@
       </c>
     </row>
     <row r="129" spans="1:10">
-      <c r="A129" s="1">
+      <c r="A129" s="2">
         <v>46054</v>
       </c>
       <c r="B129">
@@ -4693,7 +4719,7 @@
         <v>29</v>
       </c>
       <c r="G129">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="H129" t="s">
         <v>34</v>
@@ -4706,7 +4732,7 @@
       </c>
     </row>
     <row r="130" spans="1:10">
-      <c r="A130" s="1">
+      <c r="A130" s="2">
         <v>46082</v>
       </c>
       <c r="B130">
@@ -4725,7 +4751,7 @@
         <v>29</v>
       </c>
       <c r="G130">
-        <v>54.3</v>
+        <v>53.8</v>
       </c>
       <c r="H130" t="s">
         <v>34</v>
@@ -4738,7 +4764,7 @@
       </c>
     </row>
     <row r="131" spans="1:10">
-      <c r="A131" s="1">
+      <c r="A131" s="2">
         <v>46113</v>
       </c>
       <c r="B131">
@@ -4757,7 +4783,7 @@
         <v>29</v>
       </c>
       <c r="G131">
-        <v>56.8</v>
+        <v>55.7</v>
       </c>
       <c r="H131" t="s">
         <v>34</v>
@@ -4770,7 +4796,7 @@
       </c>
     </row>
     <row r="132" spans="1:10">
-      <c r="A132" s="1">
+      <c r="A132" s="2">
         <v>46143</v>
       </c>
       <c r="B132">
@@ -4789,7 +4815,7 @@
         <v>29</v>
       </c>
       <c r="G132">
-        <v>61.9</v>
+        <v>61.8</v>
       </c>
       <c r="H132" t="s">
         <v>34</v>
@@ -4802,7 +4828,7 @@
       </c>
     </row>
     <row r="133" spans="1:10">
-      <c r="A133" s="1">
+      <c r="A133" s="2">
         <v>46174</v>
       </c>
       <c r="B133">
@@ -4821,7 +4847,7 @@
         <v>29</v>
       </c>
       <c r="G133">
-        <v>70.2</v>
+        <v>70.5</v>
       </c>
       <c r="H133" t="s">
         <v>34</v>
@@ -4834,7 +4860,7 @@
       </c>
     </row>
     <row r="134" spans="1:10">
-      <c r="A134" s="1">
+      <c r="A134" s="2">
         <v>46204</v>
       </c>
       <c r="B134">
@@ -4853,7 +4879,7 @@
         <v>29</v>
       </c>
       <c r="G134">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H134" t="s">
         <v>34</v>
@@ -4866,7 +4892,7 @@
       </c>
     </row>
     <row r="135" spans="1:10">
-      <c r="A135" s="1">
+      <c r="A135" s="2">
         <v>46235</v>
       </c>
       <c r="B135">
@@ -4885,7 +4911,7 @@
         <v>29</v>
       </c>
       <c r="G135">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="H135" t="s">
         <v>34</v>
@@ -4898,7 +4924,7 @@
       </c>
     </row>
     <row r="136" spans="1:10">
-      <c r="A136" s="1">
+      <c r="A136" s="2">
         <v>46266</v>
       </c>
       <c r="B136">
@@ -4917,7 +4943,7 @@
         <v>29</v>
       </c>
       <c r="G136">
-        <v>39.6</v>
+        <v>39.1</v>
       </c>
       <c r="H136" t="s">
         <v>34</v>
@@ -4930,7 +4956,7 @@
       </c>
     </row>
     <row r="137" spans="1:10">
-      <c r="A137" s="1">
+      <c r="A137" s="2">
         <v>44927</v>
       </c>
       <c r="B137">
@@ -4962,7 +4988,7 @@
       </c>
     </row>
     <row r="138" spans="1:10">
-      <c r="A138" s="1">
+      <c r="A138" s="2">
         <v>44958</v>
       </c>
       <c r="B138">
@@ -4981,7 +5007,7 @@
         <v>30</v>
       </c>
       <c r="G138">
-        <v>69.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H138" t="s">
         <v>35</v>
@@ -4994,7 +5020,7 @@
       </c>
     </row>
     <row r="139" spans="1:10">
-      <c r="A139" s="1">
+      <c r="A139" s="2">
         <v>44986</v>
       </c>
       <c r="B139">
@@ -5013,7 +5039,7 @@
         <v>30</v>
       </c>
       <c r="G139">
-        <v>60.7</v>
+        <v>57.6</v>
       </c>
       <c r="H139" t="s">
         <v>35</v>
@@ -5026,7 +5052,7 @@
       </c>
     </row>
     <row r="140" spans="1:10">
-      <c r="A140" s="1">
+      <c r="A140" s="2">
         <v>45017</v>
       </c>
       <c r="B140">
@@ -5045,7 +5071,7 @@
         <v>30</v>
       </c>
       <c r="G140">
-        <v>41.3</v>
+        <v>41.7</v>
       </c>
       <c r="H140" t="s">
         <v>35</v>
@@ -5058,7 +5084,7 @@
       </c>
     </row>
     <row r="141" spans="1:10">
-      <c r="A141" s="1">
+      <c r="A141" s="2">
         <v>45047</v>
       </c>
       <c r="B141">
@@ -5077,7 +5103,7 @@
         <v>30</v>
       </c>
       <c r="G141">
-        <v>54.3</v>
+        <v>41.9</v>
       </c>
       <c r="H141" t="s">
         <v>35</v>
@@ -5090,7 +5116,7 @@
       </c>
     </row>
     <row r="142" spans="1:10">
-      <c r="A142" s="1">
+      <c r="A142" s="2">
         <v>45078</v>
       </c>
       <c r="B142">
@@ -5109,7 +5135,7 @@
         <v>30</v>
       </c>
       <c r="G142">
-        <v>56.2</v>
+        <v>52.8</v>
       </c>
       <c r="H142" t="s">
         <v>35</v>
@@ -5122,7 +5148,7 @@
       </c>
     </row>
     <row r="143" spans="1:10">
-      <c r="A143" s="1">
+      <c r="A143" s="2">
         <v>45108</v>
       </c>
       <c r="B143">
@@ -5141,7 +5167,7 @@
         <v>30</v>
       </c>
       <c r="G143">
-        <v>76.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H143" t="s">
         <v>35</v>
@@ -5154,7 +5180,7 @@
       </c>
     </row>
     <row r="144" spans="1:10">
-      <c r="A144" s="1">
+      <c r="A144" s="2">
         <v>45139</v>
       </c>
       <c r="B144">
@@ -5173,7 +5199,7 @@
         <v>30</v>
       </c>
       <c r="G144">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="H144" t="s">
         <v>35</v>
@@ -5186,7 +5212,7 @@
       </c>
     </row>
     <row r="145" spans="1:10">
-      <c r="A145" s="1">
+      <c r="A145" s="2">
         <v>45170</v>
       </c>
       <c r="B145">
@@ -5205,7 +5231,7 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>44.4</v>
+        <v>35.2</v>
       </c>
       <c r="H145" t="s">
         <v>35</v>
@@ -5218,7 +5244,7 @@
       </c>
     </row>
     <row r="146" spans="1:10">
-      <c r="A146" s="1">
+      <c r="A146" s="2">
         <v>45200</v>
       </c>
       <c r="B146">
@@ -5237,7 +5263,7 @@
         <v>30</v>
       </c>
       <c r="G146">
-        <v>48.1</v>
+        <v>43.7</v>
       </c>
       <c r="H146" t="s">
         <v>35</v>
@@ -5250,7 +5276,7 @@
       </c>
     </row>
     <row r="147" spans="1:10">
-      <c r="A147" s="1">
+      <c r="A147" s="2">
         <v>45231</v>
       </c>
       <c r="B147">
@@ -5269,7 +5295,7 @@
         <v>30</v>
       </c>
       <c r="G147">
-        <v>56.5</v>
+        <v>50.1</v>
       </c>
       <c r="H147" t="s">
         <v>35</v>
@@ -5282,7 +5308,7 @@
       </c>
     </row>
     <row r="148" spans="1:10">
-      <c r="A148" s="1">
+      <c r="A148" s="2">
         <v>45261</v>
       </c>
       <c r="B148">
@@ -5301,7 +5327,7 @@
         <v>30</v>
       </c>
       <c r="G148">
-        <v>55.6</v>
+        <v>51.9</v>
       </c>
       <c r="H148" t="s">
         <v>35</v>
@@ -5314,7 +5340,7 @@
       </c>
     </row>
     <row r="149" spans="1:10">
-      <c r="A149" s="1">
+      <c r="A149" s="2">
         <v>45292</v>
       </c>
       <c r="B149">
@@ -5333,7 +5359,7 @@
         <v>30</v>
       </c>
       <c r="G149">
-        <v>37.7</v>
+        <v>34.9</v>
       </c>
       <c r="H149" t="s">
         <v>35</v>
@@ -5346,7 +5372,7 @@
       </c>
     </row>
     <row r="150" spans="1:10">
-      <c r="A150" s="1">
+      <c r="A150" s="2">
         <v>45323</v>
       </c>
       <c r="B150">
@@ -5365,7 +5391,7 @@
         <v>30</v>
       </c>
       <c r="G150">
-        <v>30.8</v>
+        <v>32.5</v>
       </c>
       <c r="H150" t="s">
         <v>35</v>
@@ -5378,7 +5404,7 @@
       </c>
     </row>
     <row r="151" spans="1:10">
-      <c r="A151" s="1">
+      <c r="A151" s="2">
         <v>45352</v>
       </c>
       <c r="B151">
@@ -5397,7 +5423,7 @@
         <v>30</v>
       </c>
       <c r="G151">
-        <v>44</v>
+        <v>38.1</v>
       </c>
       <c r="H151" t="s">
         <v>35</v>
@@ -5410,7 +5436,7 @@
       </c>
     </row>
     <row r="152" spans="1:10">
-      <c r="A152" s="1">
+      <c r="A152" s="2">
         <v>45383</v>
       </c>
       <c r="B152">
@@ -5429,7 +5455,7 @@
         <v>30</v>
       </c>
       <c r="G152">
-        <v>32.3</v>
+        <v>16.4</v>
       </c>
       <c r="H152" t="s">
         <v>35</v>
@@ -5442,7 +5468,7 @@
       </c>
     </row>
     <row r="153" spans="1:10">
-      <c r="A153" s="1">
+      <c r="A153" s="2">
         <v>45413</v>
       </c>
       <c r="B153">
@@ -5474,7 +5500,7 @@
       </c>
     </row>
     <row r="154" spans="1:10">
-      <c r="A154" s="1">
+      <c r="A154" s="2">
         <v>45444</v>
       </c>
       <c r="B154">
@@ -5493,7 +5519,7 @@
         <v>30</v>
       </c>
       <c r="G154">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H154" t="s">
         <v>35</v>
@@ -5506,7 +5532,7 @@
       </c>
     </row>
     <row r="155" spans="1:10">
-      <c r="A155" s="1">
+      <c r="A155" s="2">
         <v>45474</v>
       </c>
       <c r="B155">
@@ -5525,7 +5551,7 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>50.4</v>
+        <v>43.1</v>
       </c>
       <c r="H155" t="s">
         <v>35</v>
@@ -5538,7 +5564,7 @@
       </c>
     </row>
     <row r="156" spans="1:10">
-      <c r="A156" s="1">
+      <c r="A156" s="2">
         <v>45505</v>
       </c>
       <c r="B156">
@@ -5557,7 +5583,7 @@
         <v>30</v>
       </c>
       <c r="G156">
-        <v>33.2</v>
+        <v>26.4</v>
       </c>
       <c r="H156" t="s">
         <v>35</v>
@@ -5570,7 +5596,7 @@
       </c>
     </row>
     <row r="157" spans="1:10">
-      <c r="A157" s="1">
+      <c r="A157" s="2">
         <v>45536</v>
       </c>
       <c r="B157">
@@ -5589,7 +5615,7 @@
         <v>30</v>
       </c>
       <c r="G157">
-        <v>17.9</v>
+        <v>15.8</v>
       </c>
       <c r="H157" t="s">
         <v>35</v>
@@ -5602,7 +5628,7 @@
       </c>
     </row>
     <row r="158" spans="1:10">
-      <c r="A158" s="1">
+      <c r="A158" s="2">
         <v>45566</v>
       </c>
       <c r="B158">
@@ -5621,7 +5647,7 @@
         <v>30</v>
       </c>
       <c r="G158">
-        <v>39.6</v>
+        <v>35.5</v>
       </c>
       <c r="H158" t="s">
         <v>35</v>
@@ -5634,7 +5660,7 @@
       </c>
     </row>
     <row r="159" spans="1:10">
-      <c r="A159" s="1">
+      <c r="A159" s="2">
         <v>45597</v>
       </c>
       <c r="B159">
@@ -5653,7 +5679,7 @@
         <v>30</v>
       </c>
       <c r="G159">
-        <v>56.8</v>
+        <v>54.6</v>
       </c>
       <c r="H159" t="s">
         <v>35</v>
@@ -5666,7 +5692,7 @@
       </c>
     </row>
     <row r="160" spans="1:10">
-      <c r="A160" s="1">
+      <c r="A160" s="2">
         <v>45627</v>
       </c>
       <c r="B160">
@@ -5685,7 +5711,7 @@
         <v>30</v>
       </c>
       <c r="G160">
-        <v>65.2</v>
+        <v>57.8</v>
       </c>
       <c r="H160" t="s">
         <v>35</v>
@@ -5698,7 +5724,7 @@
       </c>
     </row>
     <row r="161" spans="1:10">
-      <c r="A161" s="1">
+      <c r="A161" s="2">
         <v>45658</v>
       </c>
       <c r="B161">
@@ -5717,7 +5743,7 @@
         <v>30</v>
       </c>
       <c r="G161">
-        <v>55</v>
+        <v>42.5</v>
       </c>
       <c r="H161" t="s">
         <v>35</v>
@@ -5730,7 +5756,7 @@
       </c>
     </row>
     <row r="162" spans="1:10">
-      <c r="A162" s="1">
+      <c r="A162" s="2">
         <v>45689</v>
       </c>
       <c r="B162">
@@ -5749,7 +5775,7 @@
         <v>30</v>
       </c>
       <c r="G162">
-        <v>37.1</v>
+        <v>26.1</v>
       </c>
       <c r="H162" t="s">
         <v>35</v>
@@ -5762,7 +5788,7 @@
       </c>
     </row>
     <row r="163" spans="1:10">
-      <c r="A163" s="1">
+      <c r="A163" s="2">
         <v>45717</v>
       </c>
       <c r="B163">
@@ -5781,7 +5807,7 @@
         <v>30</v>
       </c>
       <c r="G163">
-        <v>54.6</v>
+        <v>48.5</v>
       </c>
       <c r="H163" t="s">
         <v>35</v>
@@ -5794,7 +5820,7 @@
       </c>
     </row>
     <row r="164" spans="1:10">
-      <c r="A164" s="1">
+      <c r="A164" s="2">
         <v>45748</v>
       </c>
       <c r="B164">
@@ -5813,7 +5839,7 @@
         <v>30</v>
       </c>
       <c r="G164">
-        <v>69.7</v>
+        <v>59.8</v>
       </c>
       <c r="H164" t="s">
         <v>35</v>
@@ -5826,7 +5852,7 @@
       </c>
     </row>
     <row r="165" spans="1:10">
-      <c r="A165" s="1">
+      <c r="A165" s="2">
         <v>45778</v>
       </c>
       <c r="B165">
@@ -5845,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>51.3</v>
+        <v>47.3</v>
       </c>
       <c r="H165" t="s">
         <v>35</v>
@@ -5858,7 +5884,7 @@
       </c>
     </row>
     <row r="166" spans="1:10">
-      <c r="A166" s="1">
+      <c r="A166" s="2">
         <v>45809</v>
       </c>
       <c r="B166">
@@ -5877,7 +5903,7 @@
         <v>30</v>
       </c>
       <c r="G166">
-        <v>70.5</v>
+        <v>61.4</v>
       </c>
       <c r="H166" t="s">
         <v>35</v>
@@ -5890,7 +5916,7 @@
       </c>
     </row>
     <row r="167" spans="1:10">
-      <c r="A167" s="1">
+      <c r="A167" s="2">
         <v>45839</v>
       </c>
       <c r="B167">
@@ -5909,7 +5935,7 @@
         <v>30</v>
       </c>
       <c r="G167">
-        <v>99.90000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="H167" t="s">
         <v>35</v>
@@ -5922,7 +5948,7 @@
       </c>
     </row>
     <row r="168" spans="1:10">
-      <c r="A168" s="1">
+      <c r="A168" s="2">
         <v>45870</v>
       </c>
       <c r="B168">
@@ -5941,7 +5967,7 @@
         <v>30</v>
       </c>
       <c r="G168">
-        <v>62.3</v>
+        <v>56.8</v>
       </c>
       <c r="H168" t="s">
         <v>35</v>
@@ -5954,7 +5980,7 @@
       </c>
     </row>
     <row r="169" spans="1:10">
-      <c r="A169" s="1">
+      <c r="A169" s="2">
         <v>45901</v>
       </c>
       <c r="B169">
@@ -5973,7 +5999,7 @@
         <v>30</v>
       </c>
       <c r="G169">
-        <v>32.9</v>
+        <v>30.6</v>
       </c>
       <c r="H169" t="s">
         <v>35</v>
@@ -5986,7 +6012,7 @@
       </c>
     </row>
     <row r="170" spans="1:10">
-      <c r="A170" s="1">
+      <c r="A170" s="2">
         <v>45931</v>
       </c>
       <c r="B170">
@@ -6005,7 +6031,7 @@
         <v>30</v>
       </c>
       <c r="G170">
-        <v>57.7</v>
+        <v>51</v>
       </c>
       <c r="H170" t="s">
         <v>35</v>
@@ -6018,7 +6044,7 @@
       </c>
     </row>
     <row r="171" spans="1:10">
-      <c r="A171" s="1">
+      <c r="A171" s="2">
         <v>45962</v>
       </c>
       <c r="B171">
@@ -6037,7 +6063,7 @@
         <v>30</v>
       </c>
       <c r="G171">
-        <v>71.7</v>
+        <v>68</v>
       </c>
       <c r="H171" t="s">
         <v>35</v>
@@ -6050,7 +6076,7 @@
       </c>
     </row>
     <row r="172" spans="1:10">
-      <c r="A172" s="1">
+      <c r="A172" s="2">
         <v>45992</v>
       </c>
       <c r="B172">
@@ -6069,7 +6095,7 @@
         <v>30</v>
       </c>
       <c r="G172">
-        <v>87.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H172" t="s">
         <v>35</v>
@@ -6082,7 +6108,7 @@
       </c>
     </row>
     <row r="173" spans="1:10">
-      <c r="A173" s="1">
+      <c r="A173" s="2">
         <v>46023</v>
       </c>
       <c r="B173">
@@ -6101,7 +6127,7 @@
         <v>30</v>
       </c>
       <c r="G173">
-        <v>62.8</v>
+        <v>60.7</v>
       </c>
       <c r="H173" t="s">
         <v>35</v>
@@ -6114,7 +6140,7 @@
       </c>
     </row>
     <row r="174" spans="1:10">
-      <c r="A174" s="1">
+      <c r="A174" s="2">
         <v>46054</v>
       </c>
       <c r="B174">
@@ -6133,7 +6159,7 @@
         <v>30</v>
       </c>
       <c r="G174">
-        <v>36.2</v>
+        <v>26.4</v>
       </c>
       <c r="H174" t="s">
         <v>35</v>
@@ -6146,7 +6172,7 @@
       </c>
     </row>
     <row r="175" spans="1:10">
-      <c r="A175" s="1">
+      <c r="A175" s="2">
         <v>46082</v>
       </c>
       <c r="B175">
@@ -6165,7 +6191,7 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>53.1</v>
+        <v>50.7</v>
       </c>
       <c r="H175" t="s">
         <v>35</v>
@@ -6178,7 +6204,7 @@
       </c>
     </row>
     <row r="176" spans="1:10">
-      <c r="A176" s="1">
+      <c r="A176" s="2">
         <v>46113</v>
       </c>
       <c r="B176">
@@ -6197,7 +6223,7 @@
         <v>30</v>
       </c>
       <c r="G176">
-        <v>41.1</v>
+        <v>47.6</v>
       </c>
       <c r="H176" t="s">
         <v>35</v>
@@ -6210,7 +6236,7 @@
       </c>
     </row>
     <row r="177" spans="1:10">
-      <c r="A177" s="1">
+      <c r="A177" s="2">
         <v>46143</v>
       </c>
       <c r="B177">
@@ -6229,7 +6255,7 @@
         <v>30</v>
       </c>
       <c r="G177">
-        <v>52.9</v>
+        <v>44.2</v>
       </c>
       <c r="H177" t="s">
         <v>35</v>
@@ -6242,7 +6268,7 @@
       </c>
     </row>
     <row r="178" spans="1:10">
-      <c r="A178" s="1">
+      <c r="A178" s="2">
         <v>46174</v>
       </c>
       <c r="B178">
@@ -6261,7 +6287,7 @@
         <v>30</v>
       </c>
       <c r="G178">
-        <v>78.8</v>
+        <v>76.8</v>
       </c>
       <c r="H178" t="s">
         <v>35</v>
@@ -6274,7 +6300,7 @@
       </c>
     </row>
     <row r="179" spans="1:10">
-      <c r="A179" s="1">
+      <c r="A179" s="2">
         <v>46204</v>
       </c>
       <c r="B179">
@@ -6293,7 +6319,7 @@
         <v>30</v>
       </c>
       <c r="G179">
-        <v>93.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="H179" t="s">
         <v>35</v>
@@ -6306,7 +6332,7 @@
       </c>
     </row>
     <row r="180" spans="1:10">
-      <c r="A180" s="1">
+      <c r="A180" s="2">
         <v>46235</v>
       </c>
       <c r="B180">
@@ -6325,7 +6351,7 @@
         <v>30</v>
       </c>
       <c r="G180">
-        <v>62.8</v>
+        <v>57.5</v>
       </c>
       <c r="H180" t="s">
         <v>35</v>
@@ -6338,7 +6364,7 @@
       </c>
     </row>
     <row r="181" spans="1:10">
-      <c r="A181" s="1">
+      <c r="A181" s="2">
         <v>46266</v>
       </c>
       <c r="B181">
@@ -6357,7 +6383,7 @@
         <v>30</v>
       </c>
       <c r="G181">
-        <v>49.2</v>
+        <v>47.6</v>
       </c>
       <c r="H181" t="s">
         <v>35</v>
@@ -6370,7 +6396,7 @@
       </c>
     </row>
     <row r="182" spans="1:10">
-      <c r="A182" s="1">
+      <c r="A182" s="2">
         <v>44927</v>
       </c>
       <c r="B182">
@@ -6389,7 +6415,7 @@
         <v>31</v>
       </c>
       <c r="G182">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="H182" t="s">
         <v>36</v>
@@ -6402,7 +6428,7 @@
       </c>
     </row>
     <row r="183" spans="1:10">
-      <c r="A183" s="1">
+      <c r="A183" s="2">
         <v>44958</v>
       </c>
       <c r="B183">
@@ -6434,7 +6460,7 @@
       </c>
     </row>
     <row r="184" spans="1:10">
-      <c r="A184" s="1">
+      <c r="A184" s="2">
         <v>44986</v>
       </c>
       <c r="B184">
@@ -6466,7 +6492,7 @@
       </c>
     </row>
     <row r="185" spans="1:10">
-      <c r="A185" s="1">
+      <c r="A185" s="2">
         <v>45017</v>
       </c>
       <c r="B185">
@@ -6498,7 +6524,7 @@
       </c>
     </row>
     <row r="186" spans="1:10">
-      <c r="A186" s="1">
+      <c r="A186" s="2">
         <v>45047</v>
       </c>
       <c r="B186">
@@ -6530,7 +6556,7 @@
       </c>
     </row>
     <row r="187" spans="1:10">
-      <c r="A187" s="1">
+      <c r="A187" s="2">
         <v>45078</v>
       </c>
       <c r="B187">
@@ -6562,7 +6588,7 @@
       </c>
     </row>
     <row r="188" spans="1:10">
-      <c r="A188" s="1">
+      <c r="A188" s="2">
         <v>45108</v>
       </c>
       <c r="B188">
@@ -6594,7 +6620,7 @@
       </c>
     </row>
     <row r="189" spans="1:10">
-      <c r="A189" s="1">
+      <c r="A189" s="2">
         <v>45139</v>
       </c>
       <c r="B189">
@@ -6626,7 +6652,7 @@
       </c>
     </row>
     <row r="190" spans="1:10">
-      <c r="A190" s="1">
+      <c r="A190" s="2">
         <v>45170</v>
       </c>
       <c r="B190">
@@ -6658,7 +6684,7 @@
       </c>
     </row>
     <row r="191" spans="1:10">
-      <c r="A191" s="1">
+      <c r="A191" s="2">
         <v>45200</v>
       </c>
       <c r="B191">
@@ -6690,7 +6716,7 @@
       </c>
     </row>
     <row r="192" spans="1:10">
-      <c r="A192" s="1">
+      <c r="A192" s="2">
         <v>45231</v>
       </c>
       <c r="B192">
@@ -6722,7 +6748,7 @@
       </c>
     </row>
     <row r="193" spans="1:10">
-      <c r="A193" s="1">
+      <c r="A193" s="2">
         <v>45261</v>
       </c>
       <c r="B193">
@@ -6741,7 +6767,7 @@
         <v>31</v>
       </c>
       <c r="G193">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="H193" t="s">
         <v>36</v>
@@ -6754,7 +6780,7 @@
       </c>
     </row>
     <row r="194" spans="1:10">
-      <c r="A194" s="1">
+      <c r="A194" s="2">
         <v>45292</v>
       </c>
       <c r="B194">
@@ -6786,7 +6812,7 @@
       </c>
     </row>
     <row r="195" spans="1:10">
-      <c r="A195" s="1">
+      <c r="A195" s="2">
         <v>45323</v>
       </c>
       <c r="B195">
@@ -6805,7 +6831,7 @@
         <v>31</v>
       </c>
       <c r="G195">
-        <v>0</v>
+        <v>15.7</v>
       </c>
       <c r="H195" t="s">
         <v>36</v>
@@ -6818,7 +6844,7 @@
       </c>
     </row>
     <row r="196" spans="1:10">
-      <c r="A196" s="1">
+      <c r="A196" s="2">
         <v>45352</v>
       </c>
       <c r="B196">
@@ -6837,7 +6863,7 @@
         <v>31</v>
       </c>
       <c r="G196">
-        <v>73.5</v>
+        <v>62.1</v>
       </c>
       <c r="H196" t="s">
         <v>36</v>
@@ -6850,7 +6876,7 @@
       </c>
     </row>
     <row r="197" spans="1:10">
-      <c r="A197" s="1">
+      <c r="A197" s="2">
         <v>45383</v>
       </c>
       <c r="B197">
@@ -6869,7 +6895,7 @@
         <v>31</v>
       </c>
       <c r="G197">
-        <v>19.7</v>
+        <v>45.7</v>
       </c>
       <c r="H197" t="s">
         <v>36</v>
@@ -6882,7 +6908,7 @@
       </c>
     </row>
     <row r="198" spans="1:10">
-      <c r="A198" s="1">
+      <c r="A198" s="2">
         <v>45413</v>
       </c>
       <c r="B198">
@@ -6914,7 +6940,7 @@
       </c>
     </row>
     <row r="199" spans="1:10">
-      <c r="A199" s="1">
+      <c r="A199" s="2">
         <v>45444</v>
       </c>
       <c r="B199">
@@ -6946,7 +6972,7 @@
       </c>
     </row>
     <row r="200" spans="1:10">
-      <c r="A200" s="1">
+      <c r="A200" s="2">
         <v>45474</v>
       </c>
       <c r="B200">
@@ -6978,7 +7004,7 @@
       </c>
     </row>
     <row r="201" spans="1:10">
-      <c r="A201" s="1">
+      <c r="A201" s="2">
         <v>45505</v>
       </c>
       <c r="B201">
@@ -7010,7 +7036,7 @@
       </c>
     </row>
     <row r="202" spans="1:10">
-      <c r="A202" s="1">
+      <c r="A202" s="2">
         <v>45536</v>
       </c>
       <c r="B202">
@@ -7042,7 +7068,7 @@
       </c>
     </row>
     <row r="203" spans="1:10">
-      <c r="A203" s="1">
+      <c r="A203" s="2">
         <v>45566</v>
       </c>
       <c r="B203">
@@ -7074,7 +7100,7 @@
       </c>
     </row>
     <row r="204" spans="1:10">
-      <c r="A204" s="1">
+      <c r="A204" s="2">
         <v>45597</v>
       </c>
       <c r="B204">
@@ -7106,7 +7132,7 @@
       </c>
     </row>
     <row r="205" spans="1:10">
-      <c r="A205" s="1">
+      <c r="A205" s="2">
         <v>45627</v>
       </c>
       <c r="B205">
@@ -7138,7 +7164,7 @@
       </c>
     </row>
     <row r="206" spans="1:10">
-      <c r="A206" s="1">
+      <c r="A206" s="2">
         <v>45658</v>
       </c>
       <c r="B206">
@@ -7170,7 +7196,7 @@
       </c>
     </row>
     <row r="207" spans="1:10">
-      <c r="A207" s="1">
+      <c r="A207" s="2">
         <v>45689</v>
       </c>
       <c r="B207">
@@ -7189,7 +7215,7 @@
         <v>31</v>
       </c>
       <c r="G207">
-        <v>0</v>
+        <v>16.6</v>
       </c>
       <c r="H207" t="s">
         <v>36</v>
@@ -7202,7 +7228,7 @@
       </c>
     </row>
     <row r="208" spans="1:10">
-      <c r="A208" s="1">
+      <c r="A208" s="2">
         <v>45717</v>
       </c>
       <c r="B208">
@@ -7221,7 +7247,7 @@
         <v>31</v>
       </c>
       <c r="G208">
-        <v>29.7</v>
+        <v>0</v>
       </c>
       <c r="H208" t="s">
         <v>36</v>
@@ -7234,7 +7260,7 @@
       </c>
     </row>
     <row r="209" spans="1:10">
-      <c r="A209" s="1">
+      <c r="A209" s="2">
         <v>45748</v>
       </c>
       <c r="B209">
@@ -7253,7 +7279,7 @@
         <v>31</v>
       </c>
       <c r="G209">
-        <v>18.4</v>
+        <v>17.5</v>
       </c>
       <c r="H209" t="s">
         <v>36</v>
@@ -7266,7 +7292,7 @@
       </c>
     </row>
     <row r="210" spans="1:10">
-      <c r="A210" s="1">
+      <c r="A210" s="2">
         <v>45778</v>
       </c>
       <c r="B210">
@@ -7285,7 +7311,7 @@
         <v>31</v>
       </c>
       <c r="G210">
-        <v>64.09999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H210" t="s">
         <v>36</v>
@@ -7298,7 +7324,7 @@
       </c>
     </row>
     <row r="211" spans="1:10">
-      <c r="A211" s="1">
+      <c r="A211" s="2">
         <v>45809</v>
       </c>
       <c r="B211">
@@ -7317,7 +7343,7 @@
         <v>31</v>
       </c>
       <c r="G211">
-        <v>83.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H211" t="s">
         <v>36</v>
@@ -7330,7 +7356,7 @@
       </c>
     </row>
     <row r="212" spans="1:10">
-      <c r="A212" s="1">
+      <c r="A212" s="2">
         <v>45839</v>
       </c>
       <c r="B212">
@@ -7349,7 +7375,7 @@
         <v>31</v>
       </c>
       <c r="G212">
-        <v>94.5</v>
+        <v>100</v>
       </c>
       <c r="H212" t="s">
         <v>36</v>
@@ -7362,7 +7388,7 @@
       </c>
     </row>
     <row r="213" spans="1:10">
-      <c r="A213" s="1">
+      <c r="A213" s="2">
         <v>45870</v>
       </c>
       <c r="B213">
@@ -7381,7 +7407,7 @@
         <v>31</v>
       </c>
       <c r="G213">
-        <v>89.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H213" t="s">
         <v>36</v>
@@ -7394,7 +7420,7 @@
       </c>
     </row>
     <row r="214" spans="1:10">
-      <c r="A214" s="1">
+      <c r="A214" s="2">
         <v>45901</v>
       </c>
       <c r="B214">
@@ -7413,7 +7439,7 @@
         <v>31</v>
       </c>
       <c r="G214">
-        <v>48.8</v>
+        <v>37.2</v>
       </c>
       <c r="H214" t="s">
         <v>36</v>
@@ -7426,7 +7452,7 @@
       </c>
     </row>
     <row r="215" spans="1:10">
-      <c r="A215" s="1">
+      <c r="A215" s="2">
         <v>45931</v>
       </c>
       <c r="B215">
@@ -7445,7 +7471,7 @@
         <v>31</v>
       </c>
       <c r="G215">
-        <v>66.3</v>
+        <v>26.9</v>
       </c>
       <c r="H215" t="s">
         <v>36</v>
@@ -7458,7 +7484,7 @@
       </c>
     </row>
     <row r="216" spans="1:10">
-      <c r="A216" s="1">
+      <c r="A216" s="2">
         <v>45962</v>
       </c>
       <c r="B216">
@@ -7477,7 +7503,7 @@
         <v>31</v>
       </c>
       <c r="G216">
-        <v>61.6</v>
+        <v>78.2</v>
       </c>
       <c r="H216" t="s">
         <v>36</v>
@@ -7490,7 +7516,7 @@
       </c>
     </row>
     <row r="217" spans="1:10">
-      <c r="A217" s="1">
+      <c r="A217" s="2">
         <v>45992</v>
       </c>
       <c r="B217">
@@ -7509,7 +7535,7 @@
         <v>31</v>
       </c>
       <c r="G217">
-        <v>59.1</v>
+        <v>43.9</v>
       </c>
       <c r="H217" t="s">
         <v>36</v>
@@ -7522,7 +7548,7 @@
       </c>
     </row>
     <row r="218" spans="1:10">
-      <c r="A218" s="1">
+      <c r="A218" s="2">
         <v>46023</v>
       </c>
       <c r="B218">
@@ -7541,7 +7567,7 @@
         <v>31</v>
       </c>
       <c r="G218">
-        <v>66.3</v>
+        <v>65</v>
       </c>
       <c r="H218" t="s">
         <v>36</v>
@@ -7554,7 +7580,7 @@
       </c>
     </row>
     <row r="219" spans="1:10">
-      <c r="A219" s="1">
+      <c r="A219" s="2">
         <v>46054</v>
       </c>
       <c r="B219">
@@ -7573,7 +7599,7 @@
         <v>31</v>
       </c>
       <c r="G219">
-        <v>20.2</v>
+        <v>43</v>
       </c>
       <c r="H219" t="s">
         <v>36</v>
@@ -7586,7 +7612,7 @@
       </c>
     </row>
     <row r="220" spans="1:10">
-      <c r="A220" s="1">
+      <c r="A220" s="2">
         <v>46082</v>
       </c>
       <c r="B220">
@@ -7605,7 +7631,7 @@
         <v>31</v>
       </c>
       <c r="G220">
-        <v>34.8</v>
+        <v>38</v>
       </c>
       <c r="H220" t="s">
         <v>36</v>
@@ -7618,7 +7644,7 @@
       </c>
     </row>
     <row r="221" spans="1:10">
-      <c r="A221" s="1">
+      <c r="A221" s="2">
         <v>46113</v>
       </c>
       <c r="B221">
@@ -7637,7 +7663,7 @@
         <v>31</v>
       </c>
       <c r="G221">
-        <v>55.6</v>
+        <v>19.3</v>
       </c>
       <c r="H221" t="s">
         <v>36</v>
@@ -7650,7 +7676,7 @@
       </c>
     </row>
     <row r="222" spans="1:10">
-      <c r="A222" s="1">
+      <c r="A222" s="2">
         <v>46143</v>
       </c>
       <c r="B222">
@@ -7669,7 +7695,7 @@
         <v>31</v>
       </c>
       <c r="G222">
-        <v>25.8</v>
+        <v>52.4</v>
       </c>
       <c r="H222" t="s">
         <v>36</v>
@@ -7682,7 +7708,7 @@
       </c>
     </row>
     <row r="223" spans="1:10">
-      <c r="A223" s="1">
+      <c r="A223" s="2">
         <v>46174</v>
       </c>
       <c r="B223">
@@ -7701,7 +7727,7 @@
         <v>31</v>
       </c>
       <c r="G223">
-        <v>59.1</v>
+        <v>51.6</v>
       </c>
       <c r="H223" t="s">
         <v>36</v>
@@ -7714,7 +7740,7 @@
       </c>
     </row>
     <row r="224" spans="1:10">
-      <c r="A224" s="1">
+      <c r="A224" s="2">
         <v>46204</v>
       </c>
       <c r="B224">
@@ -7733,7 +7759,7 @@
         <v>31</v>
       </c>
       <c r="G224">
-        <v>61.8</v>
+        <v>44.4</v>
       </c>
       <c r="H224" t="s">
         <v>36</v>
@@ -7746,7 +7772,7 @@
       </c>
     </row>
     <row r="225" spans="1:10">
-      <c r="A225" s="1">
+      <c r="A225" s="2">
         <v>46235</v>
       </c>
       <c r="B225">
@@ -7765,7 +7791,7 @@
         <v>31</v>
       </c>
       <c r="G225">
-        <v>100</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H225" t="s">
         <v>36</v>
@@ -7778,7 +7804,7 @@
       </c>
     </row>
     <row r="226" spans="1:10">
-      <c r="A226" s="1">
+      <c r="A226" s="2">
         <v>46266</v>
       </c>
       <c r="B226">
@@ -7797,7 +7823,7 @@
         <v>31</v>
       </c>
       <c r="G226">
-        <v>26.9</v>
+        <v>9.9</v>
       </c>
       <c r="H226" t="s">
         <v>36</v>
@@ -7820,40 +7846,40 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>48</v>
       </c>
     </row>
@@ -7865,31 +7891,31 @@
         <v>27</v>
       </c>
       <c r="C2">
-        <v>44.93333333333333</v>
+        <v>44.81111111111111</v>
       </c>
       <c r="D2">
-        <v>65.67777777777778</v>
+        <v>65.44444444444444</v>
       </c>
       <c r="E2">
-        <v>0.4616716122650841</v>
+        <v>0.4604512769650384</v>
       </c>
       <c r="F2">
-        <v>73.26666666666667</v>
+        <v>72.83333333333333</v>
       </c>
       <c r="G2">
-        <v>61.79999999999999</v>
+        <v>61.16666666666666</v>
       </c>
       <c r="H2">
-        <v>0.1855447680690401</v>
+        <v>0.1907356948228882</v>
       </c>
       <c r="I2">
-        <v>0.3398886850033078</v>
+        <v>0.3370556199609722</v>
       </c>
       <c r="J2" t="s">
         <v>49</v>
       </c>
       <c r="K2">
-        <v>20.94222222222222</v>
+        <v>20.72222222222222</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
@@ -7903,31 +7929,31 @@
         <v>28</v>
       </c>
       <c r="C3">
-        <v>48.47777777777778</v>
+        <v>47.26666666666667</v>
       </c>
       <c r="D3">
-        <v>41.21111111111111</v>
+        <v>40.94444444444444</v>
       </c>
       <c r="E3">
-        <v>-0.1498968599587441</v>
+        <v>-0.1337564645039966</v>
       </c>
       <c r="F3">
-        <v>39.56666666666667</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="G3">
-        <v>54.8</v>
+        <v>51.93333333333334</v>
       </c>
       <c r="H3">
-        <v>-0.2779805352798054</v>
+        <v>-0.2458279845956355</v>
       </c>
       <c r="I3">
-        <v>0.274203165868446</v>
+        <v>0.2759235492310365</v>
       </c>
       <c r="J3" t="s">
         <v>50</v>
       </c>
       <c r="K3">
-        <v>30.81111111111111</v>
+        <v>30.36</v>
       </c>
       <c r="L3" t="b">
         <v>0</v>
@@ -7941,31 +7967,31 @@
         <v>29</v>
       </c>
       <c r="C4">
-        <v>56.06666666666666</v>
+        <v>55.76666666666667</v>
       </c>
       <c r="D4">
-        <v>57.17777777777778</v>
+        <v>57.2</v>
       </c>
       <c r="E4">
-        <v>0.01981767736821261</v>
+        <v>0.02570233114166154</v>
       </c>
       <c r="F4">
-        <v>54.96666666666667</v>
+        <v>55.06666666666666</v>
       </c>
       <c r="G4">
-        <v>60.73333333333333</v>
+        <v>60.43333333333334</v>
       </c>
       <c r="H4">
-        <v>-0.09495060373216235</v>
+        <v>-0.08880308880308896</v>
       </c>
       <c r="I4">
-        <v>0.2384309380350671</v>
+        <v>0.2400432069719468</v>
       </c>
       <c r="J4" t="s">
         <v>50</v>
       </c>
       <c r="K4">
-        <v>58.80888888888889</v>
+        <v>58.38444444444445</v>
       </c>
       <c r="L4" t="b">
         <v>0</v>
@@ -7979,31 +8005,31 @@
         <v>30</v>
       </c>
       <c r="C5">
-        <v>59.25555555555555</v>
+        <v>51.75555555555555</v>
       </c>
       <c r="D5">
-        <v>58.94444444444444</v>
+        <v>55.36666666666667</v>
       </c>
       <c r="E5">
-        <v>-0.005250328145509076</v>
+        <v>0.06977243452125403</v>
       </c>
       <c r="F5">
-        <v>68.53333333333332</v>
+        <v>63.96666666666667</v>
       </c>
       <c r="G5">
-        <v>65.03333333333333</v>
+        <v>60.06666666666666</v>
       </c>
       <c r="H5">
-        <v>0.05381855458739082</v>
+        <v>0.06492785793562716</v>
       </c>
       <c r="I5">
-        <v>0.3972232719815187</v>
+        <v>0.4212995367574185</v>
       </c>
       <c r="J5" t="s">
         <v>49</v>
       </c>
       <c r="K5">
-        <v>8.92</v>
+        <v>8.535555555555556</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
@@ -8017,31 +8043,31 @@
         <v>31</v>
       </c>
       <c r="C6">
-        <v>47.58888888888889</v>
+        <v>46.37777777777778</v>
       </c>
       <c r="D6">
-        <v>50.05555555555556</v>
+        <v>43.68888888888889</v>
       </c>
       <c r="E6">
-        <v>0.05183282745738982</v>
+        <v>-0.05797795879252521</v>
       </c>
       <c r="F6">
-        <v>62.90000000000001</v>
+        <v>41.3</v>
       </c>
       <c r="G6">
-        <v>77.63333333333333</v>
+        <v>71.2</v>
       </c>
       <c r="H6">
-        <v>-0.1897810218978101</v>
+        <v>-0.4199438202247191</v>
       </c>
       <c r="I6">
-        <v>0.9108715011909452</v>
+        <v>0.9981094299390325</v>
       </c>
       <c r="J6" t="s">
         <v>50</v>
       </c>
       <c r="K6">
-        <v>1.628888888888889</v>
+        <v>1.475555555555556</v>
       </c>
       <c r="L6" t="b">
         <v>1</v>
@@ -8058,46 +8084,46 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>57</v>
       </c>
     </row>
@@ -8109,40 +8135,40 @@
         <v>27</v>
       </c>
       <c r="C2">
-        <v>1.070870441110096</v>
+        <v>1.089776197332781</v>
       </c>
       <c r="D2">
-        <v>0.7632387060879151</v>
+        <v>0.7526217136513916</v>
       </c>
       <c r="E2">
-        <v>0.8886034333645982</v>
+        <v>0.8987943402270527</v>
       </c>
       <c r="F2">
-        <v>0.8606972590649574</v>
+        <v>0.8498256435013219</v>
       </c>
       <c r="G2">
-        <v>0.7043276950963847</v>
+        <v>0.7041045164080951</v>
       </c>
       <c r="H2">
-        <v>0.9792467550974214</v>
+        <v>1.003252634720878</v>
       </c>
       <c r="I2">
-        <v>1.50600656111246</v>
+        <v>1.516548950393869</v>
       </c>
       <c r="J2">
-        <v>0.9605914046171105</v>
+        <v>0.8961227420168701</v>
       </c>
       <c r="K2">
-        <v>0.9979082548121841</v>
+        <v>1.014588254814756</v>
       </c>
       <c r="L2">
-        <v>1.027292101142923</v>
+        <v>1.016298740947068</v>
       </c>
       <c r="M2">
-        <v>0.9670020257179713</v>
+        <v>0.9591079084968041</v>
       </c>
       <c r="N2">
-        <v>1.274215362775978</v>
+        <v>1.298958357489112</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -8153,40 +8179,40 @@
         <v>28</v>
       </c>
       <c r="C3">
-        <v>1.062902256186142</v>
+        <v>1.047568192994405</v>
       </c>
       <c r="D3">
-        <v>0.7569694334088459</v>
+        <v>0.7615032319907343</v>
       </c>
       <c r="E3">
-        <v>0.9269655070432998</v>
+        <v>0.9454506529482686</v>
       </c>
       <c r="F3">
-        <v>1.058506288579985</v>
+        <v>1.071855824755015</v>
       </c>
       <c r="G3">
-        <v>0.8250612035577399</v>
+        <v>0.832980101119964</v>
       </c>
       <c r="H3">
-        <v>1.010116324106268</v>
+        <v>0.9989537913983414</v>
       </c>
       <c r="I3">
-        <v>1.326306658992809</v>
+        <v>1.321731228983054</v>
       </c>
       <c r="J3">
-        <v>0.901371160515673</v>
+        <v>0.8897057727834016</v>
       </c>
       <c r="K3">
-        <v>0.8538312591729526</v>
+        <v>0.8290632959137302</v>
       </c>
       <c r="L3">
-        <v>1.002782918955907</v>
+        <v>1.005772126050592</v>
       </c>
       <c r="M3">
-        <v>1.050246768904466</v>
+        <v>1.048212790956162</v>
       </c>
       <c r="N3">
-        <v>1.224940220575912</v>
+        <v>1.247202990106334</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -8197,40 +8223,40 @@
         <v>29</v>
       </c>
       <c r="C4">
-        <v>1.054535743129976</v>
+        <v>1.059448338361174</v>
       </c>
       <c r="D4">
-        <v>0.7750694659227809</v>
+        <v>0.7802604728415531</v>
       </c>
       <c r="E4">
-        <v>0.9685071104470736</v>
+        <v>0.9732952914614011</v>
       </c>
       <c r="F4">
-        <v>1.150512591880149</v>
+        <v>1.154804786456557</v>
       </c>
       <c r="G4">
-        <v>0.8202870399905889</v>
+        <v>0.8267347990596985</v>
       </c>
       <c r="H4">
-        <v>1.081793668137913</v>
+        <v>1.078654753278625</v>
       </c>
       <c r="I4">
-        <v>1.40732946093065</v>
+        <v>1.402202949642265</v>
       </c>
       <c r="J4">
-        <v>0.8550062035360964</v>
+        <v>0.8493928104138359</v>
       </c>
       <c r="K4">
-        <v>0.7906223368882607</v>
+        <v>0.7819054896755805</v>
       </c>
       <c r="L4">
-        <v>0.8886381619650251</v>
+        <v>0.8948521436874101</v>
       </c>
       <c r="M4">
-        <v>1.042474847319326</v>
+        <v>1.025617305621519</v>
       </c>
       <c r="N4">
-        <v>1.165223369852161</v>
+        <v>1.172830859500381</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -8241,40 +8267,40 @@
         <v>30</v>
       </c>
       <c r="C5">
-        <v>1.22649143104026</v>
+        <v>1.241605696932803</v>
       </c>
       <c r="D5">
-        <v>0.8926328497362793</v>
+        <v>0.9289493276442028</v>
       </c>
       <c r="E5">
-        <v>1.06469830632306</v>
+        <v>1.056782595210506</v>
       </c>
       <c r="F5">
-        <v>0.9211864656367723</v>
+        <v>0.7910034883785935</v>
       </c>
       <c r="G5">
-        <v>0.579558585716298</v>
+        <v>0.5373686886278094</v>
       </c>
       <c r="H5">
-        <v>0.6926643189181574</v>
+        <v>0.7975156323889595</v>
       </c>
       <c r="I5">
-        <v>1.456958491016676</v>
+        <v>1.465482114119869</v>
       </c>
       <c r="J5">
-        <v>0.9215357718629864</v>
+        <v>0.9127069491424075</v>
       </c>
       <c r="K5">
-        <v>0.6011759667310625</v>
+        <v>0.5696042969488808</v>
       </c>
       <c r="L5">
-        <v>0.9670878943882227</v>
+        <v>0.9594184591297639</v>
       </c>
       <c r="M5">
-        <v>1.257753962370386</v>
+        <v>1.309536769137954</v>
       </c>
       <c r="N5">
-        <v>1.41825595625984</v>
+        <v>1.43002598233825</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -8285,40 +8311,40 @@
         <v>31</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.6257336627095772</v>
       </c>
       <c r="E6">
-        <v>3.347582985793593</v>
+        <v>2.011336032388664</v>
       </c>
       <c r="F6">
-        <v>0.9651100094932582</v>
+        <v>1.603749513941307</v>
       </c>
       <c r="G6">
-        <v>0.4167072972533723</v>
+        <v>0.5444915254237288</v>
       </c>
       <c r="H6">
-        <v>0.5408743702259061</v>
+        <v>0.653954802259887</v>
       </c>
       <c r="I6">
-        <v>0.6143344709897611</v>
+        <v>0.7062146892655368</v>
       </c>
       <c r="J6">
-        <v>0.5824800910125142</v>
+        <v>0.5395480225988701</v>
       </c>
       <c r="K6">
-        <v>0.3172436209978872</v>
+        <v>0.2627118644067797</v>
       </c>
       <c r="L6">
-        <v>0.4310092637737689</v>
+        <v>0.1899717514124294</v>
       </c>
       <c r="M6">
-        <v>0.4004550625711036</v>
+        <v>0.5522598870056498</v>
       </c>
       <c r="N6">
-        <v>4.384202827888835</v>
+        <v>0.3100282485875707</v>
       </c>
     </row>
   </sheetData>
@@ -8332,25 +8358,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -8364,7 +8390,7 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>46204</v>
       </c>
       <c r="E2">
@@ -8387,11 +8413,11 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>45839</v>
       </c>
       <c r="E3">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F3">
         <v>2025</v>
@@ -8410,11 +8436,11 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="2">
         <v>45992</v>
       </c>
       <c r="E4">
-        <v>81.5</v>
+        <v>81.2</v>
       </c>
       <c r="F4">
         <v>2025</v>
@@ -8433,11 +8459,11 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="2">
         <v>46143</v>
       </c>
       <c r="E5">
-        <v>72.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F5">
         <v>2026</v>
@@ -8456,11 +8482,11 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="2">
         <v>45108</v>
       </c>
       <c r="E6">
-        <v>69.7</v>
+        <v>70</v>
       </c>
       <c r="F6">
         <v>2023</v>
@@ -8479,7 +8505,7 @@
       <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="2">
         <v>45108</v>
       </c>
       <c r="E7">
@@ -8502,11 +8528,11 @@
       <c r="C8">
         <v>2</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="2">
         <v>45078</v>
       </c>
       <c r="E8">
-        <v>81.5</v>
+        <v>79.7</v>
       </c>
       <c r="F8">
         <v>2023</v>
@@ -8525,11 +8551,11 @@
       <c r="C9">
         <v>3</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="2">
         <v>45047</v>
       </c>
       <c r="E9">
-        <v>77.3</v>
+        <v>75.5</v>
       </c>
       <c r="F9">
         <v>2023</v>
@@ -8548,11 +8574,11 @@
       <c r="C10">
         <v>4</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="2">
         <v>45017</v>
       </c>
       <c r="E10">
-        <v>73.5</v>
+        <v>72.2</v>
       </c>
       <c r="F10">
         <v>2023</v>
@@ -8571,7 +8597,7 @@
       <c r="C11">
         <v>5</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="2">
         <v>44927</v>
       </c>
       <c r="E11">
@@ -8594,7 +8620,7 @@
       <c r="C12">
         <v>1</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="2">
         <v>45108</v>
       </c>
       <c r="E12">
@@ -8617,11 +8643,11 @@
       <c r="C13">
         <v>2</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="2">
         <v>45839</v>
       </c>
       <c r="E13">
-        <v>84.2</v>
+        <v>83.5</v>
       </c>
       <c r="F13">
         <v>2025</v>
@@ -8640,11 +8666,11 @@
       <c r="C14">
         <v>3</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="2">
         <v>46204</v>
       </c>
       <c r="E14">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F14">
         <v>2026</v>
@@ -8663,11 +8689,11 @@
       <c r="C15">
         <v>4</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="2">
         <v>45078</v>
       </c>
       <c r="E15">
-        <v>79.8</v>
+        <v>78.2</v>
       </c>
       <c r="F15">
         <v>2023</v>
@@ -8686,11 +8712,11 @@
       <c r="C16">
         <v>5</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="2">
         <v>45261</v>
       </c>
       <c r="E16">
-        <v>75.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F16">
         <v>2023</v>
@@ -8709,7 +8735,7 @@
       <c r="C17">
         <v>1</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="2">
         <v>44927</v>
       </c>
       <c r="E17">
@@ -8732,11 +8758,11 @@
       <c r="C18">
         <v>2</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="2">
         <v>45839</v>
       </c>
       <c r="E18">
-        <v>99.90000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="F18">
         <v>2025</v>
@@ -8755,11 +8781,11 @@
       <c r="C19">
         <v>3</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="2">
         <v>46204</v>
       </c>
       <c r="E19">
-        <v>93.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="F19">
         <v>2026</v>
@@ -8778,11 +8804,11 @@
       <c r="C20">
         <v>4</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="2">
         <v>45992</v>
       </c>
       <c r="E20">
-        <v>87.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F20">
         <v>2025</v>
@@ -8801,11 +8827,11 @@
       <c r="C21">
         <v>5</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="2">
         <v>46174</v>
       </c>
       <c r="E21">
-        <v>78.8</v>
+        <v>76.8</v>
       </c>
       <c r="F21">
         <v>2026</v>
@@ -8824,17 +8850,17 @@
       <c r="C22">
         <v>1</v>
       </c>
-      <c r="D22" s="1">
-        <v>46235</v>
+      <c r="D22" s="2">
+        <v>45839</v>
       </c>
       <c r="E22">
         <v>100</v>
       </c>
       <c r="F22">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -8847,17 +8873,17 @@
       <c r="C23">
         <v>2</v>
       </c>
-      <c r="D23" s="1">
-        <v>45839</v>
+      <c r="D23" s="2">
+        <v>45809</v>
       </c>
       <c r="E23">
-        <v>94.5</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F23">
         <v>2025</v>
       </c>
       <c r="G23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -8870,17 +8896,17 @@
       <c r="C24">
         <v>3</v>
       </c>
-      <c r="D24" s="1">
-        <v>45870</v>
+      <c r="D24" s="2">
+        <v>45962</v>
       </c>
       <c r="E24">
-        <v>89.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="F24">
         <v>2025</v>
       </c>
       <c r="G24" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -8893,17 +8919,17 @@
       <c r="C25">
         <v>4</v>
       </c>
-      <c r="D25" s="1">
-        <v>45809</v>
+      <c r="D25" s="2">
+        <v>45778</v>
       </c>
       <c r="E25">
-        <v>83.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F25">
         <v>2025</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -8916,17 +8942,17 @@
       <c r="C26">
         <v>5</v>
       </c>
-      <c r="D26" s="1">
-        <v>45352</v>
+      <c r="D26" s="2">
+        <v>45870</v>
       </c>
       <c r="E26">
-        <v>73.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F26">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G26" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -8940,31 +8966,31 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>48</v>
       </c>
     </row>
@@ -8976,22 +9002,22 @@
         <v>27</v>
       </c>
       <c r="C2">
-        <v>65.67777777777778</v>
+        <v>65.44444444444444</v>
       </c>
       <c r="D2">
-        <v>0.4616716122650841</v>
+        <v>0.4604512769650384</v>
       </c>
       <c r="E2">
-        <v>0.1855447680690401</v>
+        <v>0.1907356948228882</v>
       </c>
       <c r="F2">
-        <v>0.3398886850033078</v>
+        <v>0.3370556199609722</v>
       </c>
       <c r="G2">
         <v>7</v>
       </c>
       <c r="H2">
-        <v>1.50600656111246</v>
+        <v>1.516548950393869</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -9005,22 +9031,22 @@
         <v>28</v>
       </c>
       <c r="C3">
-        <v>41.21111111111111</v>
+        <v>40.94444444444444</v>
       </c>
       <c r="D3">
-        <v>-0.1498968599587441</v>
+        <v>-0.1337564645039966</v>
       </c>
       <c r="E3">
-        <v>-0.2779805352798054</v>
+        <v>-0.2458279845956355</v>
       </c>
       <c r="F3">
-        <v>0.274203165868446</v>
+        <v>0.2759235492310365</v>
       </c>
       <c r="G3">
         <v>7</v>
       </c>
       <c r="H3">
-        <v>1.326306658992809</v>
+        <v>1.321731228983054</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -9034,22 +9060,22 @@
         <v>29</v>
       </c>
       <c r="C4">
-        <v>57.17777777777778</v>
+        <v>57.2</v>
       </c>
       <c r="D4">
-        <v>0.01981767736821261</v>
+        <v>0.02570233114166154</v>
       </c>
       <c r="E4">
-        <v>-0.09495060373216235</v>
+        <v>-0.08880308880308896</v>
       </c>
       <c r="F4">
-        <v>0.2384309380350671</v>
+        <v>0.2400432069719468</v>
       </c>
       <c r="G4">
         <v>7</v>
       </c>
       <c r="H4">
-        <v>1.40732946093065</v>
+        <v>1.402202949642265</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -9063,22 +9089,22 @@
         <v>30</v>
       </c>
       <c r="C5">
-        <v>58.94444444444444</v>
+        <v>55.36666666666667</v>
       </c>
       <c r="D5">
-        <v>-0.005250328145509076</v>
+        <v>0.06977243452125403</v>
       </c>
       <c r="E5">
-        <v>0.05381855458739082</v>
+        <v>0.06492785793562716</v>
       </c>
       <c r="F5">
-        <v>0.3972232719815187</v>
+        <v>0.4212995367574185</v>
       </c>
       <c r="G5">
         <v>7</v>
       </c>
       <c r="H5">
-        <v>1.456958491016676</v>
+        <v>1.465482114119869</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -9092,22 +9118,22 @@
         <v>31</v>
       </c>
       <c r="C6">
-        <v>50.05555555555556</v>
+        <v>43.68888888888889</v>
       </c>
       <c r="D6">
-        <v>0.05183282745738982</v>
+        <v>-0.05797795879252521</v>
       </c>
       <c r="E6">
-        <v>-0.1897810218978101</v>
+        <v>-0.4199438202247191</v>
       </c>
       <c r="F6">
-        <v>0.9108715011909452</v>
+        <v>0.9981094299390325</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>4.384202827888835</v>
+        <v>4</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -9124,39 +9150,39 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>44927</v>
       </c>
       <c r="B2">
@@ -9175,7 +9201,7 @@
         <v>27</v>
       </c>
       <c r="G2">
-        <v>28.8</v>
+        <v>28.2</v>
       </c>
       <c r="H2" t="s">
         <v>32</v>
@@ -9188,7 +9214,7 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>44958</v>
       </c>
       <c r="B3">
@@ -9207,7 +9233,7 @@
         <v>27</v>
       </c>
       <c r="G3">
-        <v>18.5</v>
+        <v>16.9</v>
       </c>
       <c r="H3" t="s">
         <v>32</v>
@@ -9220,7 +9246,7 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>44986</v>
       </c>
       <c r="B4">
@@ -9239,7 +9265,7 @@
         <v>27</v>
       </c>
       <c r="G4">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="H4" t="s">
         <v>32</v>
@@ -9252,7 +9278,7 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>45017</v>
       </c>
       <c r="B5">
@@ -9271,7 +9297,7 @@
         <v>27</v>
       </c>
       <c r="G5">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="H5" t="s">
         <v>32</v>
@@ -9284,7 +9310,7 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>45047</v>
       </c>
       <c r="B6">
@@ -9303,7 +9329,7 @@
         <v>27</v>
       </c>
       <c r="G6">
-        <v>20.2</v>
+        <v>20.7</v>
       </c>
       <c r="H6" t="s">
         <v>32</v>
@@ -9316,7 +9342,7 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>45078</v>
       </c>
       <c r="B7">
@@ -9335,7 +9361,7 @@
         <v>27</v>
       </c>
       <c r="G7">
-        <v>25.3</v>
+        <v>24.9</v>
       </c>
       <c r="H7" t="s">
         <v>32</v>
@@ -9348,7 +9374,7 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>45108</v>
       </c>
       <c r="B8">
@@ -9367,7 +9393,7 @@
         <v>27</v>
       </c>
       <c r="G8">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="H8" t="s">
         <v>32</v>
@@ -9380,7 +9406,7 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>45139</v>
       </c>
       <c r="B9">
@@ -9399,7 +9425,7 @@
         <v>27</v>
       </c>
       <c r="G9">
-        <v>19.9</v>
+        <v>19.3</v>
       </c>
       <c r="H9" t="s">
         <v>32</v>
@@ -9412,7 +9438,7 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>45170</v>
       </c>
       <c r="B10">
@@ -9431,7 +9457,7 @@
         <v>27</v>
       </c>
       <c r="G10">
-        <v>17.6</v>
+        <v>16.9</v>
       </c>
       <c r="H10" t="s">
         <v>32</v>
@@ -9444,7 +9470,7 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <v>45200</v>
       </c>
       <c r="B11">
@@ -9463,7 +9489,7 @@
         <v>27</v>
       </c>
       <c r="G11">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="H11" t="s">
         <v>32</v>
@@ -9476,7 +9502,7 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <v>45231</v>
       </c>
       <c r="B12">
@@ -9495,7 +9521,7 @@
         <v>27</v>
       </c>
       <c r="G12">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
       <c r="H12" t="s">
         <v>32</v>
@@ -9508,7 +9534,7 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <v>45261</v>
       </c>
       <c r="B13">
@@ -9527,7 +9553,7 @@
         <v>27</v>
       </c>
       <c r="G13">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="H13" t="s">
         <v>32</v>
@@ -9540,7 +9566,7 @@
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="1">
+      <c r="A14" s="2">
         <v>45292</v>
       </c>
       <c r="B14">
@@ -9559,7 +9585,7 @@
         <v>27</v>
       </c>
       <c r="G14">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="H14" t="s">
         <v>32</v>
@@ -9572,7 +9598,7 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="1">
+      <c r="A15" s="2">
         <v>45323</v>
       </c>
       <c r="B15">
@@ -9591,7 +9617,7 @@
         <v>27</v>
       </c>
       <c r="G15">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="H15" t="s">
         <v>32</v>
@@ -9604,7 +9630,7 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="1">
+      <c r="A16" s="2">
         <v>45352</v>
       </c>
       <c r="B16">
@@ -9623,7 +9649,7 @@
         <v>27</v>
       </c>
       <c r="G16">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="H16" t="s">
         <v>32</v>
@@ -9636,7 +9662,7 @@
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="1">
+      <c r="A17" s="2">
         <v>45383</v>
       </c>
       <c r="B17">
@@ -9655,7 +9681,7 @@
         <v>27</v>
       </c>
       <c r="G17">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="H17" t="s">
         <v>32</v>
@@ -9668,7 +9694,7 @@
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="1">
+      <c r="A18" s="2">
         <v>45413</v>
       </c>
       <c r="B18">
@@ -9687,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="G18">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="H18" t="s">
         <v>32</v>
@@ -9700,7 +9726,7 @@
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="1">
+      <c r="A19" s="2">
         <v>45444</v>
       </c>
       <c r="B19">
@@ -9719,7 +9745,7 @@
         <v>27</v>
       </c>
       <c r="G19">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H19" t="s">
         <v>32</v>
@@ -9732,7 +9758,7 @@
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="1">
+      <c r="A20" s="2">
         <v>45474</v>
       </c>
       <c r="B20">
@@ -9751,7 +9777,7 @@
         <v>27</v>
       </c>
       <c r="G20">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="H20" t="s">
         <v>32</v>
@@ -9764,7 +9790,7 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="1">
+      <c r="A21" s="2">
         <v>45505</v>
       </c>
       <c r="B21">
@@ -9783,7 +9809,7 @@
         <v>27</v>
       </c>
       <c r="G21">
-        <v>13.1</v>
+        <v>11</v>
       </c>
       <c r="H21" t="s">
         <v>32</v>
@@ -9796,7 +9822,7 @@
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="1">
+      <c r="A22" s="2">
         <v>45536</v>
       </c>
       <c r="B22">
@@ -9815,7 +9841,7 @@
         <v>27</v>
       </c>
       <c r="G22">
-        <v>18.1</v>
+        <v>19.2</v>
       </c>
       <c r="H22" t="s">
         <v>32</v>
@@ -9828,7 +9854,7 @@
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="1">
+      <c r="A23" s="2">
         <v>45566</v>
       </c>
       <c r="B23">
@@ -9847,7 +9873,7 @@
         <v>27</v>
       </c>
       <c r="G23">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="H23" t="s">
         <v>32</v>
@@ -9860,7 +9886,7 @@
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="1">
+      <c r="A24" s="2">
         <v>45597</v>
       </c>
       <c r="B24">
@@ -9879,7 +9905,7 @@
         <v>27</v>
       </c>
       <c r="G24">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="H24" t="s">
         <v>32</v>
@@ -9892,7 +9918,7 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="1">
+      <c r="A25" s="2">
         <v>45627</v>
       </c>
       <c r="B25">
@@ -9911,7 +9937,7 @@
         <v>27</v>
       </c>
       <c r="G25">
-        <v>15.2</v>
+        <v>16.1</v>
       </c>
       <c r="H25" t="s">
         <v>32</v>
@@ -9924,7 +9950,7 @@
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="1">
+      <c r="A26" s="2">
         <v>45658</v>
       </c>
       <c r="B26">
@@ -9943,7 +9969,7 @@
         <v>27</v>
       </c>
       <c r="G26">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="H26" t="s">
         <v>32</v>
@@ -9956,7 +9982,7 @@
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="1">
+      <c r="A27" s="2">
         <v>45689</v>
       </c>
       <c r="B27">
@@ -9975,7 +10001,7 @@
         <v>27</v>
       </c>
       <c r="G27">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="H27" t="s">
         <v>32</v>
@@ -9988,7 +10014,7 @@
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="1">
+      <c r="A28" s="2">
         <v>45717</v>
       </c>
       <c r="B28">
@@ -10007,7 +10033,7 @@
         <v>27</v>
       </c>
       <c r="G28">
-        <v>11.9</v>
+        <v>13</v>
       </c>
       <c r="H28" t="s">
         <v>32</v>
@@ -10020,7 +10046,7 @@
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="1">
+      <c r="A29" s="2">
         <v>45748</v>
       </c>
       <c r="B29">
@@ -10039,7 +10065,7 @@
         <v>27</v>
       </c>
       <c r="G29">
-        <v>16.1</v>
+        <v>15.4</v>
       </c>
       <c r="H29" t="s">
         <v>32</v>
@@ -10052,7 +10078,7 @@
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="1">
+      <c r="A30" s="2">
         <v>45778</v>
       </c>
       <c r="B30">
@@ -10071,7 +10097,7 @@
         <v>27</v>
       </c>
       <c r="G30">
-        <v>21.7</v>
+        <v>20.1</v>
       </c>
       <c r="H30" t="s">
         <v>32</v>
@@ -10084,7 +10110,7 @@
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="1">
+      <c r="A31" s="2">
         <v>45809</v>
       </c>
       <c r="B31">
@@ -10103,7 +10129,7 @@
         <v>27</v>
       </c>
       <c r="G31">
-        <v>24</v>
+        <v>24.9</v>
       </c>
       <c r="H31" t="s">
         <v>32</v>
@@ -10116,7 +10142,7 @@
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="1">
+      <c r="A32" s="2">
         <v>45839</v>
       </c>
       <c r="B32">
@@ -10135,7 +10161,7 @@
         <v>27</v>
       </c>
       <c r="G32">
-        <v>36.6</v>
+        <v>36.4</v>
       </c>
       <c r="H32" t="s">
         <v>32</v>
@@ -10148,7 +10174,7 @@
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="1">
+      <c r="A33" s="2">
         <v>45870</v>
       </c>
       <c r="B33">
@@ -10167,7 +10193,7 @@
         <v>27</v>
       </c>
       <c r="G33">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="H33" t="s">
         <v>32</v>
@@ -10180,7 +10206,7 @@
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="1">
+      <c r="A34" s="2">
         <v>45901</v>
       </c>
       <c r="B34">
@@ -10199,7 +10225,7 @@
         <v>27</v>
       </c>
       <c r="G34">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="H34" t="s">
         <v>32</v>
@@ -10212,7 +10238,7 @@
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="1">
+      <c r="A35" s="2">
         <v>45931</v>
       </c>
       <c r="B35">
@@ -10231,7 +10257,7 @@
         <v>27</v>
       </c>
       <c r="G35">
-        <v>23.2</v>
+        <v>22.5</v>
       </c>
       <c r="H35" t="s">
         <v>32</v>
@@ -10244,7 +10270,7 @@
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="1">
+      <c r="A36" s="2">
         <v>45962</v>
       </c>
       <c r="B36">
@@ -10263,7 +10289,7 @@
         <v>27</v>
       </c>
       <c r="G36">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="H36" t="s">
         <v>32</v>
@@ -10276,7 +10302,7 @@
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="1">
+      <c r="A37" s="2">
         <v>45992</v>
       </c>
       <c r="B37">
@@ -10295,7 +10321,7 @@
         <v>27</v>
       </c>
       <c r="G37">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="H37" t="s">
         <v>32</v>
@@ -10308,7 +10334,7 @@
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="1">
+      <c r="A38" s="2">
         <v>46023</v>
       </c>
       <c r="B38">
@@ -10327,7 +10353,7 @@
         <v>27</v>
       </c>
       <c r="G38">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="H38" t="s">
         <v>32</v>
@@ -10340,7 +10366,7 @@
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="1">
+      <c r="A39" s="2">
         <v>46054</v>
       </c>
       <c r="B39">
@@ -10359,7 +10385,7 @@
         <v>27</v>
       </c>
       <c r="G39">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="H39" t="s">
         <v>32</v>
@@ -10372,7 +10398,7 @@
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="1">
+      <c r="A40" s="2">
         <v>46082</v>
       </c>
       <c r="B40">
@@ -10391,7 +10417,7 @@
         <v>27</v>
       </c>
       <c r="G40">
-        <v>23.8</v>
+        <v>24.9</v>
       </c>
       <c r="H40" t="s">
         <v>32</v>
@@ -10404,7 +10430,7 @@
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="1">
+      <c r="A41" s="2">
         <v>46113</v>
       </c>
       <c r="B41">
@@ -10423,7 +10449,7 @@
         <v>27</v>
       </c>
       <c r="G41">
-        <v>27.7</v>
+        <v>26.4</v>
       </c>
       <c r="H41" t="s">
         <v>32</v>
@@ -10436,7 +10462,7 @@
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="1">
+      <c r="A42" s="2">
         <v>46143</v>
       </c>
       <c r="B42">
@@ -10455,7 +10481,7 @@
         <v>27</v>
       </c>
       <c r="G42">
-        <v>30.7</v>
+        <v>29.9</v>
       </c>
       <c r="H42" t="s">
         <v>32</v>
@@ -10468,7 +10494,7 @@
       </c>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="1">
+      <c r="A43" s="2">
         <v>46174</v>
       </c>
       <c r="B43">
@@ -10487,7 +10513,7 @@
         <v>27</v>
       </c>
       <c r="G43">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="H43" t="s">
         <v>32</v>
@@ -10500,7 +10526,7 @@
       </c>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="1">
+      <c r="A44" s="2">
         <v>46204</v>
       </c>
       <c r="B44">
@@ -10519,7 +10545,7 @@
         <v>27</v>
       </c>
       <c r="G44">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="H44" t="s">
         <v>32</v>
@@ -10532,7 +10558,7 @@
       </c>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="1">
+      <c r="A45" s="2">
         <v>46235</v>
       </c>
       <c r="B45">
@@ -10551,7 +10577,7 @@
         <v>27</v>
       </c>
       <c r="G45">
-        <v>27.1</v>
+        <v>25.4</v>
       </c>
       <c r="H45" t="s">
         <v>32</v>
@@ -10564,7 +10590,7 @@
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="1">
+      <c r="A46" s="2">
         <v>46266</v>
       </c>
       <c r="B46">
@@ -10583,7 +10609,7 @@
         <v>27</v>
       </c>
       <c r="G46">
-        <v>23.8</v>
+        <v>24.9</v>
       </c>
       <c r="H46" t="s">
         <v>32</v>
@@ -10596,7 +10622,7 @@
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="1">
+      <c r="A47" s="2">
         <v>44927</v>
       </c>
       <c r="B47">
@@ -10615,7 +10641,7 @@
         <v>28</v>
       </c>
       <c r="G47">
-        <v>42.9</v>
+        <v>42.7</v>
       </c>
       <c r="H47" t="s">
         <v>33</v>
@@ -10628,7 +10654,7 @@
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="1">
+      <c r="A48" s="2">
         <v>44958</v>
       </c>
       <c r="B48">
@@ -10647,7 +10673,7 @@
         <v>28</v>
       </c>
       <c r="G48">
-        <v>30.7</v>
+        <v>30.2</v>
       </c>
       <c r="H48" t="s">
         <v>33</v>
@@ -10660,7 +10686,7 @@
       </c>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="1">
+      <c r="A49" s="2">
         <v>44986</v>
       </c>
       <c r="B49">
@@ -10679,7 +10705,7 @@
         <v>28</v>
       </c>
       <c r="G49">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="H49" t="s">
         <v>33</v>
@@ -10692,7 +10718,7 @@
       </c>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="1">
+      <c r="A50" s="2">
         <v>45017</v>
       </c>
       <c r="B50">
@@ -10711,7 +10737,7 @@
         <v>28</v>
       </c>
       <c r="G50">
-        <v>43.8</v>
+        <v>43.1</v>
       </c>
       <c r="H50" t="s">
         <v>33</v>
@@ -10724,7 +10750,7 @@
       </c>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="1">
+      <c r="A51" s="2">
         <v>45047</v>
       </c>
       <c r="B51">
@@ -10743,7 +10769,7 @@
         <v>28</v>
       </c>
       <c r="G51">
-        <v>46.1</v>
+        <v>45.3</v>
       </c>
       <c r="H51" t="s">
         <v>33</v>
@@ -10756,7 +10782,7 @@
       </c>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="1">
+      <c r="A52" s="2">
         <v>45078</v>
       </c>
       <c r="B52">
@@ -10775,7 +10801,7 @@
         <v>28</v>
       </c>
       <c r="G52">
-        <v>48.8</v>
+        <v>47.4</v>
       </c>
       <c r="H52" t="s">
         <v>33</v>
@@ -10788,7 +10814,7 @@
       </c>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="1">
+      <c r="A53" s="2">
         <v>45108</v>
       </c>
       <c r="B53">
@@ -10807,7 +10833,7 @@
         <v>28</v>
       </c>
       <c r="G53">
-        <v>60</v>
+        <v>59.7</v>
       </c>
       <c r="H53" t="s">
         <v>33</v>
@@ -10820,7 +10846,7 @@
       </c>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="1">
+      <c r="A54" s="2">
         <v>45139</v>
       </c>
       <c r="B54">
@@ -10839,7 +10865,7 @@
         <v>28</v>
       </c>
       <c r="G54">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="H54" t="s">
         <v>33</v>
@@ -10852,7 +10878,7 @@
       </c>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="1">
+      <c r="A55" s="2">
         <v>45170</v>
       </c>
       <c r="B55">
@@ -10871,7 +10897,7 @@
         <v>28</v>
       </c>
       <c r="G55">
-        <v>33.3</v>
+        <v>32.3</v>
       </c>
       <c r="H55" t="s">
         <v>33</v>
@@ -10884,7 +10910,7 @@
       </c>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="1">
+      <c r="A56" s="2">
         <v>45200</v>
       </c>
       <c r="B56">
@@ -10903,7 +10929,7 @@
         <v>28</v>
       </c>
       <c r="G56">
-        <v>34</v>
+        <v>33.4</v>
       </c>
       <c r="H56" t="s">
         <v>33</v>
@@ -10916,7 +10942,7 @@
       </c>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="1">
+      <c r="A57" s="2">
         <v>45231</v>
       </c>
       <c r="B57">
@@ -10935,7 +10961,7 @@
         <v>28</v>
       </c>
       <c r="G57">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="H57" t="s">
         <v>33</v>
@@ -10948,7 +10974,7 @@
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="1">
+      <c r="A58" s="2">
         <v>45261</v>
       </c>
       <c r="B58">
@@ -10967,7 +10993,7 @@
         <v>28</v>
       </c>
       <c r="G58">
-        <v>41.9</v>
+        <v>42.2</v>
       </c>
       <c r="H58" t="s">
         <v>33</v>
@@ -10980,7 +11006,7 @@
       </c>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="1">
+      <c r="A59" s="2">
         <v>45292</v>
       </c>
       <c r="B59">
@@ -10999,7 +11025,7 @@
         <v>28</v>
       </c>
       <c r="G59">
-        <v>33</v>
+        <v>30.5</v>
       </c>
       <c r="H59" t="s">
         <v>33</v>
@@ -11012,7 +11038,7 @@
       </c>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="1">
+      <c r="A60" s="2">
         <v>45323</v>
       </c>
       <c r="B60">
@@ -11031,7 +11057,7 @@
         <v>28</v>
       </c>
       <c r="G60">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="H60" t="s">
         <v>33</v>
@@ -11044,7 +11070,7 @@
       </c>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="1">
+      <c r="A61" s="2">
         <v>45352</v>
       </c>
       <c r="B61">
@@ -11063,7 +11089,7 @@
         <v>28</v>
       </c>
       <c r="G61">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="H61" t="s">
         <v>33</v>
@@ -11076,7 +11102,7 @@
       </c>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="1">
+      <c r="A62" s="2">
         <v>45383</v>
       </c>
       <c r="B62">
@@ -11095,7 +11121,7 @@
         <v>28</v>
       </c>
       <c r="G62">
-        <v>28</v>
+        <v>28.4</v>
       </c>
       <c r="H62" t="s">
         <v>33</v>
@@ -11108,7 +11134,7 @@
       </c>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="1">
+      <c r="A63" s="2">
         <v>45413</v>
       </c>
       <c r="B63">
@@ -11127,7 +11153,7 @@
         <v>28</v>
       </c>
       <c r="G63">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="H63" t="s">
         <v>33</v>
@@ -11140,7 +11166,7 @@
       </c>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="1">
+      <c r="A64" s="2">
         <v>45444</v>
       </c>
       <c r="B64">
@@ -11159,7 +11185,7 @@
         <v>28</v>
       </c>
       <c r="G64">
-        <v>17.1</v>
+        <v>16.8</v>
       </c>
       <c r="H64" t="s">
         <v>33</v>
@@ -11172,7 +11198,7 @@
       </c>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="1">
+      <c r="A65" s="2">
         <v>45474</v>
       </c>
       <c r="B65">
@@ -11191,7 +11217,7 @@
         <v>28</v>
       </c>
       <c r="G65">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="H65" t="s">
         <v>33</v>
@@ -11204,7 +11230,7 @@
       </c>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="1">
+      <c r="A66" s="2">
         <v>45505</v>
       </c>
       <c r="B66">
@@ -11223,7 +11249,7 @@
         <v>28</v>
       </c>
       <c r="G66">
-        <v>19.3</v>
+        <v>18.1</v>
       </c>
       <c r="H66" t="s">
         <v>33</v>
@@ -11236,7 +11262,7 @@
       </c>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="1">
+      <c r="A67" s="2">
         <v>45536</v>
       </c>
       <c r="B67">
@@ -11255,7 +11281,7 @@
         <v>28</v>
       </c>
       <c r="G67">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="H67" t="s">
         <v>33</v>
@@ -11268,7 +11294,7 @@
       </c>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="1">
+      <c r="A68" s="2">
         <v>45566</v>
       </c>
       <c r="B68">
@@ -11287,7 +11313,7 @@
         <v>28</v>
       </c>
       <c r="G68">
-        <v>27.4</v>
+        <v>27</v>
       </c>
       <c r="H68" t="s">
         <v>33</v>
@@ -11300,7 +11326,7 @@
       </c>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="1">
+      <c r="A69" s="2">
         <v>45597</v>
       </c>
       <c r="B69">
@@ -11319,7 +11345,7 @@
         <v>28</v>
       </c>
       <c r="G69">
-        <v>29.2</v>
+        <v>27.8</v>
       </c>
       <c r="H69" t="s">
         <v>33</v>
@@ -11332,7 +11358,7 @@
       </c>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="1">
+      <c r="A70" s="2">
         <v>45627</v>
       </c>
       <c r="B70">
@@ -11351,7 +11377,7 @@
         <v>28</v>
       </c>
       <c r="G70">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="H70" t="s">
         <v>33</v>
@@ -11364,7 +11390,7 @@
       </c>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="1">
+      <c r="A71" s="2">
         <v>45658</v>
       </c>
       <c r="B71">
@@ -11383,7 +11409,7 @@
         <v>28</v>
       </c>
       <c r="G71">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="H71" t="s">
         <v>33</v>
@@ -11396,7 +11422,7 @@
       </c>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="1">
+      <c r="A72" s="2">
         <v>45689</v>
       </c>
       <c r="B72">
@@ -11415,7 +11441,7 @@
         <v>28</v>
       </c>
       <c r="G72">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="H72" t="s">
         <v>33</v>
@@ -11428,7 +11454,7 @@
       </c>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="1">
+      <c r="A73" s="2">
         <v>45717</v>
       </c>
       <c r="B73">
@@ -11447,7 +11473,7 @@
         <v>28</v>
       </c>
       <c r="G73">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="H73" t="s">
         <v>33</v>
@@ -11460,7 +11486,7 @@
       </c>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="1">
+      <c r="A74" s="2">
         <v>45748</v>
       </c>
       <c r="B74">
@@ -11479,7 +11505,7 @@
         <v>28</v>
       </c>
       <c r="G74">
-        <v>30.7</v>
+        <v>30.5</v>
       </c>
       <c r="H74" t="s">
         <v>33</v>
@@ -11492,7 +11518,7 @@
       </c>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="1">
+      <c r="A75" s="2">
         <v>45778</v>
       </c>
       <c r="B75">
@@ -11511,7 +11537,7 @@
         <v>28</v>
       </c>
       <c r="G75">
-        <v>30.4</v>
+        <v>30.8</v>
       </c>
       <c r="H75" t="s">
         <v>33</v>
@@ -11524,7 +11550,7 @@
       </c>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="1">
+      <c r="A76" s="2">
         <v>45809</v>
       </c>
       <c r="B76">
@@ -11543,7 +11569,7 @@
         <v>28</v>
       </c>
       <c r="G76">
-        <v>35.5</v>
+        <v>34.4</v>
       </c>
       <c r="H76" t="s">
         <v>33</v>
@@ -11556,7 +11582,7 @@
       </c>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="1">
+      <c r="A77" s="2">
         <v>45839</v>
       </c>
       <c r="B77">
@@ -11575,7 +11601,7 @@
         <v>28</v>
       </c>
       <c r="G77">
-        <v>39.9</v>
+        <v>37.6</v>
       </c>
       <c r="H77" t="s">
         <v>33</v>
@@ -11588,7 +11614,7 @@
       </c>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="1">
+      <c r="A78" s="2">
         <v>45870</v>
       </c>
       <c r="B78">
@@ -11607,7 +11633,7 @@
         <v>28</v>
       </c>
       <c r="G78">
-        <v>29.5</v>
+        <v>29.1</v>
       </c>
       <c r="H78" t="s">
         <v>33</v>
@@ -11620,7 +11646,7 @@
       </c>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="1">
+      <c r="A79" s="2">
         <v>45901</v>
       </c>
       <c r="B79">
@@ -11639,7 +11665,7 @@
         <v>28</v>
       </c>
       <c r="G79">
-        <v>28.3</v>
+        <v>26.4</v>
       </c>
       <c r="H79" t="s">
         <v>33</v>
@@ -11652,7 +11678,7 @@
       </c>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="1">
+      <c r="A80" s="2">
         <v>45931</v>
       </c>
       <c r="B80">
@@ -11671,7 +11697,7 @@
         <v>28</v>
       </c>
       <c r="G80">
-        <v>34.2</v>
+        <v>33.2</v>
       </c>
       <c r="H80" t="s">
         <v>33</v>
@@ -11684,7 +11710,7 @@
       </c>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="1">
+      <c r="A81" s="2">
         <v>45962</v>
       </c>
       <c r="B81">
@@ -11703,7 +11729,7 @@
         <v>28</v>
       </c>
       <c r="G81">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="H81" t="s">
         <v>33</v>
@@ -11716,7 +11742,7 @@
       </c>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="1">
+      <c r="A82" s="2">
         <v>45992</v>
       </c>
       <c r="B82">
@@ -11735,7 +11761,7 @@
         <v>28</v>
       </c>
       <c r="G82">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="H82" t="s">
         <v>33</v>
@@ -11748,7 +11774,7 @@
       </c>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="1">
+      <c r="A83" s="2">
         <v>46023</v>
       </c>
       <c r="B83">
@@ -11767,7 +11793,7 @@
         <v>28</v>
       </c>
       <c r="G83">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="H83" t="s">
         <v>33</v>
@@ -11780,7 +11806,7 @@
       </c>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="1">
+      <c r="A84" s="2">
         <v>46054</v>
       </c>
       <c r="B84">
@@ -11799,7 +11825,7 @@
         <v>28</v>
       </c>
       <c r="G84">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="H84" t="s">
         <v>33</v>
@@ -11812,7 +11838,7 @@
       </c>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="1">
+      <c r="A85" s="2">
         <v>46082</v>
       </c>
       <c r="B85">
@@ -11831,7 +11857,7 @@
         <v>28</v>
       </c>
       <c r="G85">
-        <v>21.9</v>
+        <v>22.7</v>
       </c>
       <c r="H85" t="s">
         <v>33</v>
@@ -11844,7 +11870,7 @@
       </c>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="1">
+      <c r="A86" s="2">
         <v>46113</v>
       </c>
       <c r="B86">
@@ -11863,7 +11889,7 @@
         <v>28</v>
       </c>
       <c r="G86">
-        <v>26.5</v>
+        <v>25.2</v>
       </c>
       <c r="H86" t="s">
         <v>33</v>
@@ -11876,7 +11902,7 @@
       </c>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="1">
+      <c r="A87" s="2">
         <v>46143</v>
       </c>
       <c r="B87">
@@ -11895,7 +11921,7 @@
         <v>28</v>
       </c>
       <c r="G87">
-        <v>28.6</v>
+        <v>28</v>
       </c>
       <c r="H87" t="s">
         <v>33</v>
@@ -11908,7 +11934,7 @@
       </c>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="1">
+      <c r="A88" s="2">
         <v>46174</v>
       </c>
       <c r="B88">
@@ -11927,7 +11953,7 @@
         <v>28</v>
       </c>
       <c r="G88">
-        <v>26.2</v>
+        <v>25.5</v>
       </c>
       <c r="H88" t="s">
         <v>33</v>
@@ -11940,7 +11966,7 @@
       </c>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="1">
+      <c r="A89" s="2">
         <v>46204</v>
       </c>
       <c r="B89">
@@ -11959,7 +11985,7 @@
         <v>28</v>
       </c>
       <c r="G89">
-        <v>32.1</v>
+        <v>31.7</v>
       </c>
       <c r="H89" t="s">
         <v>33</v>
@@ -11972,7 +11998,7 @@
       </c>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="1">
+      <c r="A90" s="2">
         <v>46235</v>
       </c>
       <c r="B90">
@@ -11991,7 +12017,7 @@
         <v>28</v>
       </c>
       <c r="G90">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="H90" t="s">
         <v>33</v>
@@ -12004,7 +12030,7 @@
       </c>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="1">
+      <c r="A91" s="2">
         <v>46266</v>
       </c>
       <c r="B91">
@@ -12023,7 +12049,7 @@
         <v>28</v>
       </c>
       <c r="G91">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="H91" t="s">
         <v>33</v>
@@ -12036,7 +12062,7 @@
       </c>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="1">
+      <c r="A92" s="2">
         <v>44927</v>
       </c>
       <c r="B92">
@@ -12055,7 +12081,7 @@
         <v>29</v>
       </c>
       <c r="G92">
-        <v>72.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="H92" t="s">
         <v>34</v>
@@ -12068,7 +12094,7 @@
       </c>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="1">
+      <c r="A93" s="2">
         <v>44958</v>
       </c>
       <c r="B93">
@@ -12087,7 +12113,7 @@
         <v>29</v>
       </c>
       <c r="G93">
-        <v>52.4</v>
+        <v>52.7</v>
       </c>
       <c r="H93" t="s">
         <v>34</v>
@@ -12100,7 +12126,7 @@
       </c>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="1">
+      <c r="A94" s="2">
         <v>44986</v>
       </c>
       <c r="B94">
@@ -12119,7 +12145,7 @@
         <v>29</v>
       </c>
       <c r="G94">
-        <v>61.3</v>
+        <v>61</v>
       </c>
       <c r="H94" t="s">
         <v>34</v>
@@ -12132,7 +12158,7 @@
       </c>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="1">
+      <c r="A95" s="2">
         <v>45017</v>
       </c>
       <c r="B95">
@@ -12151,7 +12177,7 @@
         <v>29</v>
       </c>
       <c r="G95">
-        <v>73.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H95" t="s">
         <v>34</v>
@@ -12164,7 +12190,7 @@
       </c>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="1">
+      <c r="A96" s="2">
         <v>45047</v>
       </c>
       <c r="B96">
@@ -12183,7 +12209,7 @@
         <v>29</v>
       </c>
       <c r="G96">
-        <v>69.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H96" t="s">
         <v>34</v>
@@ -12196,7 +12222,7 @@
       </c>
     </row>
     <row r="97" spans="1:10">
-      <c r="A97" s="1">
+      <c r="A97" s="2">
         <v>45078</v>
       </c>
       <c r="B97">
@@ -12215,7 +12241,7 @@
         <v>29</v>
       </c>
       <c r="G97">
-        <v>79.8</v>
+        <v>78.2</v>
       </c>
       <c r="H97" t="s">
         <v>34</v>
@@ -12228,7 +12254,7 @@
       </c>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="1">
+      <c r="A98" s="2">
         <v>45108</v>
       </c>
       <c r="B98">
@@ -12260,7 +12286,7 @@
       </c>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="1">
+      <c r="A99" s="2">
         <v>45139</v>
       </c>
       <c r="B99">
@@ -12279,7 +12305,7 @@
         <v>29</v>
       </c>
       <c r="G99">
-        <v>59.8</v>
+        <v>58.9</v>
       </c>
       <c r="H99" t="s">
         <v>34</v>
@@ -12292,7 +12318,7 @@
       </c>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="1">
+      <c r="A100" s="2">
         <v>45170</v>
       </c>
       <c r="B100">
@@ -12311,7 +12337,7 @@
         <v>29</v>
       </c>
       <c r="G100">
-        <v>54.5</v>
+        <v>53.3</v>
       </c>
       <c r="H100" t="s">
         <v>34</v>
@@ -12324,7 +12350,7 @@
       </c>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" s="1">
+      <c r="A101" s="2">
         <v>45200</v>
       </c>
       <c r="B101">
@@ -12343,7 +12369,7 @@
         <v>29</v>
       </c>
       <c r="G101">
-        <v>59</v>
+        <v>59.2</v>
       </c>
       <c r="H101" t="s">
         <v>34</v>
@@ -12356,7 +12382,7 @@
       </c>
     </row>
     <row r="102" spans="1:10">
-      <c r="A102" s="1">
+      <c r="A102" s="2">
         <v>45231</v>
       </c>
       <c r="B102">
@@ -12375,7 +12401,7 @@
         <v>29</v>
       </c>
       <c r="G102">
-        <v>66.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="H102" t="s">
         <v>34</v>
@@ -12388,7 +12414,7 @@
       </c>
     </row>
     <row r="103" spans="1:10">
-      <c r="A103" s="1">
+      <c r="A103" s="2">
         <v>45261</v>
       </c>
       <c r="B103">
@@ -12407,7 +12433,7 @@
         <v>29</v>
       </c>
       <c r="G103">
-        <v>75.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H103" t="s">
         <v>34</v>
@@ -12420,7 +12446,7 @@
       </c>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" s="1">
+      <c r="A104" s="2">
         <v>45292</v>
       </c>
       <c r="B104">
@@ -12452,7 +12478,7 @@
       </c>
     </row>
     <row r="105" spans="1:10">
-      <c r="A105" s="1">
+      <c r="A105" s="2">
         <v>45323</v>
       </c>
       <c r="B105">
@@ -12471,7 +12497,7 @@
         <v>29</v>
       </c>
       <c r="G105">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="H105" t="s">
         <v>34</v>
@@ -12484,7 +12510,7 @@
       </c>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" s="1">
+      <c r="A106" s="2">
         <v>45352</v>
       </c>
       <c r="B106">
@@ -12503,7 +12529,7 @@
         <v>29</v>
       </c>
       <c r="G106">
-        <v>57.6</v>
+        <v>57.8</v>
       </c>
       <c r="H106" t="s">
         <v>34</v>
@@ -12516,7 +12542,7 @@
       </c>
     </row>
     <row r="107" spans="1:10">
-      <c r="A107" s="1">
+      <c r="A107" s="2">
         <v>45383</v>
       </c>
       <c r="B107">
@@ -12535,7 +12561,7 @@
         <v>29</v>
       </c>
       <c r="G107">
-        <v>69.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="H107" t="s">
         <v>34</v>
@@ -12548,7 +12574,7 @@
       </c>
     </row>
     <row r="108" spans="1:10">
-      <c r="A108" s="1">
+      <c r="A108" s="2">
         <v>45413</v>
       </c>
       <c r="B108">
@@ -12567,7 +12593,7 @@
         <v>29</v>
       </c>
       <c r="G108">
-        <v>25.6</v>
+        <v>26.4</v>
       </c>
       <c r="H108" t="s">
         <v>34</v>
@@ -12580,7 +12606,7 @@
       </c>
     </row>
     <row r="109" spans="1:10">
-      <c r="A109" s="1">
+      <c r="A109" s="2">
         <v>45444</v>
       </c>
       <c r="B109">
@@ -12599,7 +12625,7 @@
         <v>29</v>
       </c>
       <c r="G109">
-        <v>42.6</v>
+        <v>42.2</v>
       </c>
       <c r="H109" t="s">
         <v>34</v>
@@ -12612,7 +12638,7 @@
       </c>
     </row>
     <row r="110" spans="1:10">
-      <c r="A110" s="1">
+      <c r="A110" s="2">
         <v>45474</v>
       </c>
       <c r="B110">
@@ -12631,7 +12657,7 @@
         <v>29</v>
       </c>
       <c r="G110">
-        <v>67</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H110" t="s">
         <v>34</v>
@@ -12644,7 +12670,7 @@
       </c>
     </row>
     <row r="111" spans="1:10">
-      <c r="A111" s="1">
+      <c r="A111" s="2">
         <v>45505</v>
       </c>
       <c r="B111">
@@ -12663,7 +12689,7 @@
         <v>29</v>
       </c>
       <c r="G111">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="H111" t="s">
         <v>34</v>
@@ -12676,7 +12702,7 @@
       </c>
     </row>
     <row r="112" spans="1:10">
-      <c r="A112" s="1">
+      <c r="A112" s="2">
         <v>45536</v>
       </c>
       <c r="B112">
@@ -12695,7 +12721,7 @@
         <v>29</v>
       </c>
       <c r="G112">
-        <v>38.1</v>
+        <v>36.5</v>
       </c>
       <c r="H112" t="s">
         <v>34</v>
@@ -12708,7 +12734,7 @@
       </c>
     </row>
     <row r="113" spans="1:10">
-      <c r="A113" s="1">
+      <c r="A113" s="2">
         <v>45566</v>
       </c>
       <c r="B113">
@@ -12727,7 +12753,7 @@
         <v>29</v>
       </c>
       <c r="G113">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="H113" t="s">
         <v>34</v>
@@ -12740,7 +12766,7 @@
       </c>
     </row>
     <row r="114" spans="1:10">
-      <c r="A114" s="1">
+      <c r="A114" s="2">
         <v>45597</v>
       </c>
       <c r="B114">
@@ -12759,7 +12785,7 @@
         <v>29</v>
       </c>
       <c r="G114">
-        <v>53.9</v>
+        <v>52.7</v>
       </c>
       <c r="H114" t="s">
         <v>34</v>
@@ -12772,7 +12798,7 @@
       </c>
     </row>
     <row r="115" spans="1:10">
-      <c r="A115" s="1">
+      <c r="A115" s="2">
         <v>45627</v>
       </c>
       <c r="B115">
@@ -12804,7 +12830,7 @@
       </c>
     </row>
     <row r="116" spans="1:10">
-      <c r="A116" s="1">
+      <c r="A116" s="2">
         <v>45658</v>
       </c>
       <c r="B116">
@@ -12823,7 +12849,7 @@
         <v>29</v>
       </c>
       <c r="G116">
-        <v>51.8</v>
+        <v>51.2</v>
       </c>
       <c r="H116" t="s">
         <v>34</v>
@@ -12836,7 +12862,7 @@
       </c>
     </row>
     <row r="117" spans="1:10">
-      <c r="A117" s="1">
+      <c r="A117" s="2">
         <v>45689</v>
       </c>
       <c r="B117">
@@ -12855,7 +12881,7 @@
         <v>29</v>
       </c>
       <c r="G117">
-        <v>33</v>
+        <v>32.6</v>
       </c>
       <c r="H117" t="s">
         <v>34</v>
@@ -12868,7 +12894,7 @@
       </c>
     </row>
     <row r="118" spans="1:10">
-      <c r="A118" s="1">
+      <c r="A118" s="2">
         <v>45717</v>
       </c>
       <c r="B118">
@@ -12887,7 +12913,7 @@
         <v>29</v>
       </c>
       <c r="G118">
-        <v>51.2</v>
+        <v>50.5</v>
       </c>
       <c r="H118" t="s">
         <v>34</v>
@@ -12900,7 +12926,7 @@
       </c>
     </row>
     <row r="119" spans="1:10">
-      <c r="A119" s="1">
+      <c r="A119" s="2">
         <v>45748</v>
       </c>
       <c r="B119">
@@ -12919,7 +12945,7 @@
         <v>29</v>
       </c>
       <c r="G119">
-        <v>58.9</v>
+        <v>59.5</v>
       </c>
       <c r="H119" t="s">
         <v>34</v>
@@ -12932,7 +12958,7 @@
       </c>
     </row>
     <row r="120" spans="1:10">
-      <c r="A120" s="1">
+      <c r="A120" s="2">
         <v>45778</v>
       </c>
       <c r="B120">
@@ -12951,7 +12977,7 @@
         <v>29</v>
       </c>
       <c r="G120">
-        <v>55.1</v>
+        <v>54.8</v>
       </c>
       <c r="H120" t="s">
         <v>34</v>
@@ -12964,7 +12990,7 @@
       </c>
     </row>
     <row r="121" spans="1:10">
-      <c r="A121" s="1">
+      <c r="A121" s="2">
         <v>45809</v>
       </c>
       <c r="B121">
@@ -12983,7 +13009,7 @@
         <v>29</v>
       </c>
       <c r="G121">
-        <v>72.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="H121" t="s">
         <v>34</v>
@@ -12996,7 +13022,7 @@
       </c>
     </row>
     <row r="122" spans="1:10">
-      <c r="A122" s="1">
+      <c r="A122" s="2">
         <v>45839</v>
       </c>
       <c r="B122">
@@ -13015,7 +13041,7 @@
         <v>29</v>
       </c>
       <c r="G122">
-        <v>84.2</v>
+        <v>83.5</v>
       </c>
       <c r="H122" t="s">
         <v>34</v>
@@ -13028,7 +13054,7 @@
       </c>
     </row>
     <row r="123" spans="1:10">
-      <c r="A123" s="1">
+      <c r="A123" s="2">
         <v>45870</v>
       </c>
       <c r="B123">
@@ -13047,7 +13073,7 @@
         <v>29</v>
       </c>
       <c r="G123">
-        <v>49.8</v>
+        <v>49.5</v>
       </c>
       <c r="H123" t="s">
         <v>34</v>
@@ -13060,7 +13086,7 @@
       </c>
     </row>
     <row r="124" spans="1:10">
-      <c r="A124" s="1">
+      <c r="A124" s="2">
         <v>45901</v>
       </c>
       <c r="B124">
@@ -13079,7 +13105,7 @@
         <v>29</v>
       </c>
       <c r="G124">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="H124" t="s">
         <v>34</v>
@@ -13092,7 +13118,7 @@
       </c>
     </row>
     <row r="125" spans="1:10">
-      <c r="A125" s="1">
+      <c r="A125" s="2">
         <v>45931</v>
       </c>
       <c r="B125">
@@ -13111,7 +13137,7 @@
         <v>29</v>
       </c>
       <c r="G125">
-        <v>56</v>
+        <v>55.4</v>
       </c>
       <c r="H125" t="s">
         <v>34</v>
@@ -13124,7 +13150,7 @@
       </c>
     </row>
     <row r="126" spans="1:10">
-      <c r="A126" s="1">
+      <c r="A126" s="2">
         <v>45962</v>
       </c>
       <c r="B126">
@@ -13143,7 +13169,7 @@
         <v>29</v>
       </c>
       <c r="G126">
-        <v>64</v>
+        <v>62.6</v>
       </c>
       <c r="H126" t="s">
         <v>34</v>
@@ -13156,7 +13182,7 @@
       </c>
     </row>
     <row r="127" spans="1:10">
-      <c r="A127" s="1">
+      <c r="A127" s="2">
         <v>45992</v>
       </c>
       <c r="B127">
@@ -13188,7 +13214,7 @@
       </c>
     </row>
     <row r="128" spans="1:10">
-      <c r="A128" s="1">
+      <c r="A128" s="2">
         <v>46023</v>
       </c>
       <c r="B128">
@@ -13207,7 +13233,7 @@
         <v>29</v>
       </c>
       <c r="G128">
-        <v>58.3</v>
+        <v>59.5</v>
       </c>
       <c r="H128" t="s">
         <v>34</v>
@@ -13220,7 +13246,7 @@
       </c>
     </row>
     <row r="129" spans="1:10">
-      <c r="A129" s="1">
+      <c r="A129" s="2">
         <v>46054</v>
       </c>
       <c r="B129">
@@ -13239,7 +13265,7 @@
         <v>29</v>
       </c>
       <c r="G129">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="H129" t="s">
         <v>34</v>
@@ -13252,7 +13278,7 @@
       </c>
     </row>
     <row r="130" spans="1:10">
-      <c r="A130" s="1">
+      <c r="A130" s="2">
         <v>46082</v>
       </c>
       <c r="B130">
@@ -13271,7 +13297,7 @@
         <v>29</v>
       </c>
       <c r="G130">
-        <v>54.3</v>
+        <v>53.8</v>
       </c>
       <c r="H130" t="s">
         <v>34</v>
@@ -13284,7 +13310,7 @@
       </c>
     </row>
     <row r="131" spans="1:10">
-      <c r="A131" s="1">
+      <c r="A131" s="2">
         <v>46113</v>
       </c>
       <c r="B131">
@@ -13303,7 +13329,7 @@
         <v>29</v>
       </c>
       <c r="G131">
-        <v>56.8</v>
+        <v>55.7</v>
       </c>
       <c r="H131" t="s">
         <v>34</v>
@@ -13316,7 +13342,7 @@
       </c>
     </row>
     <row r="132" spans="1:10">
-      <c r="A132" s="1">
+      <c r="A132" s="2">
         <v>46143</v>
       </c>
       <c r="B132">
@@ -13335,7 +13361,7 @@
         <v>29</v>
       </c>
       <c r="G132">
-        <v>61.9</v>
+        <v>61.8</v>
       </c>
       <c r="H132" t="s">
         <v>34</v>
@@ -13348,7 +13374,7 @@
       </c>
     </row>
     <row r="133" spans="1:10">
-      <c r="A133" s="1">
+      <c r="A133" s="2">
         <v>46174</v>
       </c>
       <c r="B133">
@@ -13367,7 +13393,7 @@
         <v>29</v>
       </c>
       <c r="G133">
-        <v>70.2</v>
+        <v>70.5</v>
       </c>
       <c r="H133" t="s">
         <v>34</v>
@@ -13380,7 +13406,7 @@
       </c>
     </row>
     <row r="134" spans="1:10">
-      <c r="A134" s="1">
+      <c r="A134" s="2">
         <v>46204</v>
       </c>
       <c r="B134">
@@ -13399,7 +13425,7 @@
         <v>29</v>
       </c>
       <c r="G134">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H134" t="s">
         <v>34</v>
@@ -13412,7 +13438,7 @@
       </c>
     </row>
     <row r="135" spans="1:10">
-      <c r="A135" s="1">
+      <c r="A135" s="2">
         <v>46235</v>
       </c>
       <c r="B135">
@@ -13431,7 +13457,7 @@
         <v>29</v>
       </c>
       <c r="G135">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="H135" t="s">
         <v>34</v>
@@ -13444,7 +13470,7 @@
       </c>
     </row>
     <row r="136" spans="1:10">
-      <c r="A136" s="1">
+      <c r="A136" s="2">
         <v>46266</v>
       </c>
       <c r="B136">
@@ -13463,7 +13489,7 @@
         <v>29</v>
       </c>
       <c r="G136">
-        <v>39.6</v>
+        <v>39.1</v>
       </c>
       <c r="H136" t="s">
         <v>34</v>
@@ -13476,7 +13502,7 @@
       </c>
     </row>
     <row r="137" spans="1:10">
-      <c r="A137" s="1">
+      <c r="A137" s="2">
         <v>44927</v>
       </c>
       <c r="B137">
@@ -13495,7 +13521,7 @@
         <v>30</v>
       </c>
       <c r="G137">
-        <v>16.9</v>
+        <v>17.3</v>
       </c>
       <c r="H137" t="s">
         <v>35</v>
@@ -13508,7 +13534,7 @@
       </c>
     </row>
     <row r="138" spans="1:10">
-      <c r="A138" s="1">
+      <c r="A138" s="2">
         <v>44958</v>
       </c>
       <c r="B138">
@@ -13527,7 +13553,7 @@
         <v>30</v>
       </c>
       <c r="G138">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="H138" t="s">
         <v>35</v>
@@ -13540,7 +13566,7 @@
       </c>
     </row>
     <row r="139" spans="1:10">
-      <c r="A139" s="1">
+      <c r="A139" s="2">
         <v>44986</v>
       </c>
       <c r="B139">
@@ -13559,7 +13585,7 @@
         <v>30</v>
       </c>
       <c r="G139">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="H139" t="s">
         <v>35</v>
@@ -13572,7 +13598,7 @@
       </c>
     </row>
     <row r="140" spans="1:10">
-      <c r="A140" s="1">
+      <c r="A140" s="2">
         <v>45017</v>
       </c>
       <c r="B140">
@@ -13591,7 +13617,7 @@
         <v>30</v>
       </c>
       <c r="G140">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="H140" t="s">
         <v>35</v>
@@ -13604,7 +13630,7 @@
       </c>
     </row>
     <row r="141" spans="1:10">
-      <c r="A141" s="1">
+      <c r="A141" s="2">
         <v>45047</v>
       </c>
       <c r="B141">
@@ -13623,7 +13649,7 @@
         <v>30</v>
       </c>
       <c r="G141">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="H141" t="s">
         <v>35</v>
@@ -13636,7 +13662,7 @@
       </c>
     </row>
     <row r="142" spans="1:10">
-      <c r="A142" s="1">
+      <c r="A142" s="2">
         <v>45078</v>
       </c>
       <c r="B142">
@@ -13668,7 +13694,7 @@
       </c>
     </row>
     <row r="143" spans="1:10">
-      <c r="A143" s="1">
+      <c r="A143" s="2">
         <v>45108</v>
       </c>
       <c r="B143">
@@ -13687,7 +13713,7 @@
         <v>30</v>
       </c>
       <c r="G143">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="H143" t="s">
         <v>35</v>
@@ -13700,7 +13726,7 @@
       </c>
     </row>
     <row r="144" spans="1:10">
-      <c r="A144" s="1">
+      <c r="A144" s="2">
         <v>45139</v>
       </c>
       <c r="B144">
@@ -13732,7 +13758,7 @@
       </c>
     </row>
     <row r="145" spans="1:10">
-      <c r="A145" s="1">
+      <c r="A145" s="2">
         <v>45170</v>
       </c>
       <c r="B145">
@@ -13751,7 +13777,7 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>7.7</v>
+        <v>5.9</v>
       </c>
       <c r="H145" t="s">
         <v>35</v>
@@ -13764,7 +13790,7 @@
       </c>
     </row>
     <row r="146" spans="1:10">
-      <c r="A146" s="1">
+      <c r="A146" s="2">
         <v>45200</v>
       </c>
       <c r="B146">
@@ -13783,7 +13809,7 @@
         <v>30</v>
       </c>
       <c r="G146">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="H146" t="s">
         <v>35</v>
@@ -13796,7 +13822,7 @@
       </c>
     </row>
     <row r="147" spans="1:10">
-      <c r="A147" s="1">
+      <c r="A147" s="2">
         <v>45231</v>
       </c>
       <c r="B147">
@@ -13815,7 +13841,7 @@
         <v>30</v>
       </c>
       <c r="G147">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="H147" t="s">
         <v>35</v>
@@ -13828,7 +13854,7 @@
       </c>
     </row>
     <row r="148" spans="1:10">
-      <c r="A148" s="1">
+      <c r="A148" s="2">
         <v>45261</v>
       </c>
       <c r="B148">
@@ -13847,7 +13873,7 @@
         <v>30</v>
       </c>
       <c r="G148">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="H148" t="s">
         <v>35</v>
@@ -13860,7 +13886,7 @@
       </c>
     </row>
     <row r="149" spans="1:10">
-      <c r="A149" s="1">
+      <c r="A149" s="2">
         <v>45292</v>
       </c>
       <c r="B149">
@@ -13879,7 +13905,7 @@
         <v>30</v>
       </c>
       <c r="G149">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="H149" t="s">
         <v>35</v>
@@ -13892,7 +13918,7 @@
       </c>
     </row>
     <row r="150" spans="1:10">
-      <c r="A150" s="1">
+      <c r="A150" s="2">
         <v>45323</v>
       </c>
       <c r="B150">
@@ -13911,7 +13937,7 @@
         <v>30</v>
       </c>
       <c r="G150">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="H150" t="s">
         <v>35</v>
@@ -13924,7 +13950,7 @@
       </c>
     </row>
     <row r="151" spans="1:10">
-      <c r="A151" s="1">
+      <c r="A151" s="2">
         <v>45352</v>
       </c>
       <c r="B151">
@@ -13943,7 +13969,7 @@
         <v>30</v>
       </c>
       <c r="G151">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="H151" t="s">
         <v>35</v>
@@ -13956,7 +13982,7 @@
       </c>
     </row>
     <row r="152" spans="1:10">
-      <c r="A152" s="1">
+      <c r="A152" s="2">
         <v>45383</v>
       </c>
       <c r="B152">
@@ -13975,7 +14001,7 @@
         <v>30</v>
       </c>
       <c r="G152">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="H152" t="s">
         <v>35</v>
@@ -13988,7 +14014,7 @@
       </c>
     </row>
     <row r="153" spans="1:10">
-      <c r="A153" s="1">
+      <c r="A153" s="2">
         <v>45413</v>
       </c>
       <c r="B153">
@@ -14020,7 +14046,7 @@
       </c>
     </row>
     <row r="154" spans="1:10">
-      <c r="A154" s="1">
+      <c r="A154" s="2">
         <v>45444</v>
       </c>
       <c r="B154">
@@ -14039,7 +14065,7 @@
         <v>30</v>
       </c>
       <c r="G154">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="H154" t="s">
         <v>35</v>
@@ -14052,7 +14078,7 @@
       </c>
     </row>
     <row r="155" spans="1:10">
-      <c r="A155" s="1">
+      <c r="A155" s="2">
         <v>45474</v>
       </c>
       <c r="B155">
@@ -14071,7 +14097,7 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="H155" t="s">
         <v>35</v>
@@ -14084,7 +14110,7 @@
       </c>
     </row>
     <row r="156" spans="1:10">
-      <c r="A156" s="1">
+      <c r="A156" s="2">
         <v>45505</v>
       </c>
       <c r="B156">
@@ -14103,7 +14129,7 @@
         <v>30</v>
       </c>
       <c r="G156">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="H156" t="s">
         <v>35</v>
@@ -14116,7 +14142,7 @@
       </c>
     </row>
     <row r="157" spans="1:10">
-      <c r="A157" s="1">
+      <c r="A157" s="2">
         <v>45536</v>
       </c>
       <c r="B157">
@@ -14135,7 +14161,7 @@
         <v>30</v>
       </c>
       <c r="G157">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="H157" t="s">
         <v>35</v>
@@ -14148,7 +14174,7 @@
       </c>
     </row>
     <row r="158" spans="1:10">
-      <c r="A158" s="1">
+      <c r="A158" s="2">
         <v>45566</v>
       </c>
       <c r="B158">
@@ -14167,7 +14193,7 @@
         <v>30</v>
       </c>
       <c r="G158">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="H158" t="s">
         <v>35</v>
@@ -14180,7 +14206,7 @@
       </c>
     </row>
     <row r="159" spans="1:10">
-      <c r="A159" s="1">
+      <c r="A159" s="2">
         <v>45597</v>
       </c>
       <c r="B159">
@@ -14199,7 +14225,7 @@
         <v>30</v>
       </c>
       <c r="G159">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H159" t="s">
         <v>35</v>
@@ -14212,7 +14238,7 @@
       </c>
     </row>
     <row r="160" spans="1:10">
-      <c r="A160" s="1">
+      <c r="A160" s="2">
         <v>45627</v>
       </c>
       <c r="B160">
@@ -14231,7 +14257,7 @@
         <v>30</v>
       </c>
       <c r="G160">
-        <v>10.7</v>
+        <v>10.2</v>
       </c>
       <c r="H160" t="s">
         <v>35</v>
@@ -14244,7 +14270,7 @@
       </c>
     </row>
     <row r="161" spans="1:10">
-      <c r="A161" s="1">
+      <c r="A161" s="2">
         <v>45658</v>
       </c>
       <c r="B161">
@@ -14263,7 +14289,7 @@
         <v>30</v>
       </c>
       <c r="G161">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="H161" t="s">
         <v>35</v>
@@ -14276,7 +14302,7 @@
       </c>
     </row>
     <row r="162" spans="1:10">
-      <c r="A162" s="1">
+      <c r="A162" s="2">
         <v>45689</v>
       </c>
       <c r="B162">
@@ -14295,7 +14321,7 @@
         <v>30</v>
       </c>
       <c r="G162">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="H162" t="s">
         <v>35</v>
@@ -14308,7 +14334,7 @@
       </c>
     </row>
     <row r="163" spans="1:10">
-      <c r="A163" s="1">
+      <c r="A163" s="2">
         <v>45717</v>
       </c>
       <c r="B163">
@@ -14327,7 +14353,7 @@
         <v>30</v>
       </c>
       <c r="G163">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H163" t="s">
         <v>35</v>
@@ -14340,7 +14366,7 @@
       </c>
     </row>
     <row r="164" spans="1:10">
-      <c r="A164" s="1">
+      <c r="A164" s="2">
         <v>45748</v>
       </c>
       <c r="B164">
@@ -14359,7 +14385,7 @@
         <v>30</v>
       </c>
       <c r="G164">
-        <v>11.6</v>
+        <v>10.4</v>
       </c>
       <c r="H164" t="s">
         <v>35</v>
@@ -14372,7 +14398,7 @@
       </c>
     </row>
     <row r="165" spans="1:10">
-      <c r="A165" s="1">
+      <c r="A165" s="2">
         <v>45778</v>
       </c>
       <c r="B165">
@@ -14391,7 +14417,7 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="H165" t="s">
         <v>35</v>
@@ -14404,7 +14430,7 @@
       </c>
     </row>
     <row r="166" spans="1:10">
-      <c r="A166" s="1">
+      <c r="A166" s="2">
         <v>45809</v>
       </c>
       <c r="B166">
@@ -14423,7 +14449,7 @@
         <v>30</v>
       </c>
       <c r="G166">
-        <v>11.7</v>
+        <v>10.7</v>
       </c>
       <c r="H166" t="s">
         <v>35</v>
@@ -14436,7 +14462,7 @@
       </c>
     </row>
     <row r="167" spans="1:10">
-      <c r="A167" s="1">
+      <c r="A167" s="2">
         <v>45839</v>
       </c>
       <c r="B167">
@@ -14455,7 +14481,7 @@
         <v>30</v>
       </c>
       <c r="G167">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="H167" t="s">
         <v>35</v>
@@ -14468,7 +14494,7 @@
       </c>
     </row>
     <row r="168" spans="1:10">
-      <c r="A168" s="1">
+      <c r="A168" s="2">
         <v>45870</v>
       </c>
       <c r="B168">
@@ -14487,7 +14513,7 @@
         <v>30</v>
       </c>
       <c r="G168">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="H168" t="s">
         <v>35</v>
@@ -14500,7 +14526,7 @@
       </c>
     </row>
     <row r="169" spans="1:10">
-      <c r="A169" s="1">
+      <c r="A169" s="2">
         <v>45901</v>
       </c>
       <c r="B169">
@@ -14519,7 +14545,7 @@
         <v>30</v>
       </c>
       <c r="G169">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="H169" t="s">
         <v>35</v>
@@ -14532,7 +14558,7 @@
       </c>
     </row>
     <row r="170" spans="1:10">
-      <c r="A170" s="1">
+      <c r="A170" s="2">
         <v>45931</v>
       </c>
       <c r="B170">
@@ -14551,7 +14577,7 @@
         <v>30</v>
       </c>
       <c r="G170">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H170" t="s">
         <v>35</v>
@@ -14564,7 +14590,7 @@
       </c>
     </row>
     <row r="171" spans="1:10">
-      <c r="A171" s="1">
+      <c r="A171" s="2">
         <v>45962</v>
       </c>
       <c r="B171">
@@ -14583,7 +14609,7 @@
         <v>30</v>
       </c>
       <c r="G171">
-        <v>11.7</v>
+        <v>12.1</v>
       </c>
       <c r="H171" t="s">
         <v>35</v>
@@ -14596,7 +14622,7 @@
       </c>
     </row>
     <row r="172" spans="1:10">
-      <c r="A172" s="1">
+      <c r="A172" s="2">
         <v>45992</v>
       </c>
       <c r="B172">
@@ -14615,7 +14641,7 @@
         <v>30</v>
       </c>
       <c r="G172">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="H172" t="s">
         <v>35</v>
@@ -14628,7 +14654,7 @@
       </c>
     </row>
     <row r="173" spans="1:10">
-      <c r="A173" s="1">
+      <c r="A173" s="2">
         <v>46023</v>
       </c>
       <c r="B173">
@@ -14647,7 +14673,7 @@
         <v>30</v>
       </c>
       <c r="G173">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="H173" t="s">
         <v>35</v>
@@ -14660,7 +14686,7 @@
       </c>
     </row>
     <row r="174" spans="1:10">
-      <c r="A174" s="1">
+      <c r="A174" s="2">
         <v>46054</v>
       </c>
       <c r="B174">
@@ -14679,7 +14705,7 @@
         <v>30</v>
       </c>
       <c r="G174">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="H174" t="s">
         <v>35</v>
@@ -14692,7 +14718,7 @@
       </c>
     </row>
     <row r="175" spans="1:10">
-      <c r="A175" s="1">
+      <c r="A175" s="2">
         <v>46082</v>
       </c>
       <c r="B175">
@@ -14711,7 +14737,7 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H175" t="s">
         <v>35</v>
@@ -14724,7 +14750,7 @@
       </c>
     </row>
     <row r="176" spans="1:10">
-      <c r="A176" s="1">
+      <c r="A176" s="2">
         <v>46113</v>
       </c>
       <c r="B176">
@@ -14743,7 +14769,7 @@
         <v>30</v>
       </c>
       <c r="G176">
-        <v>6.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H176" t="s">
         <v>35</v>
@@ -14756,7 +14782,7 @@
       </c>
     </row>
     <row r="177" spans="1:10">
-      <c r="A177" s="1">
+      <c r="A177" s="2">
         <v>46143</v>
       </c>
       <c r="B177">
@@ -14775,7 +14801,7 @@
         <v>30</v>
       </c>
       <c r="G177">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="H177" t="s">
         <v>35</v>
@@ -14788,7 +14814,7 @@
       </c>
     </row>
     <row r="178" spans="1:10">
-      <c r="A178" s="1">
+      <c r="A178" s="2">
         <v>46174</v>
       </c>
       <c r="B178">
@@ -14807,7 +14833,7 @@
         <v>30</v>
       </c>
       <c r="G178">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="H178" t="s">
         <v>35</v>
@@ -14820,7 +14846,7 @@
       </c>
     </row>
     <row r="179" spans="1:10">
-      <c r="A179" s="1">
+      <c r="A179" s="2">
         <v>46204</v>
       </c>
       <c r="B179">
@@ -14839,7 +14865,7 @@
         <v>30</v>
       </c>
       <c r="G179">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="H179" t="s">
         <v>35</v>
@@ -14852,7 +14878,7 @@
       </c>
     </row>
     <row r="180" spans="1:10">
-      <c r="A180" s="1">
+      <c r="A180" s="2">
         <v>46235</v>
       </c>
       <c r="B180">
@@ -14884,7 +14910,7 @@
       </c>
     </row>
     <row r="181" spans="1:10">
-      <c r="A181" s="1">
+      <c r="A181" s="2">
         <v>46266</v>
       </c>
       <c r="B181">
@@ -14903,7 +14929,7 @@
         <v>30</v>
       </c>
       <c r="G181">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H181" t="s">
         <v>35</v>
@@ -14916,7 +14942,7 @@
       </c>
     </row>
     <row r="182" spans="1:10">
-      <c r="A182" s="1">
+      <c r="A182" s="2">
         <v>44927</v>
       </c>
       <c r="B182">
@@ -14935,7 +14961,7 @@
         <v>31</v>
       </c>
       <c r="G182">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H182" t="s">
         <v>36</v>
@@ -14948,7 +14974,7 @@
       </c>
     </row>
     <row r="183" spans="1:10">
-      <c r="A183" s="1">
+      <c r="A183" s="2">
         <v>44958</v>
       </c>
       <c r="B183">
@@ -14980,7 +15006,7 @@
       </c>
     </row>
     <row r="184" spans="1:10">
-      <c r="A184" s="1">
+      <c r="A184" s="2">
         <v>44986</v>
       </c>
       <c r="B184">
@@ -15012,7 +15038,7 @@
       </c>
     </row>
     <row r="185" spans="1:10">
-      <c r="A185" s="1">
+      <c r="A185" s="2">
         <v>45017</v>
       </c>
       <c r="B185">
@@ -15044,7 +15070,7 @@
       </c>
     </row>
     <row r="186" spans="1:10">
-      <c r="A186" s="1">
+      <c r="A186" s="2">
         <v>45047</v>
       </c>
       <c r="B186">
@@ -15076,7 +15102,7 @@
       </c>
     </row>
     <row r="187" spans="1:10">
-      <c r="A187" s="1">
+      <c r="A187" s="2">
         <v>45078</v>
       </c>
       <c r="B187">
@@ -15108,7 +15134,7 @@
       </c>
     </row>
     <row r="188" spans="1:10">
-      <c r="A188" s="1">
+      <c r="A188" s="2">
         <v>45108</v>
       </c>
       <c r="B188">
@@ -15140,7 +15166,7 @@
       </c>
     </row>
     <row r="189" spans="1:10">
-      <c r="A189" s="1">
+      <c r="A189" s="2">
         <v>45139</v>
       </c>
       <c r="B189">
@@ -15172,7 +15198,7 @@
       </c>
     </row>
     <row r="190" spans="1:10">
-      <c r="A190" s="1">
+      <c r="A190" s="2">
         <v>45170</v>
       </c>
       <c r="B190">
@@ -15204,7 +15230,7 @@
       </c>
     </row>
     <row r="191" spans="1:10">
-      <c r="A191" s="1">
+      <c r="A191" s="2">
         <v>45200</v>
       </c>
       <c r="B191">
@@ -15236,7 +15262,7 @@
       </c>
     </row>
     <row r="192" spans="1:10">
-      <c r="A192" s="1">
+      <c r="A192" s="2">
         <v>45231</v>
       </c>
       <c r="B192">
@@ -15268,7 +15294,7 @@
       </c>
     </row>
     <row r="193" spans="1:10">
-      <c r="A193" s="1">
+      <c r="A193" s="2">
         <v>45261</v>
       </c>
       <c r="B193">
@@ -15287,7 +15313,7 @@
         <v>31</v>
       </c>
       <c r="G193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H193" t="s">
         <v>36</v>
@@ -15300,7 +15326,7 @@
       </c>
     </row>
     <row r="194" spans="1:10">
-      <c r="A194" s="1">
+      <c r="A194" s="2">
         <v>45292</v>
       </c>
       <c r="B194">
@@ -15332,7 +15358,7 @@
       </c>
     </row>
     <row r="195" spans="1:10">
-      <c r="A195" s="1">
+      <c r="A195" s="2">
         <v>45323</v>
       </c>
       <c r="B195">
@@ -15351,7 +15377,7 @@
         <v>31</v>
       </c>
       <c r="G195">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H195" t="s">
         <v>36</v>
@@ -15364,7 +15390,7 @@
       </c>
     </row>
     <row r="196" spans="1:10">
-      <c r="A196" s="1">
+      <c r="A196" s="2">
         <v>45352</v>
       </c>
       <c r="B196">
@@ -15383,7 +15409,7 @@
         <v>31</v>
       </c>
       <c r="G196">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="H196" t="s">
         <v>36</v>
@@ -15396,7 +15422,7 @@
       </c>
     </row>
     <row r="197" spans="1:10">
-      <c r="A197" s="1">
+      <c r="A197" s="2">
         <v>45383</v>
       </c>
       <c r="B197">
@@ -15415,7 +15441,7 @@
         <v>31</v>
       </c>
       <c r="G197">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="H197" t="s">
         <v>36</v>
@@ -15428,7 +15454,7 @@
       </c>
     </row>
     <row r="198" spans="1:10">
-      <c r="A198" s="1">
+      <c r="A198" s="2">
         <v>45413</v>
       </c>
       <c r="B198">
@@ -15460,7 +15486,7 @@
       </c>
     </row>
     <row r="199" spans="1:10">
-      <c r="A199" s="1">
+      <c r="A199" s="2">
         <v>45444</v>
       </c>
       <c r="B199">
@@ -15492,7 +15518,7 @@
       </c>
     </row>
     <row r="200" spans="1:10">
-      <c r="A200" s="1">
+      <c r="A200" s="2">
         <v>45474</v>
       </c>
       <c r="B200">
@@ -15524,7 +15550,7 @@
       </c>
     </row>
     <row r="201" spans="1:10">
-      <c r="A201" s="1">
+      <c r="A201" s="2">
         <v>45505</v>
       </c>
       <c r="B201">
@@ -15556,7 +15582,7 @@
       </c>
     </row>
     <row r="202" spans="1:10">
-      <c r="A202" s="1">
+      <c r="A202" s="2">
         <v>45536</v>
       </c>
       <c r="B202">
@@ -15588,7 +15614,7 @@
       </c>
     </row>
     <row r="203" spans="1:10">
-      <c r="A203" s="1">
+      <c r="A203" s="2">
         <v>45566</v>
       </c>
       <c r="B203">
@@ -15620,7 +15646,7 @@
       </c>
     </row>
     <row r="204" spans="1:10">
-      <c r="A204" s="1">
+      <c r="A204" s="2">
         <v>45597</v>
       </c>
       <c r="B204">
@@ -15652,7 +15678,7 @@
       </c>
     </row>
     <row r="205" spans="1:10">
-      <c r="A205" s="1">
+      <c r="A205" s="2">
         <v>45627</v>
       </c>
       <c r="B205">
@@ -15684,7 +15710,7 @@
       </c>
     </row>
     <row r="206" spans="1:10">
-      <c r="A206" s="1">
+      <c r="A206" s="2">
         <v>45658</v>
       </c>
       <c r="B206">
@@ -15716,7 +15742,7 @@
       </c>
     </row>
     <row r="207" spans="1:10">
-      <c r="A207" s="1">
+      <c r="A207" s="2">
         <v>45689</v>
       </c>
       <c r="B207">
@@ -15735,7 +15761,7 @@
         <v>31</v>
       </c>
       <c r="G207">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H207" t="s">
         <v>36</v>
@@ -15748,7 +15774,7 @@
       </c>
     </row>
     <row r="208" spans="1:10">
-      <c r="A208" s="1">
+      <c r="A208" s="2">
         <v>45717</v>
       </c>
       <c r="B208">
@@ -15767,7 +15793,7 @@
         <v>31</v>
       </c>
       <c r="G208">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="H208" t="s">
         <v>36</v>
@@ -15780,7 +15806,7 @@
       </c>
     </row>
     <row r="209" spans="1:10">
-      <c r="A209" s="1">
+      <c r="A209" s="2">
         <v>45748</v>
       </c>
       <c r="B209">
@@ -15812,7 +15838,7 @@
       </c>
     </row>
     <row r="210" spans="1:10">
-      <c r="A210" s="1">
+      <c r="A210" s="2">
         <v>45778</v>
       </c>
       <c r="B210">
@@ -15831,7 +15857,7 @@
         <v>31</v>
       </c>
       <c r="G210">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="H210" t="s">
         <v>36</v>
@@ -15844,7 +15870,7 @@
       </c>
     </row>
     <row r="211" spans="1:10">
-      <c r="A211" s="1">
+      <c r="A211" s="2">
         <v>45809</v>
       </c>
       <c r="B211">
@@ -15863,7 +15889,7 @@
         <v>31</v>
       </c>
       <c r="G211">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="H211" t="s">
         <v>36</v>
@@ -15876,7 +15902,7 @@
       </c>
     </row>
     <row r="212" spans="1:10">
-      <c r="A212" s="1">
+      <c r="A212" s="2">
         <v>45839</v>
       </c>
       <c r="B212">
@@ -15895,7 +15921,7 @@
         <v>31</v>
       </c>
       <c r="G212">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H212" t="s">
         <v>36</v>
@@ -15908,7 +15934,7 @@
       </c>
     </row>
     <row r="213" spans="1:10">
-      <c r="A213" s="1">
+      <c r="A213" s="2">
         <v>45870</v>
       </c>
       <c r="B213">
@@ -15927,7 +15953,7 @@
         <v>31</v>
       </c>
       <c r="G213">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H213" t="s">
         <v>36</v>
@@ -15940,7 +15966,7 @@
       </c>
     </row>
     <row r="214" spans="1:10">
-      <c r="A214" s="1">
+      <c r="A214" s="2">
         <v>45901</v>
       </c>
       <c r="B214">
@@ -15959,7 +15985,7 @@
         <v>31</v>
       </c>
       <c r="G214">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="H214" t="s">
         <v>36</v>
@@ -15972,7 +15998,7 @@
       </c>
     </row>
     <row r="215" spans="1:10">
-      <c r="A215" s="1">
+      <c r="A215" s="2">
         <v>45931</v>
       </c>
       <c r="B215">
@@ -15991,7 +16017,7 @@
         <v>31</v>
       </c>
       <c r="G215">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="H215" t="s">
         <v>36</v>
@@ -16004,7 +16030,7 @@
       </c>
     </row>
     <row r="216" spans="1:10">
-      <c r="A216" s="1">
+      <c r="A216" s="2">
         <v>45962</v>
       </c>
       <c r="B216">
@@ -16023,7 +16049,7 @@
         <v>31</v>
       </c>
       <c r="G216">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="H216" t="s">
         <v>36</v>
@@ -16036,7 +16062,7 @@
       </c>
     </row>
     <row r="217" spans="1:10">
-      <c r="A217" s="1">
+      <c r="A217" s="2">
         <v>45992</v>
       </c>
       <c r="B217">
@@ -16055,7 +16081,7 @@
         <v>31</v>
       </c>
       <c r="G217">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="H217" t="s">
         <v>36</v>
@@ -16068,7 +16094,7 @@
       </c>
     </row>
     <row r="218" spans="1:10">
-      <c r="A218" s="1">
+      <c r="A218" s="2">
         <v>46023</v>
       </c>
       <c r="B218">
@@ -16087,7 +16113,7 @@
         <v>31</v>
       </c>
       <c r="G218">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="H218" t="s">
         <v>36</v>
@@ -16100,7 +16126,7 @@
       </c>
     </row>
     <row r="219" spans="1:10">
-      <c r="A219" s="1">
+      <c r="A219" s="2">
         <v>46054</v>
       </c>
       <c r="B219">
@@ -16119,7 +16145,7 @@
         <v>31</v>
       </c>
       <c r="G219">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="H219" t="s">
         <v>36</v>
@@ -16132,7 +16158,7 @@
       </c>
     </row>
     <row r="220" spans="1:10">
-      <c r="A220" s="1">
+      <c r="A220" s="2">
         <v>46082</v>
       </c>
       <c r="B220">
@@ -16151,7 +16177,7 @@
         <v>31</v>
       </c>
       <c r="G220">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="H220" t="s">
         <v>36</v>
@@ -16164,7 +16190,7 @@
       </c>
     </row>
     <row r="221" spans="1:10">
-      <c r="A221" s="1">
+      <c r="A221" s="2">
         <v>46113</v>
       </c>
       <c r="B221">
@@ -16183,7 +16209,7 @@
         <v>31</v>
       </c>
       <c r="G221">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="H221" t="s">
         <v>36</v>
@@ -16196,7 +16222,7 @@
       </c>
     </row>
     <row r="222" spans="1:10">
-      <c r="A222" s="1">
+      <c r="A222" s="2">
         <v>46143</v>
       </c>
       <c r="B222">
@@ -16215,7 +16241,7 @@
         <v>31</v>
       </c>
       <c r="G222">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="H222" t="s">
         <v>36</v>
@@ -16228,7 +16254,7 @@
       </c>
     </row>
     <row r="223" spans="1:10">
-      <c r="A223" s="1">
+      <c r="A223" s="2">
         <v>46174</v>
       </c>
       <c r="B223">
@@ -16247,7 +16273,7 @@
         <v>31</v>
       </c>
       <c r="G223">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="H223" t="s">
         <v>36</v>
@@ -16260,7 +16286,7 @@
       </c>
     </row>
     <row r="224" spans="1:10">
-      <c r="A224" s="1">
+      <c r="A224" s="2">
         <v>46204</v>
       </c>
       <c r="B224">
@@ -16279,7 +16305,7 @@
         <v>31</v>
       </c>
       <c r="G224">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="H224" t="s">
         <v>36</v>
@@ -16292,7 +16318,7 @@
       </c>
     </row>
     <row r="225" spans="1:10">
-      <c r="A225" s="1">
+      <c r="A225" s="2">
         <v>46235</v>
       </c>
       <c r="B225">
@@ -16311,7 +16337,7 @@
         <v>31</v>
       </c>
       <c r="G225">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H225" t="s">
         <v>36</v>
@@ -16324,7 +16350,7 @@
       </c>
     </row>
     <row r="226" spans="1:10">
-      <c r="A226" s="1">
+      <c r="A226" s="2">
         <v>46266</v>
       </c>
       <c r="B226">
@@ -16343,7 +16369,7 @@
         <v>31</v>
       </c>
       <c r="G226">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="H226" t="s">
         <v>36</v>
@@ -16366,19 +16392,19 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>66</v>
       </c>
     </row>
